--- a/output/2025-05-24.xlsx
+++ b/output/2025-05-24.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="F14" t="n">
-        <v>11.05</v>
+        <v>11.55</v>
       </c>
       <c r="G14" t="n">
-        <v>153</v>
+        <v>148.5</v>
       </c>
       <c r="H14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-19.78</v>
+        <v>-189.62</v>
       </c>
       <c r="K14" t="n">
-        <v>-92.28</v>
+        <v>-54.89</v>
       </c>
       <c r="L14" t="n">
-        <v>94.38</v>
+        <v>197.41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:48:14</t>
+          <t>04:47:54</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.12</v>
+        <v>3.64</v>
       </c>
       <c r="F15" t="n">
-        <v>10.8</v>
+        <v>11.92</v>
       </c>
       <c r="G15" t="n">
-        <v>158.7</v>
+        <v>150.1</v>
       </c>
       <c r="H15" t="n">
-        <v>9.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>101.31</v>
+        <v>-115.94</v>
       </c>
       <c r="K15" t="n">
-        <v>23.81</v>
+        <v>127.23</v>
       </c>
       <c r="L15" t="n">
-        <v>104.07</v>
+        <v>172.13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:50:00</t>
+          <t>04:49:53</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.94</v>
+        <v>3.41</v>
       </c>
       <c r="F16" t="n">
-        <v>11.35</v>
+        <v>11.53</v>
       </c>
       <c r="G16" t="n">
-        <v>158.1</v>
+        <v>130.3</v>
       </c>
       <c r="H16" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.470000000000001</v>
+        <v>19.33</v>
       </c>
       <c r="K16" t="n">
-        <v>44.72</v>
+        <v>322.52</v>
       </c>
       <c r="L16" t="n">
-        <v>45.52</v>
+        <v>323.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:56:36</t>
+          <t>04:53:51</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="F17" t="n">
-        <v>11.68</v>
+        <v>11.8</v>
       </c>
       <c r="G17" t="n">
-        <v>158.1</v>
+        <v>146.5</v>
       </c>
       <c r="H17" t="n">
-        <v>7.8</v>
+        <v>16.6</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-175.13</v>
+        <v>114.92</v>
       </c>
       <c r="K17" t="n">
-        <v>45.96</v>
+        <v>187.44</v>
       </c>
       <c r="L17" t="n">
-        <v>181.06</v>
+        <v>219.87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:58:25</t>
+          <t>04:55:45</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>3.68</v>
       </c>
       <c r="F18" t="n">
-        <v>11.1</v>
+        <v>11.92</v>
       </c>
       <c r="G18" t="n">
-        <v>150</v>
+        <v>146.8</v>
       </c>
       <c r="H18" t="n">
-        <v>6.1</v>
+        <v>12.6</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>-47.05</v>
+        <v>102.54</v>
       </c>
       <c r="K18" t="n">
-        <v>-50.61</v>
+        <v>154.54</v>
       </c>
       <c r="L18" t="n">
-        <v>69.09999999999999</v>
+        <v>185.47</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:59:43</t>
+          <t>04:57:31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.63</v>
+        <v>3.12</v>
       </c>
       <c r="F19" t="n">
-        <v>11.72</v>
+        <v>11.03</v>
       </c>
       <c r="G19" t="n">
-        <v>153.1</v>
+        <v>155.8</v>
       </c>
       <c r="H19" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="I19" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>83.43000000000001</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>2.98</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>83.48</v>
+        <v>111.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:03:44</t>
+          <t>05:01:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="F20" t="n">
-        <v>12.27</v>
+        <v>12.22</v>
       </c>
       <c r="G20" t="n">
-        <v>148.5</v>
+        <v>150.9</v>
       </c>
       <c r="H20" t="n">
-        <v>17.5</v>
+        <v>16.1</v>
       </c>
       <c r="I20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-31.48</v>
+        <v>43.16</v>
       </c>
       <c r="K20" t="n">
-        <v>-205.4</v>
+        <v>-124.12</v>
       </c>
       <c r="L20" t="n">
-        <v>207.8</v>
+        <v>131.41</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:05:54</t>
+          <t>05:02:18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="F21" t="n">
-        <v>11.86</v>
+        <v>11.87</v>
       </c>
       <c r="G21" t="n">
-        <v>147.7</v>
+        <v>155.2</v>
       </c>
       <c r="H21" t="n">
-        <v>8.5</v>
+        <v>16.5</v>
       </c>
       <c r="I21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>199.43</v>
+        <v>409.71</v>
       </c>
       <c r="K21" t="n">
-        <v>-118.04</v>
+        <v>54.85</v>
       </c>
       <c r="L21" t="n">
-        <v>231.75</v>
+        <v>413.37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:07:12</t>
+          <t>05:04:24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="F22" t="n">
-        <v>11.06</v>
+        <v>10.43</v>
       </c>
       <c r="G22" t="n">
-        <v>153.8</v>
+        <v>145.3</v>
       </c>
       <c r="H22" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="I22" t="n">
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-194.5</v>
+        <v>-40.62</v>
       </c>
       <c r="K22" t="n">
-        <v>-105.58</v>
+        <v>-155</v>
       </c>
       <c r="L22" t="n">
-        <v>221.31</v>
+        <v>160.23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:10:53</t>
+          <t>05:09:34</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="F23" t="n">
-        <v>11.71</v>
+        <v>10.9</v>
       </c>
       <c r="G23" t="n">
-        <v>148.8</v>
+        <v>151.8</v>
       </c>
       <c r="H23" t="n">
-        <v>10.7</v>
+        <v>14</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-202.13</v>
+        <v>289.4</v>
       </c>
       <c r="K23" t="n">
-        <v>137.09</v>
+        <v>-195.34</v>
       </c>
       <c r="L23" t="n">
-        <v>244.24</v>
+        <v>349.15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:11:56</t>
+          <t>05:12:06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.18</v>
+        <v>3.33</v>
       </c>
       <c r="F24" t="n">
-        <v>10.79</v>
+        <v>11.27</v>
       </c>
       <c r="G24" t="n">
-        <v>155.2</v>
+        <v>170.3</v>
       </c>
       <c r="H24" t="n">
-        <v>7.8</v>
+        <v>13.2</v>
       </c>
       <c r="I24" t="n">
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-276.86</v>
+        <v>-45.08</v>
       </c>
       <c r="K24" t="n">
-        <v>265.05</v>
+        <v>-310.07</v>
       </c>
       <c r="L24" t="n">
-        <v>383.28</v>
+        <v>313.33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:13:03</t>
+          <t>05:13:49</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="F25" t="n">
-        <v>10.95</v>
+        <v>11.04</v>
       </c>
       <c r="G25" t="n">
-        <v>164.3</v>
+        <v>154</v>
       </c>
       <c r="H25" t="n">
-        <v>12</v>
+        <v>11.4</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>129.84</v>
+        <v>64.05</v>
       </c>
       <c r="K25" t="n">
-        <v>229</v>
+        <v>115.18</v>
       </c>
       <c r="L25" t="n">
-        <v>263.25</v>
+        <v>131.79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:17:44</t>
+          <t>05:17:27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="F26" t="n">
-        <v>11.51</v>
+        <v>11.59</v>
       </c>
       <c r="G26" t="n">
-        <v>139.5</v>
+        <v>159.1</v>
       </c>
       <c r="H26" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="I26" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-339.55</v>
+        <v>463.76</v>
       </c>
       <c r="K26" t="n">
-        <v>-356.61</v>
+        <v>-190.52</v>
       </c>
       <c r="L26" t="n">
-        <v>492.4</v>
+        <v>501.37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:18:37</t>
+          <t>05:19:02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="F27" t="n">
-        <v>11.45</v>
+        <v>11.57</v>
       </c>
       <c r="G27" t="n">
-        <v>156.8</v>
+        <v>166.4</v>
       </c>
       <c r="H27" t="n">
-        <v>19.1</v>
+        <v>1.5</v>
       </c>
       <c r="I27" t="n">
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>704.37</v>
+        <v>806.8099999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>-435.44</v>
+        <v>136.46</v>
       </c>
       <c r="L27" t="n">
-        <v>828.1</v>
+        <v>818.27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:19:22</t>
+          <t>05:20:29</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.8</v>
+        <v>2.51</v>
       </c>
       <c r="F28" t="n">
-        <v>11.91</v>
+        <v>11.24</v>
       </c>
       <c r="G28" t="n">
-        <v>151.1</v>
+        <v>168.2</v>
       </c>
       <c r="H28" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>399.78</v>
+        <v>-45.2</v>
       </c>
       <c r="K28" t="n">
-        <v>427.45</v>
+        <v>421.05</v>
       </c>
       <c r="L28" t="n">
-        <v>585.27</v>
+        <v>423.47</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:30:58</t>
+          <t>05:32:23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.2</v>
+        <v>3.59</v>
       </c>
       <c r="F29" t="n">
-        <v>11.79</v>
+        <v>11.07</v>
       </c>
       <c r="G29" t="n">
-        <v>164.8</v>
+        <v>151.9</v>
       </c>
       <c r="H29" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.53</v>
+        <v>-48.35</v>
       </c>
       <c r="K29" t="n">
-        <v>-86.79000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="L29" t="n">
-        <v>86.8</v>
+        <v>70.42</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:33:23</t>
+          <t>05:33:54</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.41</v>
+        <v>3.7</v>
       </c>
       <c r="F30" t="n">
-        <v>10.98</v>
+        <v>11.47</v>
       </c>
       <c r="G30" t="n">
-        <v>134.5</v>
+        <v>158.4</v>
       </c>
       <c r="H30" t="n">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-116.77</v>
+        <v>188.97</v>
       </c>
       <c r="K30" t="n">
-        <v>39.73</v>
+        <v>174.31</v>
       </c>
       <c r="L30" t="n">
-        <v>123.35</v>
+        <v>257.09</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:34:00</t>
+          <t>05:34:47</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.57</v>
+        <v>3.29</v>
       </c>
       <c r="F31" t="n">
-        <v>10.49</v>
+        <v>10.98</v>
       </c>
       <c r="G31" t="n">
-        <v>166.6</v>
+        <v>148</v>
       </c>
       <c r="H31" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-77.11</v>
+        <v>-134.26</v>
       </c>
       <c r="K31" t="n">
-        <v>-9.93</v>
+        <v>-237.59</v>
       </c>
       <c r="L31" t="n">
-        <v>77.75</v>
+        <v>272.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:39:05</t>
+          <t>05:40:09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.57</v>
+        <v>3.14</v>
       </c>
       <c r="F32" t="n">
-        <v>10.97</v>
+        <v>11.35</v>
       </c>
       <c r="G32" t="n">
-        <v>159.9</v>
+        <v>148.8</v>
       </c>
       <c r="H32" t="n">
-        <v>12.5</v>
+        <v>17.6</v>
       </c>
       <c r="I32" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>116.18</v>
+        <v>-80.34999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>80.77</v>
+        <v>-97.18000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>141.5</v>
+        <v>126.09</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:40:55</t>
+          <t>05:42:46</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.25</v>
+        <v>3.57</v>
       </c>
       <c r="F33" t="n">
-        <v>10.93</v>
+        <v>10.79</v>
       </c>
       <c r="G33" t="n">
-        <v>156.5</v>
+        <v>157.1</v>
       </c>
       <c r="H33" t="n">
-        <v>11.9</v>
+        <v>10.6</v>
       </c>
       <c r="I33" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-5.71</v>
+        <v>-192.66</v>
       </c>
       <c r="K33" t="n">
-        <v>-154.98</v>
+        <v>-109.61</v>
       </c>
       <c r="L33" t="n">
-        <v>155.09</v>
+        <v>221.65</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:42:34</t>
+          <t>05:43:46</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.3</v>
+        <v>4.72</v>
       </c>
       <c r="F34" t="n">
-        <v>11.78</v>
+        <v>11.72</v>
       </c>
       <c r="G34" t="n">
-        <v>160.6</v>
+        <v>162.2</v>
       </c>
       <c r="H34" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="I34" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>108.59</v>
+        <v>-299.36</v>
       </c>
       <c r="K34" t="n">
-        <v>-140.47</v>
+        <v>-37</v>
       </c>
       <c r="L34" t="n">
-        <v>177.54</v>
+        <v>301.63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:47:32</t>
+          <t>05:48:41</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.96</v>
+        <v>3.27</v>
       </c>
       <c r="F35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G35" t="n">
-        <v>150.3</v>
+        <v>147.5</v>
       </c>
       <c r="H35" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="I35" t="n">
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-45.62</v>
+        <v>-164.83</v>
       </c>
       <c r="K35" t="n">
-        <v>-134.71</v>
+        <v>-175.15</v>
       </c>
       <c r="L35" t="n">
-        <v>142.22</v>
+        <v>240.52</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:49:02</t>
+          <t>05:50:06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="F36" t="n">
-        <v>11.59</v>
+        <v>11.07</v>
       </c>
       <c r="G36" t="n">
-        <v>141.2</v>
+        <v>145.6</v>
       </c>
       <c r="H36" t="n">
-        <v>5.8</v>
+        <v>11.4</v>
       </c>
       <c r="I36" t="n">
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.28</v>
+        <v>-133.05</v>
       </c>
       <c r="K36" t="n">
-        <v>125.64</v>
+        <v>-446.86</v>
       </c>
       <c r="L36" t="n">
-        <v>125.68</v>
+        <v>466.25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:51:39</t>
+          <t>05:52:04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.86</v>
+        <v>3.6</v>
       </c>
       <c r="F37" t="n">
-        <v>11.47</v>
+        <v>11.36</v>
       </c>
       <c r="G37" t="n">
-        <v>149.3</v>
+        <v>158.9</v>
       </c>
       <c r="H37" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="I37" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>43.74</v>
+        <v>243.67</v>
       </c>
       <c r="K37" t="n">
-        <v>266.81</v>
+        <v>-475.18</v>
       </c>
       <c r="L37" t="n">
-        <v>270.37</v>
+        <v>534.02</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:54:44</t>
+          <t>05:57:08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.38</v>
+        <v>3.01</v>
       </c>
       <c r="F38" t="n">
-        <v>10.43</v>
+        <v>11.17</v>
       </c>
       <c r="G38" t="n">
-        <v>157.6</v>
+        <v>150.7</v>
       </c>
       <c r="H38" t="n">
-        <v>20.5</v>
+        <v>4.6</v>
       </c>
       <c r="I38" t="n">
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-37.5</v>
+        <v>-11.35</v>
       </c>
       <c r="K38" t="n">
-        <v>272</v>
+        <v>-103.81</v>
       </c>
       <c r="L38" t="n">
-        <v>274.57</v>
+        <v>104.42</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:56:28</t>
+          <t>05:58:32</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.71</v>
+        <v>3.36</v>
       </c>
       <c r="F39" t="n">
-        <v>10.82</v>
+        <v>12.05</v>
       </c>
       <c r="G39" t="n">
-        <v>165.4</v>
+        <v>144.8</v>
       </c>
       <c r="H39" t="n">
-        <v>13.4</v>
+        <v>16.2</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>446.13</v>
+        <v>-185.51</v>
       </c>
       <c r="K39" t="n">
-        <v>223.76</v>
+        <v>101.18</v>
       </c>
       <c r="L39" t="n">
-        <v>499.1</v>
+        <v>211.31</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:57:33</t>
+          <t>05:59:59</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.64</v>
+        <v>3.71</v>
       </c>
       <c r="F40" t="n">
-        <v>11.26</v>
+        <v>11.15</v>
       </c>
       <c r="G40" t="n">
-        <v>154.8</v>
+        <v>163.9</v>
       </c>
       <c r="H40" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="I40" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>-313.44</v>
+        <v>594.08</v>
       </c>
       <c r="K40" t="n">
-        <v>190.44</v>
+        <v>-503.83</v>
       </c>
       <c r="L40" t="n">
-        <v>366.76</v>
+        <v>778.96</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:01:02</t>
+          <t>06:04:38</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="F41" t="n">
-        <v>11.97</v>
+        <v>11.53</v>
       </c>
       <c r="G41" t="n">
-        <v>163.1</v>
+        <v>143.9</v>
       </c>
       <c r="H41" t="n">
-        <v>9.5</v>
+        <v>15</v>
       </c>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-41.61</v>
+        <v>820.09</v>
       </c>
       <c r="K41" t="n">
-        <v>39.45</v>
+        <v>234</v>
       </c>
       <c r="L41" t="n">
-        <v>57.34</v>
+        <v>852.8200000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:02:04</t>
+          <t>06:06:40</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.86</v>
+        <v>3.51</v>
       </c>
       <c r="F42" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="G42" t="n">
+        <v>160.1</v>
+      </c>
+      <c r="H42" t="n">
         <v>11.6</v>
       </c>
-      <c r="G42" t="n">
-        <v>151.7</v>
-      </c>
-      <c r="H42" t="n">
-        <v>8.9</v>
-      </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-21.36</v>
+        <v>363.88</v>
       </c>
       <c r="K42" t="n">
-        <v>316.65</v>
+        <v>-585.54</v>
       </c>
       <c r="L42" t="n">
-        <v>317.37</v>
+        <v>689.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:04:02</t>
+          <t>06:08:15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.16</v>
+        <v>3.6</v>
       </c>
       <c r="F43" t="n">
-        <v>11.65</v>
+        <v>11.33</v>
       </c>
       <c r="G43" t="n">
-        <v>146.8</v>
+        <v>140.8</v>
       </c>
       <c r="H43" t="n">
-        <v>10.5</v>
+        <v>15.4</v>
       </c>
       <c r="I43" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-150.94</v>
+        <v>-62.55</v>
       </c>
       <c r="K43" t="n">
-        <v>-226.08</v>
+        <v>-590.4400000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>271.83</v>
+        <v>593.74</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:15:06</t>
+          <t>06:18:42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="F44" t="n">
-        <v>10.82</v>
+        <v>11.4</v>
       </c>
       <c r="G44" t="n">
-        <v>151.2</v>
+        <v>164.3</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8</v>
+        <v>14.4</v>
       </c>
       <c r="I44" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>26.33</v>
+        <v>166.02</v>
       </c>
       <c r="K44" t="n">
-        <v>-45.15</v>
+        <v>-113.23</v>
       </c>
       <c r="L44" t="n">
-        <v>52.27</v>
+        <v>200.96</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:17:13</t>
+          <t>06:21:14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.3</v>
+        <v>4.09</v>
       </c>
       <c r="F45" t="n">
-        <v>11.86</v>
+        <v>10.84</v>
       </c>
       <c r="G45" t="n">
-        <v>140.7</v>
+        <v>153.9</v>
       </c>
       <c r="H45" t="n">
-        <v>13.1</v>
+        <v>12.6</v>
       </c>
       <c r="I45" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>-36.82</v>
+        <v>232.05</v>
       </c>
       <c r="K45" t="n">
-        <v>-112.59</v>
+        <v>35.35</v>
       </c>
       <c r="L45" t="n">
-        <v>118.46</v>
+        <v>234.72</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:19:14</t>
+          <t>06:22:10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.37</v>
+        <v>4.11</v>
       </c>
       <c r="F46" t="n">
-        <v>11.58</v>
+        <v>11.79</v>
       </c>
       <c r="G46" t="n">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="H46" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-161.98</v>
+        <v>-62.27</v>
       </c>
       <c r="K46" t="n">
-        <v>-178.9</v>
+        <v>-130.85</v>
       </c>
       <c r="L46" t="n">
-        <v>241.33</v>
+        <v>144.92</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:23:39</t>
+          <t>06:26:38</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.47</v>
+        <v>4</v>
       </c>
       <c r="F47" t="n">
         <v>11.62</v>
       </c>
       <c r="G47" t="n">
-        <v>149.8</v>
+        <v>151.2</v>
       </c>
       <c r="H47" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="I47" t="n">
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>336.87</v>
+        <v>19.83</v>
       </c>
       <c r="K47" t="n">
-        <v>165.92</v>
+        <v>173.23</v>
       </c>
       <c r="L47" t="n">
-        <v>375.51</v>
+        <v>174.37</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:24:41</t>
+          <t>06:28:36</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.26</v>
+        <v>3.56</v>
       </c>
       <c r="F48" t="n">
-        <v>12.07</v>
+        <v>11.19</v>
       </c>
       <c r="G48" t="n">
-        <v>146.9</v>
+        <v>161.7</v>
       </c>
       <c r="H48" t="n">
-        <v>15.7</v>
+        <v>16.8</v>
       </c>
       <c r="I48" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>-69.53</v>
+        <v>80.13</v>
       </c>
       <c r="K48" t="n">
-        <v>-68.03</v>
+        <v>-113.97</v>
       </c>
       <c r="L48" t="n">
-        <v>97.28</v>
+        <v>139.32</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:27:20</t>
+          <t>06:30:36</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.87</v>
+        <v>3.41</v>
       </c>
       <c r="F49" t="n">
-        <v>11.59</v>
+        <v>11.05</v>
       </c>
       <c r="G49" t="n">
-        <v>147.7</v>
+        <v>163</v>
       </c>
       <c r="H49" t="n">
-        <v>17.8</v>
+        <v>10.3</v>
       </c>
       <c r="I49" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>60.34</v>
+        <v>-63.42</v>
       </c>
       <c r="K49" t="n">
-        <v>-65.56</v>
+        <v>2.22</v>
       </c>
       <c r="L49" t="n">
-        <v>89.09999999999999</v>
+        <v>63.46</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:32:02</t>
+          <t>06:36:49</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.55</v>
+        <v>2.95</v>
       </c>
       <c r="F50" t="n">
-        <v>10.88</v>
+        <v>11.87</v>
       </c>
       <c r="G50" t="n">
-        <v>153.8</v>
+        <v>145</v>
       </c>
       <c r="H50" t="n">
-        <v>8.5</v>
+        <v>16.7</v>
       </c>
       <c r="I50" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>194.86</v>
+        <v>137.01</v>
       </c>
       <c r="K50" t="n">
-        <v>29.57</v>
+        <v>-70.66</v>
       </c>
       <c r="L50" t="n">
-        <v>197.09</v>
+        <v>154.16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:33:49</t>
+          <t>06:37:48</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.24</v>
+        <v>4.11</v>
       </c>
       <c r="F51" t="n">
-        <v>12.03</v>
+        <v>11.39</v>
       </c>
       <c r="G51" t="n">
-        <v>148.4</v>
+        <v>152.2</v>
       </c>
       <c r="H51" t="n">
-        <v>11.4</v>
+        <v>16.4</v>
       </c>
       <c r="I51" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-100.6</v>
+        <v>-60.77</v>
       </c>
       <c r="K51" t="n">
-        <v>-272.96</v>
+        <v>441.63</v>
       </c>
       <c r="L51" t="n">
-        <v>290.91</v>
+        <v>445.79</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:34:34</t>
+          <t>06:40:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.01</v>
+        <v>3.9</v>
       </c>
       <c r="F52" t="n">
-        <v>11.82</v>
+        <v>11.73</v>
       </c>
       <c r="G52" t="n">
-        <v>164.3</v>
+        <v>157.6</v>
       </c>
       <c r="H52" t="n">
-        <v>9.699999999999999</v>
+        <v>17.9</v>
       </c>
       <c r="I52" t="n">
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-378.69</v>
+        <v>101.96</v>
       </c>
       <c r="K52" t="n">
-        <v>122.46</v>
+        <v>-466.16</v>
       </c>
       <c r="L52" t="n">
-        <v>398</v>
+        <v>477.18</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:40:27</t>
+          <t>06:44:41</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="F53" t="n">
-        <v>10.69</v>
+        <v>11.46</v>
       </c>
       <c r="G53" t="n">
-        <v>166.2</v>
+        <v>161.2</v>
       </c>
       <c r="H53" t="n">
-        <v>8.6</v>
+        <v>11.8</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>2.15</v>
+        <v>37.56</v>
       </c>
       <c r="K53" t="n">
-        <v>-162.71</v>
+        <v>81.72</v>
       </c>
       <c r="L53" t="n">
-        <v>162.72</v>
+        <v>89.94</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:42:18</t>
+          <t>06:47:02</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="F54" t="n">
-        <v>11.27</v>
+        <v>11.17</v>
       </c>
       <c r="G54" t="n">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="H54" t="n">
-        <v>10.8</v>
+        <v>13.8</v>
       </c>
       <c r="I54" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-471.54</v>
+        <v>391.48</v>
       </c>
       <c r="K54" t="n">
-        <v>12.01</v>
+        <v>-243.74</v>
       </c>
       <c r="L54" t="n">
-        <v>471.69</v>
+        <v>461.15</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:43:29</t>
+          <t>06:47:38</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.42</v>
+        <v>4.47</v>
       </c>
       <c r="F55" t="n">
-        <v>10.43</v>
+        <v>11.22</v>
       </c>
       <c r="G55" t="n">
-        <v>146.6</v>
+        <v>163.4</v>
       </c>
       <c r="H55" t="n">
-        <v>15</v>
+        <v>6.4</v>
       </c>
       <c r="I55" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-301.57</v>
+        <v>-95.12</v>
       </c>
       <c r="K55" t="n">
-        <v>-5.86</v>
+        <v>431.35</v>
       </c>
       <c r="L55" t="n">
-        <v>301.63</v>
+        <v>441.72</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:47:42</t>
+          <t>06:52:15</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.19</v>
+        <v>3.83</v>
       </c>
       <c r="F56" t="n">
-        <v>11.6</v>
+        <v>11.31</v>
       </c>
       <c r="G56" t="n">
-        <v>145.9</v>
+        <v>165.8</v>
       </c>
       <c r="H56" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>-903.38</v>
+        <v>340.36</v>
       </c>
       <c r="K56" t="n">
-        <v>-664.99</v>
+        <v>-1439.78</v>
       </c>
       <c r="L56" t="n">
-        <v>1121.74</v>
+        <v>1479.47</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:50:07</t>
+          <t>06:53:06</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.42</v>
+        <v>4.13</v>
       </c>
       <c r="F57" t="n">
-        <v>10.64</v>
+        <v>11.6</v>
       </c>
       <c r="G57" t="n">
-        <v>165.8</v>
+        <v>166.1</v>
       </c>
       <c r="H57" t="n">
-        <v>11.4</v>
+        <v>17.6</v>
       </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>186.84</v>
+        <v>44.86</v>
       </c>
       <c r="K57" t="n">
-        <v>-146.63</v>
+        <v>259.68</v>
       </c>
       <c r="L57" t="n">
-        <v>237.5</v>
+        <v>263.53</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:51:25</t>
+          <t>06:54:47</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.05</v>
+        <v>4.03</v>
       </c>
       <c r="F58" t="n">
-        <v>11.59</v>
+        <v>11.11</v>
       </c>
       <c r="G58" t="n">
-        <v>156.6</v>
+        <v>155.4</v>
       </c>
       <c r="H58" t="n">
-        <v>12.4</v>
+        <v>17.6</v>
       </c>
       <c r="I58" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>219.13</v>
+        <v>124.68</v>
       </c>
       <c r="K58" t="n">
-        <v>-97.5</v>
+        <v>-138.74</v>
       </c>
       <c r="L58" t="n">
-        <v>239.84</v>
+        <v>186.53</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:01:55</t>
+          <t>07:05:15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.08</v>
+        <v>3.33</v>
       </c>
       <c r="F59" t="n">
-        <v>11.29</v>
+        <v>11.43</v>
       </c>
       <c r="G59" t="n">
-        <v>140.7</v>
+        <v>142</v>
       </c>
       <c r="H59" t="n">
-        <v>16.2</v>
+        <v>13.1</v>
       </c>
       <c r="I59" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>0.6899999999999999</v>
+        <v>17.43</v>
       </c>
       <c r="K59" t="n">
-        <v>-54.4</v>
+        <v>111.23</v>
       </c>
       <c r="L59" t="n">
-        <v>54.41</v>
+        <v>112.59</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:04:22</t>
+          <t>07:07:12</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.6</v>
+        <v>3.97</v>
       </c>
       <c r="F60" t="n">
-        <v>11.41</v>
+        <v>11.49</v>
       </c>
       <c r="G60" t="n">
-        <v>159.4</v>
+        <v>156.7</v>
       </c>
       <c r="H60" t="n">
-        <v>15.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>-33.36</v>
+        <v>-165.14</v>
       </c>
       <c r="K60" t="n">
-        <v>38.32</v>
+        <v>-159.49</v>
       </c>
       <c r="L60" t="n">
-        <v>50.81</v>
+        <v>229.58</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:07:07</t>
+          <t>07:08:46</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.63</v>
+        <v>3.71</v>
       </c>
       <c r="F61" t="n">
-        <v>10.74</v>
+        <v>11.85</v>
       </c>
       <c r="G61" t="n">
-        <v>144.1</v>
+        <v>152.1</v>
       </c>
       <c r="H61" t="n">
-        <v>14.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I61" t="n">
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.73</v>
+        <v>118.89</v>
       </c>
       <c r="K61" t="n">
-        <v>164.12</v>
+        <v>-80.20999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>164.47</v>
+        <v>143.42</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:12:59</t>
+          <t>07:13:07</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.63</v>
+        <v>3.56</v>
       </c>
       <c r="F62" t="n">
-        <v>11.12</v>
+        <v>11.25</v>
       </c>
       <c r="G62" t="n">
-        <v>149.3</v>
+        <v>147.4</v>
       </c>
       <c r="H62" t="n">
-        <v>8.1</v>
+        <v>10.3</v>
       </c>
       <c r="I62" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>6.21</v>
+        <v>57.83</v>
       </c>
       <c r="K62" t="n">
-        <v>-73.02</v>
+        <v>-448.43</v>
       </c>
       <c r="L62" t="n">
-        <v>73.29000000000001</v>
+        <v>452.14</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:15:09</t>
+          <t>07:14:13</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.56</v>
+        <v>4.05</v>
       </c>
       <c r="F63" t="n">
-        <v>10.75</v>
+        <v>11.15</v>
       </c>
       <c r="G63" t="n">
-        <v>157.9</v>
+        <v>162</v>
       </c>
       <c r="H63" t="n">
-        <v>10.4</v>
+        <v>20.1</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>3.41</v>
+        <v>-189.08</v>
       </c>
       <c r="K63" t="n">
-        <v>-16.6</v>
+        <v>-312.87</v>
       </c>
       <c r="L63" t="n">
-        <v>16.95</v>
+        <v>365.57</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:17:17</t>
+          <t>07:15:15</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.26</v>
+        <v>4.41</v>
       </c>
       <c r="F64" t="n">
-        <v>10.7</v>
+        <v>11.62</v>
       </c>
       <c r="G64" t="n">
-        <v>151.4</v>
+        <v>143.7</v>
       </c>
       <c r="H64" t="n">
-        <v>15.2</v>
+        <v>3.9</v>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>88.22</v>
+        <v>-115.42</v>
       </c>
       <c r="K64" t="n">
-        <v>-97.95999999999999</v>
+        <v>319.77</v>
       </c>
       <c r="L64" t="n">
-        <v>131.83</v>
+        <v>339.96</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:21:58</t>
+          <t>07:19:57</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.64</v>
+        <v>4.53</v>
       </c>
       <c r="F65" t="n">
-        <v>11.03</v>
+        <v>10.51</v>
       </c>
       <c r="G65" t="n">
-        <v>147.1</v>
+        <v>150</v>
       </c>
       <c r="H65" t="n">
-        <v>11.8</v>
+        <v>15</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-42.63</v>
+        <v>-4.58</v>
       </c>
       <c r="K65" t="n">
-        <v>62.79</v>
+        <v>201.38</v>
       </c>
       <c r="L65" t="n">
-        <v>75.89</v>
+        <v>201.43</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:23:07</t>
+          <t>07:20:53</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="F66" t="n">
-        <v>11.53</v>
+        <v>11.47</v>
       </c>
       <c r="G66" t="n">
-        <v>139.6</v>
+        <v>165.6</v>
       </c>
       <c r="H66" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="I66" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>111.55</v>
+        <v>-4.23</v>
       </c>
       <c r="K66" t="n">
-        <v>-316.66</v>
+        <v>-106.28</v>
       </c>
       <c r="L66" t="n">
-        <v>335.73</v>
+        <v>106.37</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:25:04</t>
+          <t>07:22:18</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.05</v>
+        <v>3.18</v>
       </c>
       <c r="F67" t="n">
-        <v>10.83</v>
+        <v>10.86</v>
       </c>
       <c r="G67" t="n">
-        <v>167.3</v>
+        <v>150.2</v>
       </c>
       <c r="H67" t="n">
-        <v>17.2</v>
+        <v>9.6</v>
       </c>
       <c r="I67" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>228.36</v>
+        <v>120.06</v>
       </c>
       <c r="K67" t="n">
-        <v>173.6</v>
+        <v>-167.16</v>
       </c>
       <c r="L67" t="n">
-        <v>286.85</v>
+        <v>205.81</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:29:11</t>
+          <t>07:26:36</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.62</v>
+        <v>4.14</v>
       </c>
       <c r="F68" t="n">
-        <v>11.36</v>
+        <v>11.48</v>
       </c>
       <c r="G68" t="n">
-        <v>154.6</v>
+        <v>165.5</v>
       </c>
       <c r="H68" t="n">
-        <v>9.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="I68" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>-35.41</v>
+        <v>275.27</v>
       </c>
       <c r="K68" t="n">
-        <v>76.25</v>
+        <v>-325.55</v>
       </c>
       <c r="L68" t="n">
-        <v>84.06999999999999</v>
+        <v>426.33</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:31:41</t>
+          <t>07:28:01</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.77</v>
+        <v>3.58</v>
       </c>
       <c r="F69" t="n">
-        <v>11.71</v>
+        <v>12.07</v>
       </c>
       <c r="G69" t="n">
-        <v>136.2</v>
+        <v>149.5</v>
       </c>
       <c r="H69" t="n">
-        <v>9.800000000000001</v>
+        <v>11.7</v>
       </c>
       <c r="I69" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>384.8</v>
+        <v>130.12</v>
       </c>
       <c r="K69" t="n">
-        <v>-211.78</v>
+        <v>-177.95</v>
       </c>
       <c r="L69" t="n">
-        <v>439.23</v>
+        <v>220.45</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:32:33</t>
+          <t>07:29:56</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
       <c r="F70" t="n">
-        <v>11.65</v>
+        <v>11.66</v>
       </c>
       <c r="G70" t="n">
-        <v>159</v>
+        <v>149.5</v>
       </c>
       <c r="H70" t="n">
-        <v>8.9</v>
+        <v>9.9</v>
       </c>
       <c r="I70" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>-172.37</v>
+        <v>284.74</v>
       </c>
       <c r="K70" t="n">
-        <v>-475.61</v>
+        <v>-283.59</v>
       </c>
       <c r="L70" t="n">
-        <v>505.88</v>
+        <v>401.87</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:37:46</t>
+          <t>07:34:05</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.01</v>
+        <v>3.71</v>
       </c>
       <c r="F71" t="n">
-        <v>11.71</v>
+        <v>11.07</v>
       </c>
       <c r="G71" t="n">
-        <v>166.1</v>
+        <v>157</v>
       </c>
       <c r="H71" t="n">
-        <v>18</v>
+        <v>5.6</v>
       </c>
       <c r="I71" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>-689.4</v>
+        <v>681.13</v>
       </c>
       <c r="K71" t="n">
-        <v>-842.42</v>
+        <v>-980.1799999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>1088.55</v>
+        <v>1193.6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:39:39</t>
+          <t>07:36:26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.03</v>
+        <v>3.55</v>
       </c>
       <c r="F72" t="n">
-        <v>11.39</v>
+        <v>11.43</v>
       </c>
       <c r="G72" t="n">
-        <v>152.4</v>
+        <v>162</v>
       </c>
       <c r="H72" t="n">
-        <v>3.6</v>
+        <v>11.4</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-547.16</v>
+        <v>-367.23</v>
       </c>
       <c r="K72" t="n">
-        <v>-727.9400000000001</v>
+        <v>-514.84</v>
       </c>
       <c r="L72" t="n">
-        <v>910.65</v>
+        <v>632.39</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:42:04</t>
+          <t>07:38:23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="F73" t="n">
-        <v>11.53</v>
+        <v>11</v>
       </c>
       <c r="G73" t="n">
-        <v>158.7</v>
+        <v>149.3</v>
       </c>
       <c r="H73" t="n">
-        <v>8.300000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="I73" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-35.62</v>
+        <v>-190.53</v>
       </c>
       <c r="K73" t="n">
-        <v>-66.48</v>
+        <v>-359.42</v>
       </c>
       <c r="L73" t="n">
-        <v>75.42</v>
+        <v>406.8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:54:39</t>
+          <t>07:48:48</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.53</v>
+        <v>4.07</v>
       </c>
       <c r="F74" t="n">
-        <v>11.42</v>
+        <v>11.68</v>
       </c>
       <c r="G74" t="n">
-        <v>157.1</v>
+        <v>163.5</v>
       </c>
       <c r="H74" t="n">
-        <v>10.7</v>
+        <v>6.7</v>
       </c>
       <c r="I74" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>70.31</v>
+        <v>207.88</v>
       </c>
       <c r="K74" t="n">
-        <v>0.07000000000000001</v>
+        <v>-26.96</v>
       </c>
       <c r="L74" t="n">
-        <v>70.31</v>
+        <v>209.62</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:56:18</t>
+          <t>07:50:57</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.53</v>
+        <v>3.98</v>
       </c>
       <c r="F75" t="n">
-        <v>11.39</v>
+        <v>11.59</v>
       </c>
       <c r="G75" t="n">
-        <v>173.7</v>
+        <v>154.9</v>
       </c>
       <c r="H75" t="n">
-        <v>5</v>
+        <v>13.2</v>
       </c>
       <c r="I75" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-33.49</v>
+        <v>-103.2</v>
       </c>
       <c r="K75" t="n">
-        <v>-127</v>
+        <v>-115.54</v>
       </c>
       <c r="L75" t="n">
-        <v>131.34</v>
+        <v>154.92</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:58:48</t>
+          <t>07:53:02</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="F76" t="n">
-        <v>11.2</v>
+        <v>11.51</v>
       </c>
       <c r="G76" t="n">
-        <v>147.9</v>
+        <v>159.7</v>
       </c>
       <c r="H76" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>27.7</v>
+        <v>192.09</v>
       </c>
       <c r="K76" t="n">
-        <v>102.07</v>
+        <v>103.5</v>
       </c>
       <c r="L76" t="n">
-        <v>105.77</v>
+        <v>218.2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:03:59</t>
+          <t>07:57:01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.68</v>
+        <v>3.84</v>
       </c>
       <c r="F77" t="n">
-        <v>11.72</v>
+        <v>11.59</v>
       </c>
       <c r="G77" t="n">
-        <v>148.7</v>
+        <v>147.9</v>
       </c>
       <c r="H77" t="n">
-        <v>16</v>
+        <v>5.3</v>
       </c>
       <c r="I77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>44.64</v>
+        <v>-129.24</v>
       </c>
       <c r="K77" t="n">
-        <v>-115.96</v>
+        <v>-77.38</v>
       </c>
       <c r="L77" t="n">
-        <v>124.25</v>
+        <v>150.64</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:06:34</t>
+          <t>07:58:01</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.52</v>
+        <v>4.91</v>
       </c>
       <c r="F78" t="n">
-        <v>11.51</v>
+        <v>11.54</v>
       </c>
       <c r="G78" t="n">
-        <v>147</v>
+        <v>148.1</v>
       </c>
       <c r="H78" t="n">
-        <v>11.6</v>
+        <v>15.8</v>
       </c>
       <c r="I78" t="n">
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>190.16</v>
+        <v>-73.73</v>
       </c>
       <c r="K78" t="n">
-        <v>12.93</v>
+        <v>112.08</v>
       </c>
       <c r="L78" t="n">
-        <v>190.6</v>
+        <v>134.15</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:08:25</t>
+          <t>07:59:16</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.55</v>
+        <v>3.33</v>
       </c>
       <c r="F79" t="n">
-        <v>11.14</v>
+        <v>11.16</v>
       </c>
       <c r="G79" t="n">
-        <v>152</v>
+        <v>158.3</v>
       </c>
       <c r="H79" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="I79" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>109.97</v>
+        <v>-102.26</v>
       </c>
       <c r="K79" t="n">
-        <v>26.87</v>
+        <v>-56.24</v>
       </c>
       <c r="L79" t="n">
-        <v>113.21</v>
+        <v>116.7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:13:27</t>
+          <t>08:04:11</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="F80" t="n">
-        <v>11.2</v>
+        <v>12.04</v>
       </c>
       <c r="G80" t="n">
-        <v>151.9</v>
+        <v>167.3</v>
       </c>
       <c r="H80" t="n">
-        <v>5.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-235.65</v>
+        <v>-80.20999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>270.53</v>
+        <v>-154.14</v>
       </c>
       <c r="L80" t="n">
-        <v>358.77</v>
+        <v>173.76</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:14:23</t>
+          <t>08:05:03</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.07</v>
+        <v>3.98</v>
       </c>
       <c r="F81" t="n">
-        <v>12.01</v>
+        <v>11.43</v>
       </c>
       <c r="G81" t="n">
-        <v>154.7</v>
+        <v>157.3</v>
       </c>
       <c r="H81" t="n">
-        <v>15.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>202.97</v>
+        <v>36.72</v>
       </c>
       <c r="K81" t="n">
-        <v>59.57</v>
+        <v>-169.36</v>
       </c>
       <c r="L81" t="n">
-        <v>211.53</v>
+        <v>173.3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:15:48</t>
+          <t>08:07:36</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.32</v>
+        <v>3.6</v>
       </c>
       <c r="F82" t="n">
-        <v>10.69</v>
+        <v>11.82</v>
       </c>
       <c r="G82" t="n">
-        <v>149.7</v>
+        <v>148.6</v>
       </c>
       <c r="H82" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="I82" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>2.34</v>
+        <v>407.79</v>
       </c>
       <c r="K82" t="n">
-        <v>-389.14</v>
+        <v>118.92</v>
       </c>
       <c r="L82" t="n">
-        <v>389.15</v>
+        <v>424.78</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:21:35</t>
+          <t>08:12:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="F83" t="n">
-        <v>10.99</v>
+        <v>11.62</v>
       </c>
       <c r="G83" t="n">
-        <v>153.8</v>
+        <v>156.3</v>
       </c>
       <c r="H83" t="n">
-        <v>2.5</v>
+        <v>19.3</v>
       </c>
       <c r="I83" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-176.84</v>
+        <v>116.13</v>
       </c>
       <c r="K83" t="n">
-        <v>-475.67</v>
+        <v>-127.46</v>
       </c>
       <c r="L83" t="n">
-        <v>507.48</v>
+        <v>172.43</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:23:33</t>
+          <t>08:14:03</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="F84" t="n">
-        <v>11.26</v>
+        <v>12.02</v>
       </c>
       <c r="G84" t="n">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H84" t="n">
-        <v>7.6</v>
+        <v>15.5</v>
       </c>
       <c r="I84" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-16.26</v>
+        <v>-117.66</v>
       </c>
       <c r="K84" t="n">
-        <v>227.21</v>
+        <v>-182.86</v>
       </c>
       <c r="L84" t="n">
-        <v>227.79</v>
+        <v>217.44</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:25:50</t>
+          <t>08:15:55</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>5.69</v>
+        <v>4.57</v>
       </c>
       <c r="F85" t="n">
-        <v>12.34</v>
+        <v>11.3</v>
       </c>
       <c r="G85" t="n">
-        <v>147.3</v>
+        <v>163.6</v>
       </c>
       <c r="H85" t="n">
-        <v>14</v>
+        <v>16.3</v>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>222.83</v>
+        <v>177.64</v>
       </c>
       <c r="K85" t="n">
-        <v>694.02</v>
+        <v>-150.57</v>
       </c>
       <c r="L85" t="n">
-        <v>728.91</v>
+        <v>232.87</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:30:02</t>
+          <t>08:21:33</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="F86" t="n">
-        <v>11.52</v>
+        <v>10.87</v>
       </c>
       <c r="G86" t="n">
-        <v>142.9</v>
+        <v>152.5</v>
       </c>
       <c r="H86" t="n">
-        <v>4</v>
+        <v>17.8</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>403.69</v>
+        <v>700.96</v>
       </c>
       <c r="K86" t="n">
-        <v>453.55</v>
+        <v>91.5</v>
       </c>
       <c r="L86" t="n">
-        <v>607.1799999999999</v>
+        <v>706.9</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:32:12</t>
+          <t>08:22:23</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.7</v>
+        <v>4.56</v>
       </c>
       <c r="F87" t="n">
-        <v>11.14</v>
+        <v>11.4</v>
       </c>
       <c r="G87" t="n">
-        <v>159.2</v>
+        <v>143.9</v>
       </c>
       <c r="H87" t="n">
-        <v>13.2</v>
+        <v>6.2</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>21.41</v>
+        <v>-255.65</v>
       </c>
       <c r="K87" t="n">
-        <v>46.58</v>
+        <v>-165.04</v>
       </c>
       <c r="L87" t="n">
-        <v>51.26</v>
+        <v>304.3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:34:10</t>
+          <t>08:24:35</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.22</v>
+        <v>4.23</v>
       </c>
       <c r="F88" t="n">
-        <v>11.08</v>
+        <v>11.77</v>
       </c>
       <c r="G88" t="n">
-        <v>154.7</v>
+        <v>150.7</v>
       </c>
       <c r="H88" t="n">
-        <v>14.1</v>
+        <v>8.5</v>
       </c>
       <c r="I88" t="n">
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>-92.31999999999999</v>
+        <v>167.74</v>
       </c>
       <c r="K88" t="n">
-        <v>-411.17</v>
+        <v>602.47</v>
       </c>
       <c r="L88" t="n">
-        <v>421.41</v>
+        <v>625.39</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-24.xlsx
+++ b/output/2025-05-24.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-189.62</v>
+        <v>-164.56</v>
       </c>
       <c r="K14" t="n">
-        <v>-54.89</v>
+        <v>-47.64</v>
       </c>
       <c r="L14" t="n">
-        <v>197.41</v>
+        <v>171.32</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-115.94</v>
+        <v>-112.48</v>
       </c>
       <c r="K15" t="n">
-        <v>127.23</v>
+        <v>123.44</v>
       </c>
       <c r="L15" t="n">
-        <v>172.13</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>19.33</v>
+        <v>17.14</v>
       </c>
       <c r="K16" t="n">
-        <v>322.52</v>
+        <v>285.94</v>
       </c>
       <c r="L16" t="n">
-        <v>323.1</v>
+        <v>286.45</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>114.92</v>
+        <v>124.76</v>
       </c>
       <c r="K17" t="n">
-        <v>187.44</v>
+        <v>203.49</v>
       </c>
       <c r="L17" t="n">
-        <v>219.87</v>
+        <v>238.69</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>102.54</v>
+        <v>97.64</v>
       </c>
       <c r="K18" t="n">
-        <v>154.54</v>
+        <v>147.15</v>
       </c>
       <c r="L18" t="n">
-        <v>185.47</v>
+        <v>176.59</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>77.73999999999999</v>
+        <v>86.06</v>
       </c>
       <c r="K19" t="n">
-        <v>80.48999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>111.9</v>
+        <v>123.88</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>43.16</v>
+        <v>66.95</v>
       </c>
       <c r="K20" t="n">
-        <v>-124.12</v>
+        <v>-192.52</v>
       </c>
       <c r="L20" t="n">
-        <v>131.41</v>
+        <v>203.83</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>409.71</v>
+        <v>409.01</v>
       </c>
       <c r="K21" t="n">
-        <v>54.85</v>
+        <v>54.75</v>
       </c>
       <c r="L21" t="n">
-        <v>413.37</v>
+        <v>412.66</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-40.62</v>
+        <v>-55.32</v>
       </c>
       <c r="K22" t="n">
-        <v>-155</v>
+        <v>-211.08</v>
       </c>
       <c r="L22" t="n">
-        <v>160.23</v>
+        <v>218.21</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>289.4</v>
+        <v>313.2</v>
       </c>
       <c r="K23" t="n">
-        <v>-195.34</v>
+        <v>-211.41</v>
       </c>
       <c r="L23" t="n">
-        <v>349.15</v>
+        <v>377.87</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-45.08</v>
+        <v>-58.6</v>
       </c>
       <c r="K24" t="n">
-        <v>-310.07</v>
+        <v>-403.1</v>
       </c>
       <c r="L24" t="n">
-        <v>313.33</v>
+        <v>407.34</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>64.05</v>
+        <v>107.02</v>
       </c>
       <c r="K25" t="n">
-        <v>115.18</v>
+        <v>192.46</v>
       </c>
       <c r="L25" t="n">
-        <v>131.79</v>
+        <v>220.22</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>463.76</v>
+        <v>629.79</v>
       </c>
       <c r="K26" t="n">
-        <v>-190.52</v>
+        <v>-258.73</v>
       </c>
       <c r="L26" t="n">
-        <v>501.37</v>
+        <v>680.87</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>806.8099999999999</v>
+        <v>933.8099999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>136.46</v>
+        <v>157.94</v>
       </c>
       <c r="L27" t="n">
-        <v>818.27</v>
+        <v>947.0700000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-45.2</v>
+        <v>-49.81</v>
       </c>
       <c r="K28" t="n">
-        <v>421.05</v>
+        <v>464.02</v>
       </c>
       <c r="L28" t="n">
-        <v>423.47</v>
+        <v>466.69</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-48.35</v>
+        <v>-69.01000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>51.2</v>
+        <v>73.08</v>
       </c>
       <c r="L29" t="n">
-        <v>70.42</v>
+        <v>100.52</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>188.97</v>
+        <v>176.12</v>
       </c>
       <c r="K30" t="n">
-        <v>174.31</v>
+        <v>162.46</v>
       </c>
       <c r="L30" t="n">
-        <v>257.09</v>
+        <v>239.61</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-134.26</v>
+        <v>-117.55</v>
       </c>
       <c r="K31" t="n">
-        <v>-237.59</v>
+        <v>-208.03</v>
       </c>
       <c r="L31" t="n">
-        <v>272.9</v>
+        <v>238.95</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>-80.34999999999999</v>
+        <v>-77.98999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>-97.18000000000001</v>
+        <v>-94.33</v>
       </c>
       <c r="L32" t="n">
-        <v>126.09</v>
+        <v>122.39</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-192.66</v>
+        <v>-196.96</v>
       </c>
       <c r="K33" t="n">
-        <v>-109.61</v>
+        <v>-112.06</v>
       </c>
       <c r="L33" t="n">
-        <v>221.65</v>
+        <v>226.61</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>-299.36</v>
+        <v>-307.57</v>
       </c>
       <c r="K34" t="n">
-        <v>-37</v>
+        <v>-38.02</v>
       </c>
       <c r="L34" t="n">
-        <v>301.63</v>
+        <v>309.91</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-164.83</v>
+        <v>-204.13</v>
       </c>
       <c r="K35" t="n">
-        <v>-175.15</v>
+        <v>-216.92</v>
       </c>
       <c r="L35" t="n">
-        <v>240.52</v>
+        <v>297.87</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-133.05</v>
+        <v>-127</v>
       </c>
       <c r="K36" t="n">
-        <v>-446.86</v>
+        <v>-426.56</v>
       </c>
       <c r="L36" t="n">
-        <v>466.25</v>
+        <v>445.07</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>243.67</v>
+        <v>227.95</v>
       </c>
       <c r="K37" t="n">
-        <v>-475.18</v>
+        <v>-444.53</v>
       </c>
       <c r="L37" t="n">
-        <v>534.02</v>
+        <v>499.57</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-11.35</v>
+        <v>-21.03</v>
       </c>
       <c r="K38" t="n">
-        <v>-103.81</v>
+        <v>-192.38</v>
       </c>
       <c r="L38" t="n">
-        <v>104.42</v>
+        <v>193.52</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-185.51</v>
+        <v>-235.26</v>
       </c>
       <c r="K39" t="n">
-        <v>101.18</v>
+        <v>128.31</v>
       </c>
       <c r="L39" t="n">
-        <v>211.31</v>
+        <v>267.98</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>594.08</v>
+        <v>579.1</v>
       </c>
       <c r="K40" t="n">
-        <v>-503.83</v>
+        <v>-491.13</v>
       </c>
       <c r="L40" t="n">
-        <v>778.96</v>
+        <v>759.3200000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>820.09</v>
+        <v>824.85</v>
       </c>
       <c r="K41" t="n">
-        <v>234</v>
+        <v>235.36</v>
       </c>
       <c r="L41" t="n">
-        <v>852.8200000000001</v>
+        <v>857.77</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>363.88</v>
+        <v>434.45</v>
       </c>
       <c r="K42" t="n">
-        <v>-585.54</v>
+        <v>-699.1</v>
       </c>
       <c r="L42" t="n">
-        <v>689.4</v>
+        <v>823.1</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-62.55</v>
+        <v>-71.38</v>
       </c>
       <c r="K43" t="n">
-        <v>-590.4400000000001</v>
+        <v>-673.7</v>
       </c>
       <c r="L43" t="n">
-        <v>593.74</v>
+        <v>677.47</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>166.02</v>
+        <v>141.18</v>
       </c>
       <c r="K44" t="n">
-        <v>-113.23</v>
+        <v>-96.29000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>200.96</v>
+        <v>170.89</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>232.05</v>
+        <v>221.03</v>
       </c>
       <c r="K45" t="n">
-        <v>35.35</v>
+        <v>33.67</v>
       </c>
       <c r="L45" t="n">
-        <v>234.72</v>
+        <v>223.58</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-62.27</v>
+        <v>-75.95999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>-130.85</v>
+        <v>-159.61</v>
       </c>
       <c r="L46" t="n">
-        <v>144.92</v>
+        <v>176.76</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>19.83</v>
+        <v>25.82</v>
       </c>
       <c r="K47" t="n">
-        <v>173.23</v>
+        <v>225.53</v>
       </c>
       <c r="L47" t="n">
-        <v>174.37</v>
+        <v>227</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>80.13</v>
+        <v>107.52</v>
       </c>
       <c r="K48" t="n">
-        <v>-113.97</v>
+        <v>-152.92</v>
       </c>
       <c r="L48" t="n">
-        <v>139.32</v>
+        <v>186.94</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>-63.42</v>
+        <v>-93.27</v>
       </c>
       <c r="K49" t="n">
-        <v>2.22</v>
+        <v>3.27</v>
       </c>
       <c r="L49" t="n">
-        <v>63.46</v>
+        <v>93.33</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>137.01</v>
+        <v>164.77</v>
       </c>
       <c r="K50" t="n">
-        <v>-70.66</v>
+        <v>-84.97</v>
       </c>
       <c r="L50" t="n">
-        <v>154.16</v>
+        <v>185.39</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-60.77</v>
+        <v>-65.54000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>441.63</v>
+        <v>476.3</v>
       </c>
       <c r="L51" t="n">
-        <v>445.79</v>
+        <v>480.79</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>101.96</v>
+        <v>101.86</v>
       </c>
       <c r="K52" t="n">
-        <v>-466.16</v>
+        <v>-465.73</v>
       </c>
       <c r="L52" t="n">
-        <v>477.18</v>
+        <v>476.74</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>37.56</v>
+        <v>100.69</v>
       </c>
       <c r="K53" t="n">
-        <v>81.72</v>
+        <v>219.07</v>
       </c>
       <c r="L53" t="n">
-        <v>89.94</v>
+        <v>241.1</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>391.48</v>
+        <v>437.89</v>
       </c>
       <c r="K54" t="n">
-        <v>-243.74</v>
+        <v>-272.64</v>
       </c>
       <c r="L54" t="n">
-        <v>461.15</v>
+        <v>515.83</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-95.12</v>
+        <v>-123.4</v>
       </c>
       <c r="K55" t="n">
-        <v>431.35</v>
+        <v>559.61</v>
       </c>
       <c r="L55" t="n">
-        <v>441.72</v>
+        <v>573.05</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>340.36</v>
+        <v>354.8</v>
       </c>
       <c r="K56" t="n">
-        <v>-1439.78</v>
+        <v>-1500.85</v>
       </c>
       <c r="L56" t="n">
-        <v>1479.47</v>
+        <v>1542.22</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>44.86</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="K57" t="n">
-        <v>259.68</v>
+        <v>444.67</v>
       </c>
       <c r="L57" t="n">
-        <v>263.53</v>
+        <v>451.25</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>124.68</v>
+        <v>278.22</v>
       </c>
       <c r="K58" t="n">
-        <v>-138.74</v>
+        <v>-309.61</v>
       </c>
       <c r="L58" t="n">
-        <v>186.53</v>
+        <v>416.25</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>17.43</v>
+        <v>20.04</v>
       </c>
       <c r="K59" t="n">
-        <v>111.23</v>
+        <v>127.84</v>
       </c>
       <c r="L59" t="n">
-        <v>112.59</v>
+        <v>129.4</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>-165.14</v>
+        <v>-149.42</v>
       </c>
       <c r="K60" t="n">
-        <v>-159.49</v>
+        <v>-144.32</v>
       </c>
       <c r="L60" t="n">
-        <v>229.58</v>
+        <v>207.74</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>118.89</v>
+        <v>125.07</v>
       </c>
       <c r="K61" t="n">
-        <v>-80.20999999999999</v>
+        <v>-84.39</v>
       </c>
       <c r="L61" t="n">
-        <v>143.42</v>
+        <v>150.88</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>57.83</v>
+        <v>49.35</v>
       </c>
       <c r="K62" t="n">
-        <v>-448.43</v>
+        <v>-382.68</v>
       </c>
       <c r="L62" t="n">
-        <v>452.14</v>
+        <v>385.85</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-189.08</v>
+        <v>-177.23</v>
       </c>
       <c r="K63" t="n">
-        <v>-312.87</v>
+        <v>-293.26</v>
       </c>
       <c r="L63" t="n">
-        <v>365.57</v>
+        <v>342.65</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-115.42</v>
+        <v>-107.92</v>
       </c>
       <c r="K64" t="n">
-        <v>319.77</v>
+        <v>298.98</v>
       </c>
       <c r="L64" t="n">
-        <v>339.96</v>
+        <v>317.86</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.58</v>
+        <v>-5.92</v>
       </c>
       <c r="K65" t="n">
-        <v>201.38</v>
+        <v>260.55</v>
       </c>
       <c r="L65" t="n">
-        <v>201.43</v>
+        <v>260.61</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-4.23</v>
+        <v>-8</v>
       </c>
       <c r="K66" t="n">
-        <v>-106.28</v>
+        <v>-201.1</v>
       </c>
       <c r="L66" t="n">
-        <v>106.37</v>
+        <v>201.26</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>120.06</v>
+        <v>145.34</v>
       </c>
       <c r="K67" t="n">
-        <v>-167.16</v>
+        <v>-202.37</v>
       </c>
       <c r="L67" t="n">
-        <v>205.81</v>
+        <v>249.16</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>275.27</v>
+        <v>306.15</v>
       </c>
       <c r="K68" t="n">
-        <v>-325.55</v>
+        <v>-362.07</v>
       </c>
       <c r="L68" t="n">
-        <v>426.33</v>
+        <v>474.16</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>130.12</v>
+        <v>200.57</v>
       </c>
       <c r="K69" t="n">
-        <v>-177.95</v>
+        <v>-274.31</v>
       </c>
       <c r="L69" t="n">
-        <v>220.45</v>
+        <v>339.82</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>284.74</v>
+        <v>336.33</v>
       </c>
       <c r="K70" t="n">
-        <v>-283.59</v>
+        <v>-334.97</v>
       </c>
       <c r="L70" t="n">
-        <v>401.87</v>
+        <v>474.68</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>681.13</v>
+        <v>642.01</v>
       </c>
       <c r="K71" t="n">
-        <v>-980.1799999999999</v>
+        <v>-923.88</v>
       </c>
       <c r="L71" t="n">
-        <v>1193.6</v>
+        <v>1125.05</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-367.23</v>
+        <v>-423.69</v>
       </c>
       <c r="K72" t="n">
-        <v>-514.84</v>
+        <v>-594</v>
       </c>
       <c r="L72" t="n">
-        <v>632.39</v>
+        <v>729.62</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-190.53</v>
+        <v>-254.93</v>
       </c>
       <c r="K73" t="n">
-        <v>-359.42</v>
+        <v>-480.92</v>
       </c>
       <c r="L73" t="n">
-        <v>406.8</v>
+        <v>544.3099999999999</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>207.88</v>
+        <v>188.84</v>
       </c>
       <c r="K74" t="n">
-        <v>-26.96</v>
+        <v>-24.49</v>
       </c>
       <c r="L74" t="n">
-        <v>209.62</v>
+        <v>190.42</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-103.2</v>
+        <v>-128.22</v>
       </c>
       <c r="K75" t="n">
-        <v>-115.54</v>
+        <v>-143.55</v>
       </c>
       <c r="L75" t="n">
-        <v>154.92</v>
+        <v>192.47</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>192.09</v>
+        <v>200.07</v>
       </c>
       <c r="K76" t="n">
-        <v>103.5</v>
+        <v>107.79</v>
       </c>
       <c r="L76" t="n">
-        <v>218.2</v>
+        <v>227.26</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-129.24</v>
+        <v>-162.53</v>
       </c>
       <c r="K77" t="n">
-        <v>-77.38</v>
+        <v>-97.31</v>
       </c>
       <c r="L77" t="n">
-        <v>150.64</v>
+        <v>189.43</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-73.73</v>
+        <v>-117.6</v>
       </c>
       <c r="K78" t="n">
-        <v>112.08</v>
+        <v>178.78</v>
       </c>
       <c r="L78" t="n">
-        <v>134.15</v>
+        <v>213.99</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>-102.26</v>
+        <v>-112.93</v>
       </c>
       <c r="K79" t="n">
-        <v>-56.24</v>
+        <v>-62.11</v>
       </c>
       <c r="L79" t="n">
-        <v>116.7</v>
+        <v>128.88</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-80.20999999999999</v>
+        <v>-108.38</v>
       </c>
       <c r="K80" t="n">
-        <v>-154.14</v>
+        <v>-208.29</v>
       </c>
       <c r="L80" t="n">
-        <v>173.76</v>
+        <v>234.8</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>36.72</v>
+        <v>47.22</v>
       </c>
       <c r="K81" t="n">
-        <v>-169.36</v>
+        <v>-217.77</v>
       </c>
       <c r="L81" t="n">
-        <v>173.3</v>
+        <v>222.83</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>407.79</v>
+        <v>403.7</v>
       </c>
       <c r="K82" t="n">
-        <v>118.92</v>
+        <v>117.72</v>
       </c>
       <c r="L82" t="n">
-        <v>424.78</v>
+        <v>420.52</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>116.13</v>
+        <v>204.43</v>
       </c>
       <c r="K83" t="n">
-        <v>-127.46</v>
+        <v>-224.38</v>
       </c>
       <c r="L83" t="n">
-        <v>172.43</v>
+        <v>303.54</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-117.66</v>
+        <v>-175.71</v>
       </c>
       <c r="K84" t="n">
-        <v>-182.86</v>
+        <v>-273.07</v>
       </c>
       <c r="L84" t="n">
-        <v>217.44</v>
+        <v>324.72</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>177.64</v>
+        <v>333.51</v>
       </c>
       <c r="K85" t="n">
-        <v>-150.57</v>
+        <v>-282.69</v>
       </c>
       <c r="L85" t="n">
-        <v>232.87</v>
+        <v>437.19</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>700.96</v>
+        <v>793.04</v>
       </c>
       <c r="K86" t="n">
-        <v>91.5</v>
+        <v>103.52</v>
       </c>
       <c r="L86" t="n">
-        <v>706.9</v>
+        <v>799.77</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-255.65</v>
+        <v>-489.01</v>
       </c>
       <c r="K87" t="n">
-        <v>-165.04</v>
+        <v>-315.68</v>
       </c>
       <c r="L87" t="n">
-        <v>304.3</v>
+        <v>582.05</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>167.74</v>
+        <v>210.58</v>
       </c>
       <c r="K88" t="n">
-        <v>602.47</v>
+        <v>756.37</v>
       </c>
       <c r="L88" t="n">
-        <v>625.39</v>
+        <v>785.14</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-24.xlsx
+++ b/output/2025-05-24.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-164.56</v>
+        <v>-131.47</v>
       </c>
       <c r="K14" t="n">
-        <v>-47.64</v>
+        <v>-38.06</v>
       </c>
       <c r="L14" t="n">
-        <v>171.32</v>
+        <v>136.87</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-112.48</v>
+        <v>-94.38</v>
       </c>
       <c r="K15" t="n">
-        <v>123.44</v>
+        <v>103.58</v>
       </c>
       <c r="L15" t="n">
-        <v>167</v>
+        <v>140.13</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>17.14</v>
+        <v>12.69</v>
       </c>
       <c r="K16" t="n">
-        <v>285.94</v>
+        <v>211.62</v>
       </c>
       <c r="L16" t="n">
-        <v>286.45</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>124.76</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>203.49</v>
+        <v>148.95</v>
       </c>
       <c r="L17" t="n">
-        <v>238.69</v>
+        <v>174.71</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>97.64</v>
+        <v>84.87</v>
       </c>
       <c r="K18" t="n">
-        <v>147.15</v>
+        <v>127.91</v>
       </c>
       <c r="L18" t="n">
-        <v>176.59</v>
+        <v>153.51</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>86.06</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>89.09999999999999</v>
+        <v>73.98</v>
       </c>
       <c r="L19" t="n">
-        <v>123.88</v>
+        <v>102.86</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>66.95</v>
+        <v>42.86</v>
       </c>
       <c r="K20" t="n">
-        <v>-192.52</v>
+        <v>-123.25</v>
       </c>
       <c r="L20" t="n">
-        <v>203.83</v>
+        <v>130.49</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>409.01</v>
+        <v>267.6</v>
       </c>
       <c r="K21" t="n">
-        <v>54.75</v>
+        <v>35.82</v>
       </c>
       <c r="L21" t="n">
-        <v>412.66</v>
+        <v>269.99</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-55.32</v>
+        <v>-36.59</v>
       </c>
       <c r="K22" t="n">
-        <v>-211.08</v>
+        <v>-139.59</v>
       </c>
       <c r="L22" t="n">
-        <v>218.21</v>
+        <v>144.31</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>313.2</v>
+        <v>198.85</v>
       </c>
       <c r="K23" t="n">
-        <v>-211.41</v>
+        <v>-134.22</v>
       </c>
       <c r="L23" t="n">
-        <v>377.87</v>
+        <v>239.91</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-58.6</v>
+        <v>-32.95</v>
       </c>
       <c r="K24" t="n">
-        <v>-403.1</v>
+        <v>-226.67</v>
       </c>
       <c r="L24" t="n">
-        <v>407.34</v>
+        <v>229.05</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>107.02</v>
+        <v>63.05</v>
       </c>
       <c r="K25" t="n">
-        <v>192.46</v>
+        <v>113.39</v>
       </c>
       <c r="L25" t="n">
-        <v>220.22</v>
+        <v>129.74</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>629.79</v>
+        <v>311.42</v>
       </c>
       <c r="K26" t="n">
-        <v>-258.73</v>
+        <v>-127.94</v>
       </c>
       <c r="L26" t="n">
-        <v>680.87</v>
+        <v>336.67</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>933.8099999999999</v>
+        <v>463.29</v>
       </c>
       <c r="K27" t="n">
-        <v>157.94</v>
+        <v>78.36</v>
       </c>
       <c r="L27" t="n">
-        <v>947.0700000000001</v>
+        <v>469.87</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-49.81</v>
+        <v>-28.86</v>
       </c>
       <c r="K28" t="n">
-        <v>464.02</v>
+        <v>268.88</v>
       </c>
       <c r="L28" t="n">
-        <v>466.69</v>
+        <v>270.43</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-69.01000000000001</v>
+        <v>-58.08</v>
       </c>
       <c r="K29" t="n">
-        <v>73.08</v>
+        <v>61.51</v>
       </c>
       <c r="L29" t="n">
-        <v>100.52</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>176.12</v>
+        <v>136.62</v>
       </c>
       <c r="K30" t="n">
-        <v>162.46</v>
+        <v>126.02</v>
       </c>
       <c r="L30" t="n">
-        <v>239.61</v>
+        <v>185.87</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-117.55</v>
+        <v>-90.62</v>
       </c>
       <c r="K31" t="n">
-        <v>-208.03</v>
+        <v>-160.37</v>
       </c>
       <c r="L31" t="n">
-        <v>238.95</v>
+        <v>184.2</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>-77.98999999999999</v>
+        <v>-70.5</v>
       </c>
       <c r="K32" t="n">
-        <v>-94.33</v>
+        <v>-85.26000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>122.39</v>
+        <v>110.63</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-196.96</v>
+        <v>-146.76</v>
       </c>
       <c r="K33" t="n">
-        <v>-112.06</v>
+        <v>-83.5</v>
       </c>
       <c r="L33" t="n">
-        <v>226.61</v>
+        <v>168.85</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>-307.57</v>
+        <v>-245.94</v>
       </c>
       <c r="K34" t="n">
-        <v>-38.02</v>
+        <v>-30.4</v>
       </c>
       <c r="L34" t="n">
-        <v>309.91</v>
+        <v>247.81</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-204.13</v>
+        <v>-125.99</v>
       </c>
       <c r="K35" t="n">
-        <v>-216.92</v>
+        <v>-133.88</v>
       </c>
       <c r="L35" t="n">
-        <v>297.87</v>
+        <v>183.84</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-127</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-426.56</v>
+        <v>-287.51</v>
       </c>
       <c r="L36" t="n">
-        <v>445.07</v>
+        <v>299.98</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>227.95</v>
+        <v>153.02</v>
       </c>
       <c r="K37" t="n">
-        <v>-444.53</v>
+        <v>-298.41</v>
       </c>
       <c r="L37" t="n">
-        <v>499.57</v>
+        <v>335.35</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-21.03</v>
+        <v>-13.48</v>
       </c>
       <c r="K38" t="n">
-        <v>-192.38</v>
+        <v>-123.31</v>
       </c>
       <c r="L38" t="n">
-        <v>193.52</v>
+        <v>124.04</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-235.26</v>
+        <v>-160.5</v>
       </c>
       <c r="K39" t="n">
-        <v>128.31</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>267.98</v>
+        <v>182.82</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>579.1</v>
+        <v>355.38</v>
       </c>
       <c r="K40" t="n">
-        <v>-491.13</v>
+        <v>-301.39</v>
       </c>
       <c r="L40" t="n">
-        <v>759.3200000000001</v>
+        <v>465.97</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>824.85</v>
+        <v>472.04</v>
       </c>
       <c r="K41" t="n">
-        <v>235.36</v>
+        <v>134.69</v>
       </c>
       <c r="L41" t="n">
-        <v>857.77</v>
+        <v>490.88</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>434.45</v>
+        <v>221.51</v>
       </c>
       <c r="K42" t="n">
-        <v>-699.1</v>
+        <v>-356.44</v>
       </c>
       <c r="L42" t="n">
-        <v>823.1</v>
+        <v>419.66</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-71.38</v>
+        <v>-40.43</v>
       </c>
       <c r="K43" t="n">
-        <v>-673.7</v>
+        <v>-381.6</v>
       </c>
       <c r="L43" t="n">
-        <v>677.47</v>
+        <v>383.73</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>141.18</v>
+        <v>129.3</v>
       </c>
       <c r="K44" t="n">
-        <v>-96.29000000000001</v>
+        <v>-88.19</v>
       </c>
       <c r="L44" t="n">
-        <v>170.89</v>
+        <v>156.52</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>221.03</v>
+        <v>181.07</v>
       </c>
       <c r="K45" t="n">
-        <v>33.67</v>
+        <v>27.58</v>
       </c>
       <c r="L45" t="n">
-        <v>223.58</v>
+        <v>183.16</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-75.95999999999999</v>
+        <v>-57.68</v>
       </c>
       <c r="K46" t="n">
-        <v>-159.61</v>
+        <v>-121.21</v>
       </c>
       <c r="L46" t="n">
-        <v>176.76</v>
+        <v>134.23</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>25.82</v>
+        <v>17.56</v>
       </c>
       <c r="K47" t="n">
-        <v>225.53</v>
+        <v>153.43</v>
       </c>
       <c r="L47" t="n">
-        <v>227</v>
+        <v>154.43</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>107.52</v>
+        <v>77.5</v>
       </c>
       <c r="K48" t="n">
-        <v>-152.92</v>
+        <v>-110.22</v>
       </c>
       <c r="L48" t="n">
-        <v>186.94</v>
+        <v>134.74</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>-93.27</v>
+        <v>-82.59999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>3.27</v>
+        <v>2.9</v>
       </c>
       <c r="L49" t="n">
-        <v>93.33</v>
+        <v>82.65000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>164.77</v>
+        <v>119.94</v>
       </c>
       <c r="K50" t="n">
-        <v>-84.97</v>
+        <v>-61.85</v>
       </c>
       <c r="L50" t="n">
-        <v>185.39</v>
+        <v>134.95</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-65.54000000000001</v>
+        <v>-41.49</v>
       </c>
       <c r="K51" t="n">
-        <v>476.3</v>
+        <v>301.52</v>
       </c>
       <c r="L51" t="n">
-        <v>480.79</v>
+        <v>304.36</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>101.86</v>
+        <v>67.44</v>
       </c>
       <c r="K52" t="n">
-        <v>-465.73</v>
+        <v>-308.33</v>
       </c>
       <c r="L52" t="n">
-        <v>476.74</v>
+        <v>315.62</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>100.69</v>
+        <v>60.85</v>
       </c>
       <c r="K53" t="n">
-        <v>219.07</v>
+        <v>132.39</v>
       </c>
       <c r="L53" t="n">
-        <v>241.1</v>
+        <v>145.71</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>437.89</v>
+        <v>267.53</v>
       </c>
       <c r="K54" t="n">
-        <v>-272.64</v>
+        <v>-166.57</v>
       </c>
       <c r="L54" t="n">
-        <v>515.83</v>
+        <v>315.15</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-123.4</v>
+        <v>-70.58</v>
       </c>
       <c r="K55" t="n">
-        <v>559.61</v>
+        <v>320.06</v>
       </c>
       <c r="L55" t="n">
-        <v>573.05</v>
+        <v>327.75</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>354.8</v>
+        <v>178.7</v>
       </c>
       <c r="K56" t="n">
-        <v>-1500.85</v>
+        <v>-755.9299999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>1542.22</v>
+        <v>776.77</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>76.81999999999999</v>
+        <v>42.7</v>
       </c>
       <c r="K57" t="n">
-        <v>444.67</v>
+        <v>247.18</v>
       </c>
       <c r="L57" t="n">
-        <v>451.25</v>
+        <v>250.84</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>278.22</v>
+        <v>143.97</v>
       </c>
       <c r="K58" t="n">
-        <v>-309.61</v>
+        <v>-160.21</v>
       </c>
       <c r="L58" t="n">
-        <v>416.25</v>
+        <v>215.39</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>20.04</v>
+        <v>15.93</v>
       </c>
       <c r="K59" t="n">
-        <v>127.84</v>
+        <v>101.64</v>
       </c>
       <c r="L59" t="n">
-        <v>129.4</v>
+        <v>102.88</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>-149.42</v>
+        <v>-128.34</v>
       </c>
       <c r="K60" t="n">
-        <v>-144.32</v>
+        <v>-123.96</v>
       </c>
       <c r="L60" t="n">
-        <v>207.74</v>
+        <v>178.43</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>125.07</v>
+        <v>104.51</v>
       </c>
       <c r="K61" t="n">
-        <v>-84.39</v>
+        <v>-70.51000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>150.88</v>
+        <v>126.07</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>49.35</v>
+        <v>36.8</v>
       </c>
       <c r="K62" t="n">
-        <v>-382.68</v>
+        <v>-285.34</v>
       </c>
       <c r="L62" t="n">
-        <v>385.85</v>
+        <v>287.7</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-177.23</v>
+        <v>-133.18</v>
       </c>
       <c r="K63" t="n">
-        <v>-293.26</v>
+        <v>-220.37</v>
       </c>
       <c r="L63" t="n">
-        <v>342.65</v>
+        <v>257.48</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-107.92</v>
+        <v>-86.48</v>
       </c>
       <c r="K64" t="n">
-        <v>298.98</v>
+        <v>239.58</v>
       </c>
       <c r="L64" t="n">
-        <v>317.86</v>
+        <v>254.71</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.92</v>
+        <v>-4.34</v>
       </c>
       <c r="K65" t="n">
-        <v>260.55</v>
+        <v>190.89</v>
       </c>
       <c r="L65" t="n">
-        <v>260.61</v>
+        <v>190.94</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-8</v>
+        <v>-5.15</v>
       </c>
       <c r="K66" t="n">
-        <v>-201.1</v>
+        <v>-129.27</v>
       </c>
       <c r="L66" t="n">
-        <v>201.26</v>
+        <v>129.37</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>145.34</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>-202.37</v>
+        <v>-134.22</v>
       </c>
       <c r="L67" t="n">
-        <v>249.16</v>
+        <v>165.25</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>306.15</v>
+        <v>200.87</v>
       </c>
       <c r="K68" t="n">
-        <v>-362.07</v>
+        <v>-237.56</v>
       </c>
       <c r="L68" t="n">
-        <v>474.16</v>
+        <v>311.1</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>200.57</v>
+        <v>114.98</v>
       </c>
       <c r="K69" t="n">
-        <v>-274.31</v>
+        <v>-157.26</v>
       </c>
       <c r="L69" t="n">
-        <v>339.82</v>
+        <v>194.81</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>336.33</v>
+        <v>204.8</v>
       </c>
       <c r="K70" t="n">
-        <v>-334.97</v>
+        <v>-203.97</v>
       </c>
       <c r="L70" t="n">
-        <v>474.68</v>
+        <v>289.05</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>642.01</v>
+        <v>377.49</v>
       </c>
       <c r="K71" t="n">
-        <v>-923.88</v>
+        <v>-543.23</v>
       </c>
       <c r="L71" t="n">
-        <v>1125.05</v>
+        <v>661.51</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-423.69</v>
+        <v>-231.33</v>
       </c>
       <c r="K72" t="n">
-        <v>-594</v>
+        <v>-324.32</v>
       </c>
       <c r="L72" t="n">
-        <v>729.62</v>
+        <v>398.36</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-254.93</v>
+        <v>-139.36</v>
       </c>
       <c r="K73" t="n">
-        <v>-480.92</v>
+        <v>-262.89</v>
       </c>
       <c r="L73" t="n">
-        <v>544.3099999999999</v>
+        <v>297.55</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>188.84</v>
+        <v>168.81</v>
       </c>
       <c r="K74" t="n">
-        <v>-24.49</v>
+        <v>-21.89</v>
       </c>
       <c r="L74" t="n">
-        <v>190.42</v>
+        <v>170.22</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-128.22</v>
+        <v>-91.73999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>-143.55</v>
+        <v>-102.71</v>
       </c>
       <c r="L75" t="n">
-        <v>192.47</v>
+        <v>137.71</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>200.07</v>
+        <v>145.32</v>
       </c>
       <c r="K76" t="n">
-        <v>107.79</v>
+        <v>78.3</v>
       </c>
       <c r="L76" t="n">
-        <v>227.26</v>
+        <v>165.07</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-162.53</v>
+        <v>-119.1</v>
       </c>
       <c r="K77" t="n">
-        <v>-97.31</v>
+        <v>-71.31</v>
       </c>
       <c r="L77" t="n">
-        <v>189.43</v>
+        <v>138.81</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-117.6</v>
+        <v>-83.29000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>178.78</v>
+        <v>126.62</v>
       </c>
       <c r="L78" t="n">
-        <v>213.99</v>
+        <v>151.56</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>-112.93</v>
+        <v>-96.23</v>
       </c>
       <c r="K79" t="n">
-        <v>-62.11</v>
+        <v>-52.93</v>
       </c>
       <c r="L79" t="n">
-        <v>128.88</v>
+        <v>109.83</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-108.38</v>
+        <v>-75.08</v>
       </c>
       <c r="K80" t="n">
-        <v>-208.29</v>
+        <v>-144.3</v>
       </c>
       <c r="L80" t="n">
-        <v>234.8</v>
+        <v>162.67</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>47.22</v>
+        <v>35.31</v>
       </c>
       <c r="K81" t="n">
-        <v>-217.77</v>
+        <v>-162.83</v>
       </c>
       <c r="L81" t="n">
-        <v>222.83</v>
+        <v>166.61</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>403.7</v>
+        <v>271</v>
       </c>
       <c r="K82" t="n">
-        <v>117.72</v>
+        <v>79.03</v>
       </c>
       <c r="L82" t="n">
-        <v>420.52</v>
+        <v>282.29</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>204.43</v>
+        <v>117.19</v>
       </c>
       <c r="K83" t="n">
-        <v>-224.38</v>
+        <v>-128.63</v>
       </c>
       <c r="L83" t="n">
-        <v>303.54</v>
+        <v>174.01</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-175.71</v>
+        <v>-104.61</v>
       </c>
       <c r="K84" t="n">
-        <v>-273.07</v>
+        <v>-162.58</v>
       </c>
       <c r="L84" t="n">
-        <v>324.72</v>
+        <v>193.33</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>333.51</v>
+        <v>177.57</v>
       </c>
       <c r="K85" t="n">
-        <v>-282.69</v>
+        <v>-150.51</v>
       </c>
       <c r="L85" t="n">
-        <v>437.19</v>
+        <v>232.78</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>793.04</v>
+        <v>443.47</v>
       </c>
       <c r="K86" t="n">
-        <v>103.52</v>
+        <v>57.89</v>
       </c>
       <c r="L86" t="n">
-        <v>799.77</v>
+        <v>447.23</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-489.01</v>
+        <v>-239.41</v>
       </c>
       <c r="K87" t="n">
-        <v>-315.68</v>
+        <v>-154.55</v>
       </c>
       <c r="L87" t="n">
-        <v>582.05</v>
+        <v>284.97</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>210.58</v>
+        <v>112.26</v>
       </c>
       <c r="K88" t="n">
-        <v>756.37</v>
+        <v>403.2</v>
       </c>
       <c r="L88" t="n">
-        <v>785.14</v>
+        <v>418.54</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-24.xlsx
+++ b/output/2025-05-24.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-131.47</v>
+        <v>-122.87</v>
       </c>
       <c r="K14" t="n">
-        <v>-38.06</v>
+        <v>-35.57</v>
       </c>
       <c r="L14" t="n">
-        <v>136.87</v>
+        <v>127.91</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-94.38</v>
+        <v>-87.58</v>
       </c>
       <c r="K15" t="n">
-        <v>103.58</v>
+        <v>96.11</v>
       </c>
       <c r="L15" t="n">
-        <v>140.13</v>
+        <v>130.03</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>12.69</v>
+        <v>11.94</v>
       </c>
       <c r="K16" t="n">
-        <v>211.62</v>
+        <v>199.19</v>
       </c>
       <c r="L16" t="n">
-        <v>212</v>
+        <v>199.54</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>91.31999999999999</v>
+        <v>89.17</v>
       </c>
       <c r="K17" t="n">
-        <v>148.95</v>
+        <v>145.43</v>
       </c>
       <c r="L17" t="n">
-        <v>174.71</v>
+        <v>170.59</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>84.87</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>127.91</v>
+        <v>121.71</v>
       </c>
       <c r="L18" t="n">
-        <v>153.51</v>
+        <v>146.07</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>71.45999999999999</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>73.98</v>
+        <v>70.91</v>
       </c>
       <c r="L19" t="n">
-        <v>102.86</v>
+        <v>98.58</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>42.86</v>
+        <v>43.53</v>
       </c>
       <c r="K20" t="n">
-        <v>-123.25</v>
+        <v>-125.16</v>
       </c>
       <c r="L20" t="n">
-        <v>130.49</v>
+        <v>132.51</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>267.6</v>
+        <v>270.56</v>
       </c>
       <c r="K21" t="n">
-        <v>35.82</v>
+        <v>36.22</v>
       </c>
       <c r="L21" t="n">
-        <v>269.99</v>
+        <v>272.97</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-36.59</v>
+        <v>-36.75</v>
       </c>
       <c r="K22" t="n">
-        <v>-139.59</v>
+        <v>-140.21</v>
       </c>
       <c r="L22" t="n">
-        <v>144.31</v>
+        <v>144.95</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>198.85</v>
+        <v>202.25</v>
       </c>
       <c r="K23" t="n">
-        <v>-134.22</v>
+        <v>-136.52</v>
       </c>
       <c r="L23" t="n">
-        <v>239.91</v>
+        <v>244.01</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-32.95</v>
+        <v>-33.99</v>
       </c>
       <c r="K24" t="n">
-        <v>-226.67</v>
+        <v>-233.82</v>
       </c>
       <c r="L24" t="n">
-        <v>229.05</v>
+        <v>236.28</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>63.05</v>
+        <v>65.13</v>
       </c>
       <c r="K25" t="n">
-        <v>113.39</v>
+        <v>117.11</v>
       </c>
       <c r="L25" t="n">
-        <v>129.74</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>311.42</v>
+        <v>329.92</v>
       </c>
       <c r="K26" t="n">
-        <v>-127.94</v>
+        <v>-135.54</v>
       </c>
       <c r="L26" t="n">
-        <v>336.67</v>
+        <v>356.67</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>463.29</v>
+        <v>479.1</v>
       </c>
       <c r="K27" t="n">
-        <v>78.36</v>
+        <v>81.03</v>
       </c>
       <c r="L27" t="n">
-        <v>469.87</v>
+        <v>485.91</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-28.86</v>
+        <v>-30.02</v>
       </c>
       <c r="K28" t="n">
-        <v>268.88</v>
+        <v>279.67</v>
       </c>
       <c r="L28" t="n">
-        <v>270.43</v>
+        <v>281.28</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-58.08</v>
+        <v>-54.23</v>
       </c>
       <c r="K29" t="n">
-        <v>61.51</v>
+        <v>57.43</v>
       </c>
       <c r="L29" t="n">
-        <v>84.59999999999999</v>
+        <v>78.98999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>136.62</v>
+        <v>129.07</v>
       </c>
       <c r="K30" t="n">
-        <v>126.02</v>
+        <v>119.06</v>
       </c>
       <c r="L30" t="n">
-        <v>185.87</v>
+        <v>175.59</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-90.62</v>
+        <v>-85.64</v>
       </c>
       <c r="K31" t="n">
-        <v>-160.37</v>
+        <v>-151.55</v>
       </c>
       <c r="L31" t="n">
-        <v>184.2</v>
+        <v>174.08</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>-70.5</v>
+        <v>-67.8</v>
       </c>
       <c r="K32" t="n">
-        <v>-85.26000000000001</v>
+        <v>-82</v>
       </c>
       <c r="L32" t="n">
-        <v>110.63</v>
+        <v>106.4</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-146.76</v>
+        <v>-142.42</v>
       </c>
       <c r="K33" t="n">
-        <v>-83.5</v>
+        <v>-81.03</v>
       </c>
       <c r="L33" t="n">
-        <v>168.85</v>
+        <v>163.85</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>-245.94</v>
+        <v>-233.13</v>
       </c>
       <c r="K34" t="n">
-        <v>-30.4</v>
+        <v>-28.82</v>
       </c>
       <c r="L34" t="n">
-        <v>247.81</v>
+        <v>234.9</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-125.99</v>
+        <v>-126.58</v>
       </c>
       <c r="K35" t="n">
-        <v>-133.88</v>
+        <v>-134.51</v>
       </c>
       <c r="L35" t="n">
-        <v>183.84</v>
+        <v>184.7</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-85.59999999999999</v>
+        <v>-85.47</v>
       </c>
       <c r="K36" t="n">
-        <v>-287.51</v>
+        <v>-287.07</v>
       </c>
       <c r="L36" t="n">
-        <v>299.98</v>
+        <v>299.52</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>153.02</v>
+        <v>152.69</v>
       </c>
       <c r="K37" t="n">
-        <v>-298.41</v>
+        <v>-297.77</v>
       </c>
       <c r="L37" t="n">
-        <v>335.35</v>
+        <v>334.64</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-13.48</v>
+        <v>-13.54</v>
       </c>
       <c r="K38" t="n">
-        <v>-123.31</v>
+        <v>-123.83</v>
       </c>
       <c r="L38" t="n">
-        <v>124.04</v>
+        <v>124.57</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-160.5</v>
+        <v>-162.01</v>
       </c>
       <c r="K39" t="n">
-        <v>87.54000000000001</v>
+        <v>88.36</v>
       </c>
       <c r="L39" t="n">
-        <v>182.82</v>
+        <v>184.53</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>355.38</v>
+        <v>360.66</v>
       </c>
       <c r="K40" t="n">
-        <v>-301.39</v>
+        <v>-305.87</v>
       </c>
       <c r="L40" t="n">
-        <v>465.97</v>
+        <v>472.9</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>472.04</v>
+        <v>487.57</v>
       </c>
       <c r="K41" t="n">
-        <v>134.69</v>
+        <v>139.12</v>
       </c>
       <c r="L41" t="n">
-        <v>490.88</v>
+        <v>507.03</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>221.51</v>
+        <v>231.96</v>
       </c>
       <c r="K42" t="n">
-        <v>-356.44</v>
+        <v>-373.27</v>
       </c>
       <c r="L42" t="n">
-        <v>419.66</v>
+        <v>439.47</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-40.43</v>
+        <v>-42.01</v>
       </c>
       <c r="K43" t="n">
-        <v>-381.6</v>
+        <v>-396.49</v>
       </c>
       <c r="L43" t="n">
-        <v>383.73</v>
+        <v>398.71</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>129.3</v>
+        <v>119.69</v>
       </c>
       <c r="K44" t="n">
-        <v>-88.19</v>
+        <v>-81.63</v>
       </c>
       <c r="L44" t="n">
-        <v>156.52</v>
+        <v>144.87</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>181.07</v>
+        <v>170.69</v>
       </c>
       <c r="K45" t="n">
-        <v>27.58</v>
+        <v>26</v>
       </c>
       <c r="L45" t="n">
-        <v>183.16</v>
+        <v>172.66</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-57.68</v>
+        <v>-54.61</v>
       </c>
       <c r="K46" t="n">
-        <v>-121.21</v>
+        <v>-114.74</v>
       </c>
       <c r="L46" t="n">
-        <v>134.23</v>
+        <v>127.08</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>17.56</v>
+        <v>17.11</v>
       </c>
       <c r="K47" t="n">
-        <v>153.43</v>
+        <v>149.42</v>
       </c>
       <c r="L47" t="n">
-        <v>154.43</v>
+        <v>150.4</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>77.5</v>
+        <v>76.27</v>
       </c>
       <c r="K48" t="n">
-        <v>-110.22</v>
+        <v>-108.48</v>
       </c>
       <c r="L48" t="n">
-        <v>134.74</v>
+        <v>132.61</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>-82.59999999999999</v>
+        <v>-78.55</v>
       </c>
       <c r="K49" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="L49" t="n">
-        <v>82.65000000000001</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>119.94</v>
+        <v>120.05</v>
       </c>
       <c r="K50" t="n">
-        <v>-61.85</v>
+        <v>-61.91</v>
       </c>
       <c r="L50" t="n">
-        <v>134.95</v>
+        <v>135.07</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-41.49</v>
+        <v>-41.94</v>
       </c>
       <c r="K51" t="n">
-        <v>301.52</v>
+        <v>304.82</v>
       </c>
       <c r="L51" t="n">
-        <v>304.36</v>
+        <v>307.69</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>67.44</v>
+        <v>67.98</v>
       </c>
       <c r="K52" t="n">
-        <v>-308.33</v>
+        <v>-310.79</v>
       </c>
       <c r="L52" t="n">
-        <v>315.62</v>
+        <v>318.14</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>60.85</v>
+        <v>62.09</v>
       </c>
       <c r="K53" t="n">
-        <v>132.39</v>
+        <v>135.07</v>
       </c>
       <c r="L53" t="n">
-        <v>145.71</v>
+        <v>148.66</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>267.53</v>
+        <v>273.24</v>
       </c>
       <c r="K54" t="n">
-        <v>-166.57</v>
+        <v>-170.12</v>
       </c>
       <c r="L54" t="n">
-        <v>315.15</v>
+        <v>321.87</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-70.58</v>
+        <v>-72.03</v>
       </c>
       <c r="K55" t="n">
-        <v>320.06</v>
+        <v>326.63</v>
       </c>
       <c r="L55" t="n">
-        <v>327.75</v>
+        <v>334.48</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>178.7</v>
+        <v>187.7</v>
       </c>
       <c r="K56" t="n">
-        <v>-755.9299999999999</v>
+        <v>-793.99</v>
       </c>
       <c r="L56" t="n">
-        <v>776.77</v>
+        <v>815.87</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>42.7</v>
+        <v>44.95</v>
       </c>
       <c r="K57" t="n">
-        <v>247.18</v>
+        <v>260.2</v>
       </c>
       <c r="L57" t="n">
-        <v>250.84</v>
+        <v>264.05</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>143.97</v>
+        <v>152.87</v>
       </c>
       <c r="K58" t="n">
-        <v>-160.21</v>
+        <v>-170.11</v>
       </c>
       <c r="L58" t="n">
-        <v>215.39</v>
+        <v>228.71</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>15.93</v>
+        <v>14.92</v>
       </c>
       <c r="K59" t="n">
-        <v>101.64</v>
+        <v>95.22</v>
       </c>
       <c r="L59" t="n">
-        <v>102.88</v>
+        <v>96.38</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>-128.34</v>
+        <v>-119.48</v>
       </c>
       <c r="K60" t="n">
-        <v>-123.96</v>
+        <v>-115.39</v>
       </c>
       <c r="L60" t="n">
-        <v>178.43</v>
+        <v>166.1</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>104.51</v>
+        <v>97.22</v>
       </c>
       <c r="K61" t="n">
-        <v>-70.51000000000001</v>
+        <v>-65.59</v>
       </c>
       <c r="L61" t="n">
-        <v>126.07</v>
+        <v>117.28</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>36.8</v>
+        <v>35.7</v>
       </c>
       <c r="K62" t="n">
-        <v>-285.34</v>
+        <v>-276.8</v>
       </c>
       <c r="L62" t="n">
-        <v>287.7</v>
+        <v>279.09</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-133.18</v>
+        <v>-129.84</v>
       </c>
       <c r="K63" t="n">
-        <v>-220.37</v>
+        <v>-214.84</v>
       </c>
       <c r="L63" t="n">
-        <v>257.48</v>
+        <v>251.03</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-86.48</v>
+        <v>-81.25</v>
       </c>
       <c r="K64" t="n">
-        <v>239.58</v>
+        <v>225.09</v>
       </c>
       <c r="L64" t="n">
-        <v>254.71</v>
+        <v>239.31</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.34</v>
+        <v>-4.28</v>
       </c>
       <c r="K65" t="n">
-        <v>190.89</v>
+        <v>188.48</v>
       </c>
       <c r="L65" t="n">
-        <v>190.94</v>
+        <v>188.53</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.15</v>
+        <v>-5.19</v>
       </c>
       <c r="K66" t="n">
-        <v>-129.27</v>
+        <v>-130.41</v>
       </c>
       <c r="L66" t="n">
-        <v>129.37</v>
+        <v>130.52</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>96.40000000000001</v>
+        <v>96.48</v>
       </c>
       <c r="K67" t="n">
-        <v>-134.22</v>
+        <v>-134.34</v>
       </c>
       <c r="L67" t="n">
-        <v>165.25</v>
+        <v>165.4</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>200.87</v>
+        <v>200.89</v>
       </c>
       <c r="K68" t="n">
-        <v>-237.56</v>
+        <v>-237.58</v>
       </c>
       <c r="L68" t="n">
-        <v>311.1</v>
+        <v>311.12</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>114.98</v>
+        <v>118.06</v>
       </c>
       <c r="K69" t="n">
-        <v>-157.26</v>
+        <v>-161.47</v>
       </c>
       <c r="L69" t="n">
-        <v>194.81</v>
+        <v>200.03</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>204.8</v>
+        <v>208.09</v>
       </c>
       <c r="K70" t="n">
-        <v>-203.97</v>
+        <v>-207.25</v>
       </c>
       <c r="L70" t="n">
-        <v>289.05</v>
+        <v>293.7</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>377.49</v>
+        <v>385.35</v>
       </c>
       <c r="K71" t="n">
-        <v>-543.23</v>
+        <v>-554.54</v>
       </c>
       <c r="L71" t="n">
-        <v>661.51</v>
+        <v>675.28</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-231.33</v>
+        <v>-239.97</v>
       </c>
       <c r="K72" t="n">
-        <v>-324.32</v>
+        <v>-336.43</v>
       </c>
       <c r="L72" t="n">
-        <v>398.36</v>
+        <v>413.25</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-139.36</v>
+        <v>-144.35</v>
       </c>
       <c r="K73" t="n">
-        <v>-262.89</v>
+        <v>-272.3</v>
       </c>
       <c r="L73" t="n">
-        <v>297.55</v>
+        <v>308.2</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>168.81</v>
+        <v>155.95</v>
       </c>
       <c r="K74" t="n">
-        <v>-21.89</v>
+        <v>-20.22</v>
       </c>
       <c r="L74" t="n">
-        <v>170.22</v>
+        <v>157.26</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-91.73999999999999</v>
+        <v>-88.13</v>
       </c>
       <c r="K75" t="n">
-        <v>-102.71</v>
+        <v>-98.66</v>
       </c>
       <c r="L75" t="n">
-        <v>137.71</v>
+        <v>132.29</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>145.32</v>
+        <v>138.05</v>
       </c>
       <c r="K76" t="n">
-        <v>78.3</v>
+        <v>74.38</v>
       </c>
       <c r="L76" t="n">
-        <v>165.07</v>
+        <v>156.81</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-119.1</v>
+        <v>-114.39</v>
       </c>
       <c r="K77" t="n">
-        <v>-71.31</v>
+        <v>-68.48999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>138.81</v>
+        <v>133.33</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-83.29000000000001</v>
+        <v>-80.88</v>
       </c>
       <c r="K78" t="n">
-        <v>126.62</v>
+        <v>122.96</v>
       </c>
       <c r="L78" t="n">
-        <v>151.56</v>
+        <v>147.18</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>-96.23</v>
+        <v>-92.48</v>
       </c>
       <c r="K79" t="n">
-        <v>-52.93</v>
+        <v>-50.86</v>
       </c>
       <c r="L79" t="n">
-        <v>109.83</v>
+        <v>105.55</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-75.08</v>
+        <v>-74.34</v>
       </c>
       <c r="K80" t="n">
-        <v>-144.3</v>
+        <v>-142.88</v>
       </c>
       <c r="L80" t="n">
-        <v>162.67</v>
+        <v>161.06</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>35.31</v>
+        <v>34.6</v>
       </c>
       <c r="K81" t="n">
-        <v>-162.83</v>
+        <v>-159.55</v>
       </c>
       <c r="L81" t="n">
-        <v>166.61</v>
+        <v>163.26</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>271</v>
+        <v>269.67</v>
       </c>
       <c r="K82" t="n">
-        <v>79.03</v>
+        <v>78.64</v>
       </c>
       <c r="L82" t="n">
-        <v>282.29</v>
+        <v>280.9</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>117.19</v>
+        <v>121.68</v>
       </c>
       <c r="K83" t="n">
-        <v>-128.63</v>
+        <v>-133.55</v>
       </c>
       <c r="L83" t="n">
-        <v>174.01</v>
+        <v>180.67</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-104.61</v>
+        <v>-107.44</v>
       </c>
       <c r="K84" t="n">
-        <v>-162.58</v>
+        <v>-166.97</v>
       </c>
       <c r="L84" t="n">
-        <v>193.33</v>
+        <v>198.55</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>177.57</v>
+        <v>185.83</v>
       </c>
       <c r="K85" t="n">
-        <v>-150.51</v>
+        <v>-157.52</v>
       </c>
       <c r="L85" t="n">
-        <v>232.78</v>
+        <v>243.61</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>443.47</v>
+        <v>465.51</v>
       </c>
       <c r="K86" t="n">
-        <v>57.89</v>
+        <v>60.76</v>
       </c>
       <c r="L86" t="n">
-        <v>447.23</v>
+        <v>469.46</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-239.41</v>
+        <v>-253.37</v>
       </c>
       <c r="K87" t="n">
-        <v>-154.55</v>
+        <v>-163.56</v>
       </c>
       <c r="L87" t="n">
-        <v>284.97</v>
+        <v>301.57</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>112.26</v>
+        <v>117.42</v>
       </c>
       <c r="K88" t="n">
-        <v>403.2</v>
+        <v>421.73</v>
       </c>
       <c r="L88" t="n">
-        <v>418.54</v>
+        <v>437.77</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-24.xlsx
+++ b/output/2025-05-24.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-122.87</v>
+        <v>-70.38</v>
       </c>
       <c r="K14" t="n">
-        <v>-35.57</v>
+        <v>-20.37</v>
       </c>
       <c r="L14" t="n">
-        <v>127.91</v>
+        <v>73.27</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-87.58</v>
+        <v>-43.2</v>
       </c>
       <c r="K15" t="n">
-        <v>96.11</v>
+        <v>47.41</v>
       </c>
       <c r="L15" t="n">
-        <v>130.03</v>
+        <v>64.13</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>11.94</v>
+        <v>6.24</v>
       </c>
       <c r="K16" t="n">
-        <v>199.19</v>
+        <v>104.04</v>
       </c>
       <c r="L16" t="n">
-        <v>199.54</v>
+        <v>104.23</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>89.17</v>
+        <v>42.44</v>
       </c>
       <c r="K17" t="n">
-        <v>145.43</v>
+        <v>69.22</v>
       </c>
       <c r="L17" t="n">
-        <v>170.59</v>
+        <v>81.19</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>80.76000000000001</v>
+        <v>39.77</v>
       </c>
       <c r="K18" t="n">
-        <v>121.71</v>
+        <v>59.93</v>
       </c>
       <c r="L18" t="n">
-        <v>146.07</v>
+        <v>71.93000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>68.48999999999999</v>
+        <v>37.81</v>
       </c>
       <c r="K19" t="n">
-        <v>70.91</v>
+        <v>39.15</v>
       </c>
       <c r="L19" t="n">
-        <v>98.58</v>
+        <v>54.43</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>43.53</v>
+        <v>22.66</v>
       </c>
       <c r="K20" t="n">
-        <v>-125.16</v>
+        <v>-65.17</v>
       </c>
       <c r="L20" t="n">
-        <v>132.51</v>
+        <v>68.98999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>270.56</v>
+        <v>138.13</v>
       </c>
       <c r="K21" t="n">
-        <v>36.22</v>
+        <v>18.49</v>
       </c>
       <c r="L21" t="n">
-        <v>272.97</v>
+        <v>139.37</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-36.75</v>
+        <v>-19.06</v>
       </c>
       <c r="K22" t="n">
-        <v>-140.21</v>
+        <v>-72.72</v>
       </c>
       <c r="L22" t="n">
-        <v>144.95</v>
+        <v>75.17</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>202.25</v>
+        <v>118.78</v>
       </c>
       <c r="K23" t="n">
-        <v>-136.52</v>
+        <v>-80.18000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>244.01</v>
+        <v>143.31</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-33.99</v>
+        <v>-19.3</v>
       </c>
       <c r="K24" t="n">
-        <v>-233.82</v>
+        <v>-132.78</v>
       </c>
       <c r="L24" t="n">
-        <v>236.28</v>
+        <v>134.18</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>65.13</v>
+        <v>40.77</v>
       </c>
       <c r="K25" t="n">
-        <v>117.11</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>134</v>
+        <v>83.89</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>329.92</v>
+        <v>184.59</v>
       </c>
       <c r="K26" t="n">
-        <v>-135.54</v>
+        <v>-75.83</v>
       </c>
       <c r="L26" t="n">
-        <v>356.67</v>
+        <v>199.56</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>479.1</v>
+        <v>269.28</v>
       </c>
       <c r="K27" t="n">
-        <v>81.03</v>
+        <v>45.54</v>
       </c>
       <c r="L27" t="n">
-        <v>485.91</v>
+        <v>273.11</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-30.02</v>
+        <v>-19.45</v>
       </c>
       <c r="K28" t="n">
-        <v>279.67</v>
+        <v>181.22</v>
       </c>
       <c r="L28" t="n">
-        <v>281.28</v>
+        <v>182.26</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-54.23</v>
+        <v>-27.07</v>
       </c>
       <c r="K29" t="n">
-        <v>57.43</v>
+        <v>28.67</v>
       </c>
       <c r="L29" t="n">
-        <v>78.98999999999999</v>
+        <v>39.43</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>129.07</v>
+        <v>62.77</v>
       </c>
       <c r="K30" t="n">
-        <v>119.06</v>
+        <v>57.9</v>
       </c>
       <c r="L30" t="n">
-        <v>175.59</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-85.64</v>
+        <v>-46.2</v>
       </c>
       <c r="K31" t="n">
-        <v>-151.55</v>
+        <v>-81.75</v>
       </c>
       <c r="L31" t="n">
-        <v>174.08</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>-67.8</v>
+        <v>-37.31</v>
       </c>
       <c r="K32" t="n">
-        <v>-82</v>
+        <v>-45.12</v>
       </c>
       <c r="L32" t="n">
-        <v>106.4</v>
+        <v>58.55</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-142.42</v>
+        <v>-71.69</v>
       </c>
       <c r="K33" t="n">
-        <v>-81.03</v>
+        <v>-40.79</v>
       </c>
       <c r="L33" t="n">
-        <v>163.85</v>
+        <v>82.48</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>-233.13</v>
+        <v>-97.01000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>-28.82</v>
+        <v>-11.99</v>
       </c>
       <c r="L34" t="n">
-        <v>234.9</v>
+        <v>97.75</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-126.58</v>
+        <v>-65.18000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>-134.51</v>
+        <v>-69.26000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>184.7</v>
+        <v>95.11</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-85.47</v>
+        <v>-43.31</v>
       </c>
       <c r="K36" t="n">
-        <v>-287.07</v>
+        <v>-145.47</v>
       </c>
       <c r="L36" t="n">
-        <v>299.52</v>
+        <v>151.78</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>152.69</v>
+        <v>77</v>
       </c>
       <c r="K37" t="n">
-        <v>-297.77</v>
+        <v>-150.17</v>
       </c>
       <c r="L37" t="n">
-        <v>334.64</v>
+        <v>168.76</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-13.54</v>
+        <v>-8.1</v>
       </c>
       <c r="K38" t="n">
-        <v>-123.83</v>
+        <v>-74.09</v>
       </c>
       <c r="L38" t="n">
-        <v>124.57</v>
+        <v>74.53</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-162.01</v>
+        <v>-91.37</v>
       </c>
       <c r="K39" t="n">
-        <v>88.36</v>
+        <v>49.83</v>
       </c>
       <c r="L39" t="n">
-        <v>184.53</v>
+        <v>104.08</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>360.66</v>
+        <v>188.62</v>
       </c>
       <c r="K40" t="n">
-        <v>-305.87</v>
+        <v>-159.96</v>
       </c>
       <c r="L40" t="n">
-        <v>472.9</v>
+        <v>247.32</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>487.57</v>
+        <v>274.84</v>
       </c>
       <c r="K41" t="n">
-        <v>139.12</v>
+        <v>78.42</v>
       </c>
       <c r="L41" t="n">
-        <v>507.03</v>
+        <v>285.81</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>231.96</v>
+        <v>129.57</v>
       </c>
       <c r="K42" t="n">
-        <v>-373.27</v>
+        <v>-208.5</v>
       </c>
       <c r="L42" t="n">
-        <v>439.47</v>
+        <v>245.48</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-42.01</v>
+        <v>-23.35</v>
       </c>
       <c r="K43" t="n">
-        <v>-396.49</v>
+        <v>-220.38</v>
       </c>
       <c r="L43" t="n">
-        <v>398.71</v>
+        <v>221.62</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>119.69</v>
+        <v>59.32</v>
       </c>
       <c r="K44" t="n">
-        <v>-81.63</v>
+        <v>-40.46</v>
       </c>
       <c r="L44" t="n">
-        <v>144.87</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>170.69</v>
+        <v>76.31</v>
       </c>
       <c r="K45" t="n">
-        <v>26</v>
+        <v>11.63</v>
       </c>
       <c r="L45" t="n">
-        <v>172.66</v>
+        <v>77.19</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-54.61</v>
+        <v>-24.32</v>
       </c>
       <c r="K46" t="n">
-        <v>-114.74</v>
+        <v>-51.09</v>
       </c>
       <c r="L46" t="n">
-        <v>127.08</v>
+        <v>56.59</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>17.11</v>
+        <v>7.94</v>
       </c>
       <c r="K47" t="n">
-        <v>149.42</v>
+        <v>69.37</v>
       </c>
       <c r="L47" t="n">
-        <v>150.4</v>
+        <v>69.83</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>76.27</v>
+        <v>38.47</v>
       </c>
       <c r="K48" t="n">
-        <v>-108.48</v>
+        <v>-54.72</v>
       </c>
       <c r="L48" t="n">
-        <v>132.61</v>
+        <v>66.89</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>-78.55</v>
+        <v>-40.9</v>
       </c>
       <c r="K49" t="n">
-        <v>2.75</v>
+        <v>1.43</v>
       </c>
       <c r="L49" t="n">
-        <v>78.59999999999999</v>
+        <v>40.93</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>120.05</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>-61.91</v>
+        <v>-33.95</v>
       </c>
       <c r="L50" t="n">
-        <v>135.07</v>
+        <v>74.06</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-41.94</v>
+        <v>-20.58</v>
       </c>
       <c r="K51" t="n">
-        <v>304.82</v>
+        <v>149.59</v>
       </c>
       <c r="L51" t="n">
-        <v>307.69</v>
+        <v>150.99</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>67.98</v>
+        <v>33.71</v>
       </c>
       <c r="K52" t="n">
-        <v>-310.79</v>
+        <v>-154.14</v>
       </c>
       <c r="L52" t="n">
-        <v>318.14</v>
+        <v>157.79</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>62.09</v>
+        <v>16.12</v>
       </c>
       <c r="K53" t="n">
-        <v>135.07</v>
+        <v>35.07</v>
       </c>
       <c r="L53" t="n">
-        <v>148.66</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>273.24</v>
+        <v>140.33</v>
       </c>
       <c r="K54" t="n">
-        <v>-170.12</v>
+        <v>-87.37</v>
       </c>
       <c r="L54" t="n">
-        <v>321.87</v>
+        <v>165.31</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-72.03</v>
+        <v>-32.76</v>
       </c>
       <c r="K55" t="n">
-        <v>326.63</v>
+        <v>148.58</v>
       </c>
       <c r="L55" t="n">
-        <v>334.48</v>
+        <v>152.15</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>187.7</v>
+        <v>103.09</v>
       </c>
       <c r="K56" t="n">
-        <v>-793.99</v>
+        <v>-436.1</v>
       </c>
       <c r="L56" t="n">
-        <v>815.87</v>
+        <v>448.12</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>44.95</v>
+        <v>24.34</v>
       </c>
       <c r="K57" t="n">
-        <v>260.2</v>
+        <v>140.89</v>
       </c>
       <c r="L57" t="n">
-        <v>264.05</v>
+        <v>142.98</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>152.87</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>-170.11</v>
+        <v>-92.54000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>228.71</v>
+        <v>124.41</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>14.92</v>
+        <v>7.96</v>
       </c>
       <c r="K59" t="n">
-        <v>95.22</v>
+        <v>50.8</v>
       </c>
       <c r="L59" t="n">
-        <v>96.38</v>
+        <v>51.42</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>-119.48</v>
+        <v>-54.75</v>
       </c>
       <c r="K60" t="n">
-        <v>-115.39</v>
+        <v>-52.87</v>
       </c>
       <c r="L60" t="n">
-        <v>166.1</v>
+        <v>76.11</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>97.22</v>
+        <v>47.17</v>
       </c>
       <c r="K61" t="n">
-        <v>-65.59</v>
+        <v>-31.83</v>
       </c>
       <c r="L61" t="n">
-        <v>117.28</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>35.7</v>
+        <v>18.01</v>
       </c>
       <c r="K62" t="n">
-        <v>-276.8</v>
+        <v>-139.62</v>
       </c>
       <c r="L62" t="n">
-        <v>279.09</v>
+        <v>140.77</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-129.84</v>
+        <v>-59.77</v>
       </c>
       <c r="K63" t="n">
-        <v>-214.84</v>
+        <v>-98.90000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>251.03</v>
+        <v>115.56</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-81.25</v>
+        <v>-35.32</v>
       </c>
       <c r="K64" t="n">
-        <v>225.09</v>
+        <v>97.86</v>
       </c>
       <c r="L64" t="n">
-        <v>239.31</v>
+        <v>104.04</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.28</v>
+        <v>-2.06</v>
       </c>
       <c r="K65" t="n">
-        <v>188.48</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>188.53</v>
+        <v>90.78</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.19</v>
+        <v>-2.6</v>
       </c>
       <c r="K66" t="n">
-        <v>-130.41</v>
+        <v>-65.20999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>130.52</v>
+        <v>65.26000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>96.48</v>
+        <v>50.43</v>
       </c>
       <c r="K67" t="n">
-        <v>-134.34</v>
+        <v>-70.22</v>
       </c>
       <c r="L67" t="n">
-        <v>165.4</v>
+        <v>86.45999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>200.89</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>-237.58</v>
+        <v>-114.4</v>
       </c>
       <c r="L68" t="n">
-        <v>311.12</v>
+        <v>149.82</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>118.06</v>
+        <v>63.44</v>
       </c>
       <c r="K69" t="n">
-        <v>-161.47</v>
+        <v>-86.76000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>200.03</v>
+        <v>107.48</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>208.09</v>
+        <v>105.41</v>
       </c>
       <c r="K70" t="n">
-        <v>-207.25</v>
+        <v>-104.99</v>
       </c>
       <c r="L70" t="n">
-        <v>293.7</v>
+        <v>148.77</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>385.35</v>
+        <v>212.95</v>
       </c>
       <c r="K71" t="n">
-        <v>-554.54</v>
+        <v>-306.44</v>
       </c>
       <c r="L71" t="n">
-        <v>675.28</v>
+        <v>373.17</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-239.97</v>
+        <v>-133.75</v>
       </c>
       <c r="K72" t="n">
-        <v>-336.43</v>
+        <v>-187.51</v>
       </c>
       <c r="L72" t="n">
-        <v>413.25</v>
+        <v>230.32</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-144.35</v>
+        <v>-80.58</v>
       </c>
       <c r="K73" t="n">
-        <v>-272.3</v>
+        <v>-152.02</v>
       </c>
       <c r="L73" t="n">
-        <v>308.2</v>
+        <v>172.05</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>155.95</v>
+        <v>70</v>
       </c>
       <c r="K74" t="n">
-        <v>-20.22</v>
+        <v>-9.08</v>
       </c>
       <c r="L74" t="n">
-        <v>157.26</v>
+        <v>70.59</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-88.13</v>
+        <v>-40.3</v>
       </c>
       <c r="K75" t="n">
-        <v>-98.66</v>
+        <v>-45.11</v>
       </c>
       <c r="L75" t="n">
-        <v>132.29</v>
+        <v>60.49</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>138.05</v>
+        <v>67.14</v>
       </c>
       <c r="K76" t="n">
-        <v>74.38</v>
+        <v>36.17</v>
       </c>
       <c r="L76" t="n">
-        <v>156.81</v>
+        <v>76.26000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-114.39</v>
+        <v>-54.64</v>
       </c>
       <c r="K77" t="n">
-        <v>-68.48999999999999</v>
+        <v>-32.72</v>
       </c>
       <c r="L77" t="n">
-        <v>133.33</v>
+        <v>63.69</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-80.88</v>
+        <v>-33.77</v>
       </c>
       <c r="K78" t="n">
-        <v>122.96</v>
+        <v>51.34</v>
       </c>
       <c r="L78" t="n">
-        <v>147.18</v>
+        <v>61.45</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>-92.48</v>
+        <v>-49.03</v>
       </c>
       <c r="K79" t="n">
-        <v>-50.86</v>
+        <v>-26.96</v>
       </c>
       <c r="L79" t="n">
-        <v>105.55</v>
+        <v>55.95</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-74.34</v>
+        <v>-37.17</v>
       </c>
       <c r="K80" t="n">
-        <v>-142.88</v>
+        <v>-71.44</v>
       </c>
       <c r="L80" t="n">
-        <v>161.06</v>
+        <v>80.53</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>34.6</v>
+        <v>17.09</v>
       </c>
       <c r="K81" t="n">
-        <v>-159.55</v>
+        <v>-78.81</v>
       </c>
       <c r="L81" t="n">
-        <v>163.26</v>
+        <v>80.64</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>269.67</v>
+        <v>136</v>
       </c>
       <c r="K82" t="n">
-        <v>78.64</v>
+        <v>39.66</v>
       </c>
       <c r="L82" t="n">
-        <v>280.9</v>
+        <v>141.66</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>121.68</v>
+        <v>65.38</v>
       </c>
       <c r="K83" t="n">
-        <v>-133.55</v>
+        <v>-71.76000000000001</v>
       </c>
       <c r="L83" t="n">
-        <v>180.67</v>
+        <v>97.08</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-107.44</v>
+        <v>-58.1</v>
       </c>
       <c r="K84" t="n">
-        <v>-166.97</v>
+        <v>-90.29000000000001</v>
       </c>
       <c r="L84" t="n">
-        <v>198.55</v>
+        <v>107.37</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>185.83</v>
+        <v>83.16</v>
       </c>
       <c r="K85" t="n">
-        <v>-157.52</v>
+        <v>-70.48999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>243.61</v>
+        <v>109.02</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>465.51</v>
+        <v>254.18</v>
       </c>
       <c r="K86" t="n">
-        <v>60.76</v>
+        <v>33.18</v>
       </c>
       <c r="L86" t="n">
-        <v>469.46</v>
+        <v>256.34</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-253.37</v>
+        <v>-134.71</v>
       </c>
       <c r="K87" t="n">
-        <v>-163.56</v>
+        <v>-86.95999999999999</v>
       </c>
       <c r="L87" t="n">
-        <v>301.57</v>
+        <v>160.34</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>117.42</v>
+        <v>63.29</v>
       </c>
       <c r="K88" t="n">
-        <v>421.73</v>
+        <v>227.34</v>
       </c>
       <c r="L88" t="n">
-        <v>437.77</v>
+        <v>235.99</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-24.xlsx
+++ b/output/2025-05-24.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-70.38</v>
+        <v>-68.67</v>
       </c>
       <c r="K14" t="n">
-        <v>-20.37</v>
+        <v>-19.88</v>
       </c>
       <c r="L14" t="n">
-        <v>73.27</v>
+        <v>71.48</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-43.2</v>
+        <v>-42.44</v>
       </c>
       <c r="K15" t="n">
-        <v>47.41</v>
+        <v>46.57</v>
       </c>
       <c r="L15" t="n">
-        <v>64.13</v>
+        <v>63.01</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>6.24</v>
+        <v>5.92</v>
       </c>
       <c r="K16" t="n">
-        <v>104.04</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>104.23</v>
+        <v>98.94</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>42.44</v>
+        <v>41.42</v>
       </c>
       <c r="K17" t="n">
-        <v>69.22</v>
+        <v>67.55</v>
       </c>
       <c r="L17" t="n">
-        <v>81.19</v>
+        <v>79.23999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>39.77</v>
+        <v>39.09</v>
       </c>
       <c r="K18" t="n">
-        <v>59.93</v>
+        <v>58.91</v>
       </c>
       <c r="L18" t="n">
-        <v>71.93000000000001</v>
+        <v>70.69</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>37.81</v>
+        <v>38.99</v>
       </c>
       <c r="K19" t="n">
-        <v>39.15</v>
+        <v>40.37</v>
       </c>
       <c r="L19" t="n">
-        <v>54.43</v>
+        <v>56.12</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>22.66</v>
+        <v>24.03</v>
       </c>
       <c r="K20" t="n">
-        <v>-65.17</v>
+        <v>-69.09</v>
       </c>
       <c r="L20" t="n">
-        <v>68.98999999999999</v>
+        <v>73.15000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>138.13</v>
+        <v>133.59</v>
       </c>
       <c r="K21" t="n">
-        <v>18.49</v>
+        <v>17.88</v>
       </c>
       <c r="L21" t="n">
-        <v>139.37</v>
+        <v>134.78</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-19.06</v>
+        <v>-19.84</v>
       </c>
       <c r="K22" t="n">
-        <v>-72.72</v>
+        <v>-75.70999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>75.17</v>
+        <v>78.27</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>118.78</v>
+        <v>117.89</v>
       </c>
       <c r="K23" t="n">
-        <v>-80.18000000000001</v>
+        <v>-79.56999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>143.31</v>
+        <v>142.23</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-19.3</v>
+        <v>-19.53</v>
       </c>
       <c r="K24" t="n">
-        <v>-132.78</v>
+        <v>-134.31</v>
       </c>
       <c r="L24" t="n">
-        <v>134.18</v>
+        <v>135.72</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>40.77</v>
+        <v>43.71</v>
       </c>
       <c r="K25" t="n">
-        <v>73.31999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>83.89</v>
+        <v>89.94</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>184.59</v>
+        <v>187.58</v>
       </c>
       <c r="K26" t="n">
-        <v>-75.83</v>
+        <v>-77.06</v>
       </c>
       <c r="L26" t="n">
-        <v>199.56</v>
+        <v>202.79</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>269.28</v>
+        <v>262.35</v>
       </c>
       <c r="K27" t="n">
-        <v>45.54</v>
+        <v>44.37</v>
       </c>
       <c r="L27" t="n">
-        <v>273.11</v>
+        <v>266.07</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-19.45</v>
+        <v>-19.36</v>
       </c>
       <c r="K28" t="n">
-        <v>181.22</v>
+        <v>180.33</v>
       </c>
       <c r="L28" t="n">
-        <v>182.26</v>
+        <v>181.36</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-27.07</v>
+        <v>-28.65</v>
       </c>
       <c r="K29" t="n">
-        <v>28.67</v>
+        <v>30.34</v>
       </c>
       <c r="L29" t="n">
-        <v>39.43</v>
+        <v>41.72</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>62.77</v>
+        <v>60.04</v>
       </c>
       <c r="K30" t="n">
-        <v>57.9</v>
+        <v>55.39</v>
       </c>
       <c r="L30" t="n">
-        <v>85.40000000000001</v>
+        <v>81.69</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-46.2</v>
+        <v>-44.36</v>
       </c>
       <c r="K31" t="n">
-        <v>-81.75</v>
+        <v>-78.5</v>
       </c>
       <c r="L31" t="n">
-        <v>93.90000000000001</v>
+        <v>90.17</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>-37.31</v>
+        <v>-37.94</v>
       </c>
       <c r="K32" t="n">
-        <v>-45.12</v>
+        <v>-45.88</v>
       </c>
       <c r="L32" t="n">
-        <v>58.55</v>
+        <v>59.54</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-71.69</v>
+        <v>-70.17</v>
       </c>
       <c r="K33" t="n">
-        <v>-40.79</v>
+        <v>-39.92</v>
       </c>
       <c r="L33" t="n">
-        <v>82.48</v>
+        <v>80.73</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>-97.01000000000001</v>
+        <v>-86.40000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>-11.99</v>
+        <v>-10.68</v>
       </c>
       <c r="L34" t="n">
-        <v>97.75</v>
+        <v>87.06</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-65.18000000000001</v>
+        <v>-65.94</v>
       </c>
       <c r="K35" t="n">
-        <v>-69.26000000000001</v>
+        <v>-70.06999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>95.11</v>
+        <v>96.22</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-43.31</v>
+        <v>-41.49</v>
       </c>
       <c r="K36" t="n">
-        <v>-145.47</v>
+        <v>-139.35</v>
       </c>
       <c r="L36" t="n">
-        <v>151.78</v>
+        <v>145.39</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>77</v>
+        <v>73.13</v>
       </c>
       <c r="K37" t="n">
-        <v>-150.17</v>
+        <v>-142.61</v>
       </c>
       <c r="L37" t="n">
-        <v>168.76</v>
+        <v>160.26</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-8.1</v>
+        <v>-8.84</v>
       </c>
       <c r="K38" t="n">
-        <v>-74.09</v>
+        <v>-80.90000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>74.53</v>
+        <v>81.38</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-91.37</v>
+        <v>-94.56999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>49.83</v>
+        <v>51.58</v>
       </c>
       <c r="L39" t="n">
-        <v>104.08</v>
+        <v>107.72</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>188.62</v>
+        <v>169.82</v>
       </c>
       <c r="K40" t="n">
-        <v>-159.96</v>
+        <v>-144.02</v>
       </c>
       <c r="L40" t="n">
-        <v>247.32</v>
+        <v>222.67</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>274.84</v>
+        <v>264.41</v>
       </c>
       <c r="K41" t="n">
-        <v>78.42</v>
+        <v>75.45</v>
       </c>
       <c r="L41" t="n">
-        <v>285.81</v>
+        <v>274.97</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>129.57</v>
+        <v>128.54</v>
       </c>
       <c r="K42" t="n">
-        <v>-208.5</v>
+        <v>-206.84</v>
       </c>
       <c r="L42" t="n">
-        <v>245.48</v>
+        <v>243.53</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-23.35</v>
+        <v>-23.43</v>
       </c>
       <c r="K43" t="n">
-        <v>-220.38</v>
+        <v>-221.14</v>
       </c>
       <c r="L43" t="n">
-        <v>221.62</v>
+        <v>222.38</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>59.32</v>
+        <v>57.43</v>
       </c>
       <c r="K44" t="n">
-        <v>-40.46</v>
+        <v>-39.17</v>
       </c>
       <c r="L44" t="n">
-        <v>71.8</v>
+        <v>69.52</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>76.31</v>
+        <v>72.86</v>
       </c>
       <c r="K45" t="n">
-        <v>11.63</v>
+        <v>11.1</v>
       </c>
       <c r="L45" t="n">
-        <v>77.19</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-24.32</v>
+        <v>-24.21</v>
       </c>
       <c r="K46" t="n">
-        <v>-51.09</v>
+        <v>-50.88</v>
       </c>
       <c r="L46" t="n">
-        <v>56.59</v>
+        <v>56.35</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>7.94</v>
+        <v>7.93</v>
       </c>
       <c r="K47" t="n">
-        <v>69.37</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>69.83</v>
+        <v>69.69</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>38.47</v>
+        <v>37.29</v>
       </c>
       <c r="K48" t="n">
-        <v>-54.72</v>
+        <v>-53.03</v>
       </c>
       <c r="L48" t="n">
-        <v>66.89</v>
+        <v>64.83</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>-40.9</v>
+        <v>-44.06</v>
       </c>
       <c r="K49" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="L49" t="n">
-        <v>40.93</v>
+        <v>44.09</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>65.81999999999999</v>
+        <v>68.17</v>
       </c>
       <c r="K50" t="n">
-        <v>-33.95</v>
+        <v>-35.16</v>
       </c>
       <c r="L50" t="n">
-        <v>74.06</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-20.58</v>
+        <v>-19.85</v>
       </c>
       <c r="K51" t="n">
-        <v>149.59</v>
+        <v>144.25</v>
       </c>
       <c r="L51" t="n">
-        <v>150.99</v>
+        <v>145.61</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>33.71</v>
+        <v>32.29</v>
       </c>
       <c r="K52" t="n">
-        <v>-154.14</v>
+        <v>-147.61</v>
       </c>
       <c r="L52" t="n">
-        <v>157.79</v>
+        <v>151.1</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>16.12</v>
+        <v>15.88</v>
       </c>
       <c r="K53" t="n">
-        <v>35.07</v>
+        <v>34.55</v>
       </c>
       <c r="L53" t="n">
-        <v>38.6</v>
+        <v>38.02</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>140.33</v>
+        <v>138.69</v>
       </c>
       <c r="K54" t="n">
-        <v>-87.37</v>
+        <v>-86.34999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>165.31</v>
+        <v>163.38</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-32.76</v>
+        <v>-33.07</v>
       </c>
       <c r="K55" t="n">
-        <v>148.58</v>
+        <v>149.96</v>
       </c>
       <c r="L55" t="n">
-        <v>152.15</v>
+        <v>153.56</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>103.09</v>
+        <v>99.52</v>
       </c>
       <c r="K56" t="n">
-        <v>-436.1</v>
+        <v>-420.99</v>
       </c>
       <c r="L56" t="n">
-        <v>448.12</v>
+        <v>432.59</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>24.34</v>
+        <v>26.98</v>
       </c>
       <c r="K57" t="n">
-        <v>140.89</v>
+        <v>156.2</v>
       </c>
       <c r="L57" t="n">
-        <v>142.98</v>
+        <v>158.51</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>83.15000000000001</v>
+        <v>94.59</v>
       </c>
       <c r="K58" t="n">
-        <v>-92.54000000000001</v>
+        <v>-105.26</v>
       </c>
       <c r="L58" t="n">
-        <v>124.41</v>
+        <v>141.51</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>7.96</v>
+        <v>8.17</v>
       </c>
       <c r="K59" t="n">
-        <v>50.8</v>
+        <v>52.1</v>
       </c>
       <c r="L59" t="n">
-        <v>51.42</v>
+        <v>52.74</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>-54.75</v>
+        <v>-52.31</v>
       </c>
       <c r="K60" t="n">
-        <v>-52.87</v>
+        <v>-50.52</v>
       </c>
       <c r="L60" t="n">
-        <v>76.11</v>
+        <v>72.73</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>47.17</v>
+        <v>47.01</v>
       </c>
       <c r="K61" t="n">
-        <v>-31.83</v>
+        <v>-31.72</v>
       </c>
       <c r="L61" t="n">
-        <v>56.9</v>
+        <v>56.71</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>18.01</v>
+        <v>16.8</v>
       </c>
       <c r="K62" t="n">
-        <v>-139.62</v>
+        <v>-130.3</v>
       </c>
       <c r="L62" t="n">
-        <v>140.77</v>
+        <v>131.38</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-59.77</v>
+        <v>-56</v>
       </c>
       <c r="K63" t="n">
-        <v>-98.90000000000001</v>
+        <v>-92.66</v>
       </c>
       <c r="L63" t="n">
-        <v>115.56</v>
+        <v>108.27</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-35.32</v>
+        <v>-32.98</v>
       </c>
       <c r="K64" t="n">
-        <v>97.86</v>
+        <v>91.38</v>
       </c>
       <c r="L64" t="n">
-        <v>104.04</v>
+        <v>97.15000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.06</v>
+        <v>-2.1</v>
       </c>
       <c r="K65" t="n">
-        <v>90.76000000000001</v>
+        <v>92.52</v>
       </c>
       <c r="L65" t="n">
-        <v>90.78</v>
+        <v>92.55</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-2.6</v>
+        <v>-2.8</v>
       </c>
       <c r="K66" t="n">
-        <v>-65.20999999999999</v>
+        <v>-70.39</v>
       </c>
       <c r="L66" t="n">
-        <v>65.26000000000001</v>
+        <v>70.45</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>50.43</v>
+        <v>51.42</v>
       </c>
       <c r="K67" t="n">
-        <v>-70.22</v>
+        <v>-71.59</v>
       </c>
       <c r="L67" t="n">
-        <v>86.45999999999999</v>
+        <v>88.14</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>96.73999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="K68" t="n">
-        <v>-114.4</v>
+        <v>-114.13</v>
       </c>
       <c r="L68" t="n">
-        <v>149.82</v>
+        <v>149.46</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>63.44</v>
+        <v>66.42</v>
       </c>
       <c r="K69" t="n">
-        <v>-86.76000000000001</v>
+        <v>-90.84</v>
       </c>
       <c r="L69" t="n">
-        <v>107.48</v>
+        <v>112.53</v>
       </c>
     </row>
     <row r="70">
@@ -2995,7 +2995,7 @@
         <v>105.41</v>
       </c>
       <c r="K70" t="n">
-        <v>-104.99</v>
+        <v>-104.98</v>
       </c>
       <c r="L70" t="n">
         <v>148.77</v>
@@ -3034,13 +3034,13 @@
         <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>212.95</v>
+        <v>205.26</v>
       </c>
       <c r="K71" t="n">
-        <v>-306.44</v>
+        <v>-295.37</v>
       </c>
       <c r="L71" t="n">
-        <v>373.17</v>
+        <v>359.69</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-133.75</v>
+        <v>-133.43</v>
       </c>
       <c r="K72" t="n">
-        <v>-187.51</v>
+        <v>-187.06</v>
       </c>
       <c r="L72" t="n">
-        <v>230.32</v>
+        <v>229.77</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-80.58</v>
+        <v>-83.06</v>
       </c>
       <c r="K73" t="n">
-        <v>-152.02</v>
+        <v>-156.69</v>
       </c>
       <c r="L73" t="n">
-        <v>172.05</v>
+        <v>177.35</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>70</v>
+        <v>67.22</v>
       </c>
       <c r="K74" t="n">
-        <v>-9.08</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>70.59</v>
+        <v>67.79000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-40.3</v>
+        <v>-40.18</v>
       </c>
       <c r="K75" t="n">
-        <v>-45.11</v>
+        <v>-44.98</v>
       </c>
       <c r="L75" t="n">
-        <v>60.49</v>
+        <v>60.31</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>67.14</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>36.17</v>
+        <v>35.21</v>
       </c>
       <c r="L76" t="n">
-        <v>76.26000000000001</v>
+        <v>74.23999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-54.64</v>
+        <v>-55.13</v>
       </c>
       <c r="K77" t="n">
-        <v>-32.72</v>
+        <v>-33.01</v>
       </c>
       <c r="L77" t="n">
-        <v>63.69</v>
+        <v>64.26000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-33.77</v>
+        <v>-33.18</v>
       </c>
       <c r="K78" t="n">
-        <v>51.34</v>
+        <v>50.44</v>
       </c>
       <c r="L78" t="n">
-        <v>61.45</v>
+        <v>60.38</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>-49.03</v>
+        <v>-50.46</v>
       </c>
       <c r="K79" t="n">
-        <v>-26.96</v>
+        <v>-27.75</v>
       </c>
       <c r="L79" t="n">
-        <v>55.95</v>
+        <v>57.58</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-37.17</v>
+        <v>-38.47</v>
       </c>
       <c r="K80" t="n">
-        <v>-71.44</v>
+        <v>-73.93000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>80.53</v>
+        <v>83.34</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>17.09</v>
+        <v>17.63</v>
       </c>
       <c r="K81" t="n">
-        <v>-78.81</v>
+        <v>-81.29000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>80.64</v>
+        <v>83.18000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>136</v>
+        <v>131.34</v>
       </c>
       <c r="K82" t="n">
-        <v>39.66</v>
+        <v>38.3</v>
       </c>
       <c r="L82" t="n">
-        <v>141.66</v>
+        <v>136.81</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>65.38</v>
+        <v>69.98</v>
       </c>
       <c r="K83" t="n">
-        <v>-71.76000000000001</v>
+        <v>-76.81</v>
       </c>
       <c r="L83" t="n">
-        <v>97.08</v>
+        <v>103.9</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-58.1</v>
+        <v>-60.83</v>
       </c>
       <c r="K84" t="n">
-        <v>-90.29000000000001</v>
+        <v>-94.54000000000001</v>
       </c>
       <c r="L84" t="n">
-        <v>107.37</v>
+        <v>112.42</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>83.16</v>
+        <v>89.8</v>
       </c>
       <c r="K85" t="n">
-        <v>-70.48999999999999</v>
+        <v>-76.11</v>
       </c>
       <c r="L85" t="n">
-        <v>109.02</v>
+        <v>117.72</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>254.18</v>
+        <v>257.8</v>
       </c>
       <c r="K86" t="n">
-        <v>33.18</v>
+        <v>33.65</v>
       </c>
       <c r="L86" t="n">
-        <v>256.34</v>
+        <v>259.99</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-134.71</v>
+        <v>-156.61</v>
       </c>
       <c r="K87" t="n">
-        <v>-86.95999999999999</v>
+        <v>-101.1</v>
       </c>
       <c r="L87" t="n">
-        <v>160.34</v>
+        <v>186.4</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>63.29</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="K88" t="n">
-        <v>227.34</v>
+        <v>236.92</v>
       </c>
       <c r="L88" t="n">
-        <v>235.99</v>
+        <v>245.93</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-24.xlsx
+++ b/output/2025-05-24.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-68.67</v>
+        <v>-66.70999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-19.88</v>
+        <v>-19.31</v>
       </c>
       <c r="L14" t="n">
-        <v>71.48</v>
+        <v>69.45</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-42.44</v>
+        <v>-42.14</v>
       </c>
       <c r="K15" t="n">
-        <v>46.57</v>
+        <v>46.24</v>
       </c>
       <c r="L15" t="n">
-        <v>63.01</v>
+        <v>62.56</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>5.92</v>
+        <v>5.59</v>
       </c>
       <c r="K16" t="n">
-        <v>98.76000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="L16" t="n">
-        <v>98.94</v>
+        <v>93.45999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>41.42</v>
+        <v>41.11</v>
       </c>
       <c r="K17" t="n">
-        <v>67.55</v>
+        <v>67.05</v>
       </c>
       <c r="L17" t="n">
-        <v>79.23999999999999</v>
+        <v>78.65000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>39.09</v>
+        <v>38.89</v>
       </c>
       <c r="K18" t="n">
-        <v>58.91</v>
+        <v>58.6</v>
       </c>
       <c r="L18" t="n">
-        <v>70.69</v>
+        <v>70.33</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>38.99</v>
+        <v>40.33</v>
       </c>
       <c r="K19" t="n">
-        <v>40.37</v>
+        <v>41.75</v>
       </c>
       <c r="L19" t="n">
-        <v>56.12</v>
+        <v>58.05</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>24.03</v>
+        <v>25.59</v>
       </c>
       <c r="K20" t="n">
-        <v>-69.09</v>
+        <v>-73.56999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>73.15000000000001</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>133.59</v>
+        <v>128.67</v>
       </c>
       <c r="K21" t="n">
-        <v>17.88</v>
+        <v>17.22</v>
       </c>
       <c r="L21" t="n">
-        <v>134.78</v>
+        <v>129.82</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-19.84</v>
+        <v>-20.74</v>
       </c>
       <c r="K22" t="n">
-        <v>-75.70999999999999</v>
+        <v>-79.14</v>
       </c>
       <c r="L22" t="n">
-        <v>78.27</v>
+        <v>81.81</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>117.89</v>
+        <v>116.86</v>
       </c>
       <c r="K23" t="n">
-        <v>-79.56999999999999</v>
+        <v>-78.88</v>
       </c>
       <c r="L23" t="n">
-        <v>142.23</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-19.53</v>
+        <v>-19.77</v>
       </c>
       <c r="K24" t="n">
-        <v>-134.31</v>
+        <v>-135.97</v>
       </c>
       <c r="L24" t="n">
-        <v>135.72</v>
+        <v>137.4</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>43.71</v>
+        <v>47.07</v>
       </c>
       <c r="K25" t="n">
-        <v>78.59999999999999</v>
+        <v>84.64</v>
       </c>
       <c r="L25" t="n">
-        <v>89.94</v>
+        <v>96.84999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>187.58</v>
+        <v>188.42</v>
       </c>
       <c r="K26" t="n">
-        <v>-77.06</v>
+        <v>-77.41</v>
       </c>
       <c r="L26" t="n">
-        <v>202.79</v>
+        <v>203.7</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>262.35</v>
+        <v>251.92</v>
       </c>
       <c r="K27" t="n">
-        <v>44.37</v>
+        <v>42.61</v>
       </c>
       <c r="L27" t="n">
-        <v>266.07</v>
+        <v>255.5</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-19.36</v>
+        <v>-19.25</v>
       </c>
       <c r="K28" t="n">
+        <v>179.3</v>
+      </c>
+      <c r="L28" t="n">
         <v>180.33</v>
-      </c>
-      <c r="L28" t="n">
-        <v>181.36</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-28.65</v>
+        <v>-30.75</v>
       </c>
       <c r="K29" t="n">
-        <v>30.34</v>
+        <v>32.57</v>
       </c>
       <c r="L29" t="n">
-        <v>41.72</v>
+        <v>44.79</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>60.04</v>
+        <v>57.88</v>
       </c>
       <c r="K30" t="n">
-        <v>55.39</v>
+        <v>53.39</v>
       </c>
       <c r="L30" t="n">
-        <v>81.69</v>
+        <v>78.73999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-44.36</v>
+        <v>-42.32</v>
       </c>
       <c r="K31" t="n">
-        <v>-78.5</v>
+        <v>-74.90000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>90.17</v>
+        <v>86.03</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>-37.94</v>
+        <v>-38.66</v>
       </c>
       <c r="K32" t="n">
-        <v>-45.88</v>
+        <v>-46.76</v>
       </c>
       <c r="L32" t="n">
-        <v>59.54</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-70.17</v>
+        <v>-69.22</v>
       </c>
       <c r="K33" t="n">
-        <v>-39.92</v>
+        <v>-39.38</v>
       </c>
       <c r="L33" t="n">
-        <v>80.73</v>
+        <v>79.64</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>-86.40000000000001</v>
+        <v>-85.72</v>
       </c>
       <c r="K34" t="n">
-        <v>-10.68</v>
+        <v>-10.6</v>
       </c>
       <c r="L34" t="n">
-        <v>87.06</v>
+        <v>86.37</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-65.94</v>
+        <v>-66.83</v>
       </c>
       <c r="K35" t="n">
-        <v>-70.06999999999999</v>
+        <v>-71.02</v>
       </c>
       <c r="L35" t="n">
-        <v>96.22</v>
+        <v>97.52</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-41.49</v>
+        <v>-39.56</v>
       </c>
       <c r="K36" t="n">
-        <v>-139.35</v>
+        <v>-132.86</v>
       </c>
       <c r="L36" t="n">
-        <v>145.39</v>
+        <v>138.62</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>73.13</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>-142.61</v>
+        <v>-134.63</v>
       </c>
       <c r="L37" t="n">
-        <v>160.26</v>
+        <v>151.3</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-8.84</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>-80.90000000000001</v>
+        <v>-88.69</v>
       </c>
       <c r="L38" t="n">
-        <v>81.38</v>
+        <v>89.20999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-94.56999999999999</v>
+        <v>-98.14</v>
       </c>
       <c r="K39" t="n">
-        <v>51.58</v>
+        <v>53.52</v>
       </c>
       <c r="L39" t="n">
-        <v>107.72</v>
+        <v>111.78</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>169.82</v>
+        <v>162.04</v>
       </c>
       <c r="K40" t="n">
-        <v>-144.02</v>
+        <v>-137.42</v>
       </c>
       <c r="L40" t="n">
-        <v>222.67</v>
+        <v>212.46</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>264.41</v>
+        <v>250.78</v>
       </c>
       <c r="K41" t="n">
-        <v>75.45</v>
+        <v>71.56</v>
       </c>
       <c r="L41" t="n">
-        <v>274.97</v>
+        <v>260.79</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>128.54</v>
+        <v>125.32</v>
       </c>
       <c r="K42" t="n">
-        <v>-206.84</v>
+        <v>-201.66</v>
       </c>
       <c r="L42" t="n">
-        <v>243.53</v>
+        <v>237.43</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-23.43</v>
+        <v>-23.03</v>
       </c>
       <c r="K43" t="n">
-        <v>-221.14</v>
+        <v>-217.39</v>
       </c>
       <c r="L43" t="n">
-        <v>222.38</v>
+        <v>218.61</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>57.43</v>
+        <v>56.02</v>
       </c>
       <c r="K44" t="n">
-        <v>-39.17</v>
+        <v>-38.21</v>
       </c>
       <c r="L44" t="n">
-        <v>69.52</v>
+        <v>67.81</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>72.86</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>11.1</v>
+        <v>10.82</v>
       </c>
       <c r="L45" t="n">
-        <v>73.7</v>
+        <v>71.83</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-24.21</v>
+        <v>-24.77</v>
       </c>
       <c r="K46" t="n">
-        <v>-50.88</v>
+        <v>-52.06</v>
       </c>
       <c r="L46" t="n">
-        <v>56.35</v>
+        <v>57.65</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>7.93</v>
+        <v>8.1</v>
       </c>
       <c r="K47" t="n">
-        <v>69.23999999999999</v>
+        <v>70.77</v>
       </c>
       <c r="L47" t="n">
-        <v>69.69</v>
+        <v>71.23999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>37.29</v>
+        <v>39.24</v>
       </c>
       <c r="K48" t="n">
-        <v>-53.03</v>
+        <v>-55.81</v>
       </c>
       <c r="L48" t="n">
-        <v>64.83</v>
+        <v>68.23</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>-44.06</v>
+        <v>-47.9</v>
       </c>
       <c r="K49" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="L49" t="n">
-        <v>44.09</v>
+        <v>47.92</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>68.17</v>
+        <v>70.86</v>
       </c>
       <c r="K50" t="n">
-        <v>-35.16</v>
+        <v>-36.54</v>
       </c>
       <c r="L50" t="n">
-        <v>76.7</v>
+        <v>79.73</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-19.85</v>
+        <v>-19.21</v>
       </c>
       <c r="K51" t="n">
-        <v>144.25</v>
+        <v>139.65</v>
       </c>
       <c r="L51" t="n">
-        <v>145.61</v>
+        <v>140.96</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>32.29</v>
+        <v>30.92</v>
       </c>
       <c r="K52" t="n">
-        <v>-147.61</v>
+        <v>-141.36</v>
       </c>
       <c r="L52" t="n">
-        <v>151.1</v>
+        <v>144.7</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>15.88</v>
+        <v>17.23</v>
       </c>
       <c r="K53" t="n">
-        <v>34.55</v>
+        <v>37.48</v>
       </c>
       <c r="L53" t="n">
-        <v>38.02</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>138.69</v>
+        <v>136.19</v>
       </c>
       <c r="K54" t="n">
-        <v>-86.34999999999999</v>
+        <v>-84.79000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>163.38</v>
+        <v>160.43</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-33.07</v>
+        <v>-33.1</v>
       </c>
       <c r="K55" t="n">
-        <v>149.96</v>
+        <v>150.09</v>
       </c>
       <c r="L55" t="n">
-        <v>153.56</v>
+        <v>153.7</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>99.52</v>
+        <v>91.94</v>
       </c>
       <c r="K56" t="n">
-        <v>-420.99</v>
+        <v>-388.92</v>
       </c>
       <c r="L56" t="n">
-        <v>432.59</v>
+        <v>399.64</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>26.98</v>
+        <v>28.83</v>
       </c>
       <c r="K57" t="n">
-        <v>156.2</v>
+        <v>166.9</v>
       </c>
       <c r="L57" t="n">
-        <v>158.51</v>
+        <v>169.38</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>94.59</v>
+        <v>104.08</v>
       </c>
       <c r="K58" t="n">
-        <v>-105.26</v>
+        <v>-115.82</v>
       </c>
       <c r="L58" t="n">
-        <v>141.51</v>
+        <v>155.71</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>8.17</v>
+        <v>8.42</v>
       </c>
       <c r="K59" t="n">
-        <v>52.1</v>
+        <v>53.72</v>
       </c>
       <c r="L59" t="n">
-        <v>52.74</v>
+        <v>54.38</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>-52.31</v>
+        <v>-50.83</v>
       </c>
       <c r="K60" t="n">
-        <v>-50.52</v>
+        <v>-49.09</v>
       </c>
       <c r="L60" t="n">
-        <v>72.73</v>
+        <v>70.66</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>47.01</v>
+        <v>47.55</v>
       </c>
       <c r="K61" t="n">
-        <v>-31.72</v>
+        <v>-32.08</v>
       </c>
       <c r="L61" t="n">
-        <v>56.71</v>
+        <v>57.36</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>16.8</v>
+        <v>15.63</v>
       </c>
       <c r="K62" t="n">
-        <v>-130.3</v>
+        <v>-121.16</v>
       </c>
       <c r="L62" t="n">
-        <v>131.38</v>
+        <v>122.16</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-56</v>
+        <v>-53.26</v>
       </c>
       <c r="K63" t="n">
-        <v>-92.66</v>
+        <v>-88.13</v>
       </c>
       <c r="L63" t="n">
-        <v>108.27</v>
+        <v>102.98</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-32.98</v>
+        <v>-31.6</v>
       </c>
       <c r="K64" t="n">
-        <v>91.38</v>
+        <v>87.55</v>
       </c>
       <c r="L64" t="n">
-        <v>97.15000000000001</v>
+        <v>93.08</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.1</v>
+        <v>-2.18</v>
       </c>
       <c r="K65" t="n">
-        <v>92.52</v>
+        <v>95.79000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>92.55</v>
+        <v>95.81999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-2.8</v>
+        <v>-3.05</v>
       </c>
       <c r="K66" t="n">
-        <v>-70.39</v>
+        <v>-76.72</v>
       </c>
       <c r="L66" t="n">
-        <v>70.45</v>
+        <v>76.78</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>51.42</v>
+        <v>52.54</v>
       </c>
       <c r="K67" t="n">
-        <v>-71.59</v>
+        <v>-73.16</v>
       </c>
       <c r="L67" t="n">
-        <v>88.14</v>
+        <v>90.06999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>96.5</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>-114.13</v>
+        <v>-112.99</v>
       </c>
       <c r="L68" t="n">
-        <v>149.46</v>
+        <v>147.97</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>66.42</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>-90.84</v>
+        <v>-95.26000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>112.53</v>
+        <v>118.01</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>105.41</v>
+        <v>104.87</v>
       </c>
       <c r="K70" t="n">
-        <v>-104.98</v>
+        <v>-104.44</v>
       </c>
       <c r="L70" t="n">
-        <v>148.77</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>205.26</v>
+        <v>190.64</v>
       </c>
       <c r="K71" t="n">
-        <v>-295.37</v>
+        <v>-274.34</v>
       </c>
       <c r="L71" t="n">
-        <v>359.69</v>
+        <v>334.08</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-133.43</v>
+        <v>-130.64</v>
       </c>
       <c r="K72" t="n">
-        <v>-187.06</v>
+        <v>-183.16</v>
       </c>
       <c r="L72" t="n">
-        <v>229.77</v>
+        <v>224.98</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-83.06</v>
+        <v>-84.58</v>
       </c>
       <c r="K73" t="n">
-        <v>-156.69</v>
+        <v>-159.57</v>
       </c>
       <c r="L73" t="n">
-        <v>177.35</v>
+        <v>180.6</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>67.22</v>
+        <v>65.92</v>
       </c>
       <c r="K74" t="n">
-        <v>-8.720000000000001</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>67.79000000000001</v>
+        <v>66.47</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-40.18</v>
+        <v>-41</v>
       </c>
       <c r="K75" t="n">
-        <v>-44.98</v>
+        <v>-45.9</v>
       </c>
       <c r="L75" t="n">
-        <v>60.31</v>
+        <v>61.54</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>65.34999999999999</v>
+        <v>64.33</v>
       </c>
       <c r="K76" t="n">
-        <v>35.21</v>
+        <v>34.66</v>
       </c>
       <c r="L76" t="n">
-        <v>74.23999999999999</v>
+        <v>73.06999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-55.13</v>
+        <v>-56.75</v>
       </c>
       <c r="K77" t="n">
-        <v>-33.01</v>
+        <v>-33.98</v>
       </c>
       <c r="L77" t="n">
-        <v>64.26000000000001</v>
+        <v>66.15000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-33.18</v>
+        <v>-35.1</v>
       </c>
       <c r="K78" t="n">
-        <v>50.44</v>
+        <v>53.36</v>
       </c>
       <c r="L78" t="n">
-        <v>60.38</v>
+        <v>63.87</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>-50.46</v>
+        <v>-52.23</v>
       </c>
       <c r="K79" t="n">
-        <v>-27.75</v>
+        <v>-28.73</v>
       </c>
       <c r="L79" t="n">
-        <v>57.58</v>
+        <v>59.61</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-38.47</v>
+        <v>-40.18</v>
       </c>
       <c r="K80" t="n">
-        <v>-73.93000000000001</v>
+        <v>-77.22</v>
       </c>
       <c r="L80" t="n">
-        <v>83.34</v>
+        <v>87.05</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>17.63</v>
+        <v>18.39</v>
       </c>
       <c r="K81" t="n">
-        <v>-81.29000000000001</v>
+        <v>-84.8</v>
       </c>
       <c r="L81" t="n">
-        <v>83.18000000000001</v>
+        <v>86.78</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>131.34</v>
+        <v>126.62</v>
       </c>
       <c r="K82" t="n">
-        <v>38.3</v>
+        <v>36.92</v>
       </c>
       <c r="L82" t="n">
-        <v>136.81</v>
+        <v>131.9</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>69.98</v>
+        <v>75.05</v>
       </c>
       <c r="K83" t="n">
-        <v>-76.81</v>
+        <v>-82.38</v>
       </c>
       <c r="L83" t="n">
-        <v>103.9</v>
+        <v>111.44</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-60.83</v>
+        <v>-63.81</v>
       </c>
       <c r="K84" t="n">
-        <v>-94.54000000000001</v>
+        <v>-99.17</v>
       </c>
       <c r="L84" t="n">
-        <v>112.42</v>
+        <v>117.92</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>89.8</v>
+        <v>96.22</v>
       </c>
       <c r="K85" t="n">
-        <v>-76.11</v>
+        <v>-81.56</v>
       </c>
       <c r="L85" t="n">
-        <v>117.72</v>
+        <v>126.14</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>257.8</v>
+        <v>251.78</v>
       </c>
       <c r="K86" t="n">
-        <v>33.65</v>
+        <v>32.86</v>
       </c>
       <c r="L86" t="n">
-        <v>259.99</v>
+        <v>253.91</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-156.61</v>
+        <v>-168.48</v>
       </c>
       <c r="K87" t="n">
-        <v>-101.1</v>
+        <v>-108.76</v>
       </c>
       <c r="L87" t="n">
-        <v>186.4</v>
+        <v>200.53</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>65.95999999999999</v>
+        <v>65.61</v>
       </c>
       <c r="K88" t="n">
-        <v>236.92</v>
+        <v>235.66</v>
       </c>
       <c r="L88" t="n">
-        <v>245.93</v>
+        <v>244.62</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-24.xlsx
+++ b/output/2025-05-24.xlsx
@@ -628,25 +628,25 @@
         <v>2.92</v>
       </c>
       <c r="F14" t="n">
-        <v>11.55</v>
+        <v>7.6</v>
       </c>
       <c r="G14" t="n">
-        <v>148.5</v>
+        <v>157.4</v>
       </c>
       <c r="H14" t="n">
-        <v>9.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I14" t="n">
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-66.70999999999999</v>
+        <v>-72.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-19.31</v>
+        <v>-21.68</v>
       </c>
       <c r="L14" t="n">
-        <v>69.45</v>
+        <v>75.58</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>3.64</v>
       </c>
       <c r="F15" t="n">
-        <v>11.92</v>
+        <v>11.02</v>
       </c>
       <c r="G15" t="n">
-        <v>150.1</v>
+        <v>164.9</v>
       </c>
       <c r="H15" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-42.14</v>
+        <v>-49.89</v>
       </c>
       <c r="K15" t="n">
-        <v>46.24</v>
+        <v>53.48</v>
       </c>
       <c r="L15" t="n">
-        <v>62.56</v>
+        <v>73.14</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>3.41</v>
       </c>
       <c r="F16" t="n">
-        <v>11.53</v>
+        <v>8.35</v>
       </c>
       <c r="G16" t="n">
-        <v>130.3</v>
+        <v>157.1</v>
       </c>
       <c r="H16" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>5.59</v>
+        <v>5.11</v>
       </c>
       <c r="K16" t="n">
-        <v>93.3</v>
+        <v>85.59</v>
       </c>
       <c r="L16" t="n">
-        <v>93.45999999999999</v>
+        <v>85.73999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>3.86</v>
       </c>
       <c r="F17" t="n">
-        <v>11.8</v>
+        <v>9.27</v>
       </c>
       <c r="G17" t="n">
-        <v>146.5</v>
+        <v>162.4</v>
       </c>
       <c r="H17" t="n">
-        <v>16.6</v>
+        <v>7.4</v>
       </c>
       <c r="I17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>41.11</v>
+        <v>43.33</v>
       </c>
       <c r="K17" t="n">
-        <v>67.05</v>
+        <v>67.16</v>
       </c>
       <c r="L17" t="n">
-        <v>78.65000000000001</v>
+        <v>79.92</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>3.68</v>
       </c>
       <c r="F18" t="n">
-        <v>11.92</v>
+        <v>11.18</v>
       </c>
       <c r="G18" t="n">
-        <v>146.8</v>
+        <v>164.8</v>
       </c>
       <c r="H18" t="n">
-        <v>12.6</v>
+        <v>7.6</v>
       </c>
       <c r="I18" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>38.89</v>
+        <v>47.28</v>
       </c>
       <c r="K18" t="n">
-        <v>58.6</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>70.33</v>
+        <v>82.83</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>3.12</v>
       </c>
       <c r="F19" t="n">
-        <v>11.03</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>155.8</v>
+        <v>147.2</v>
       </c>
       <c r="H19" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>40.33</v>
+        <v>48.08</v>
       </c>
       <c r="K19" t="n">
-        <v>41.75</v>
+        <v>45.05</v>
       </c>
       <c r="L19" t="n">
-        <v>58.05</v>
+        <v>65.89</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>3.2</v>
       </c>
       <c r="F20" t="n">
-        <v>12.22</v>
+        <v>11.47</v>
       </c>
       <c r="G20" t="n">
-        <v>150.9</v>
+        <v>171</v>
       </c>
       <c r="H20" t="n">
-        <v>16.1</v>
+        <v>9.6</v>
       </c>
       <c r="I20" t="n">
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>25.59</v>
+        <v>25.98</v>
       </c>
       <c r="K20" t="n">
-        <v>-73.56999999999999</v>
+        <v>-97.68000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>77.90000000000001</v>
+        <v>101.08</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>3.4</v>
       </c>
       <c r="F21" t="n">
-        <v>11.87</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>155.2</v>
+        <v>163.9</v>
       </c>
       <c r="H21" t="n">
-        <v>16.5</v>
+        <v>11.8</v>
       </c>
       <c r="I21" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>128.67</v>
+        <v>146.76</v>
       </c>
       <c r="K21" t="n">
-        <v>17.22</v>
+        <v>10.26</v>
       </c>
       <c r="L21" t="n">
-        <v>129.82</v>
+        <v>147.12</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>3.22</v>
       </c>
       <c r="F22" t="n">
-        <v>10.43</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>145.3</v>
+        <v>135.1</v>
       </c>
       <c r="H22" t="n">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>-20.74</v>
+        <v>-10.06</v>
       </c>
       <c r="K22" t="n">
-        <v>-79.14</v>
+        <v>-91.31</v>
       </c>
       <c r="L22" t="n">
-        <v>81.81</v>
+        <v>91.87</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>3.14</v>
       </c>
       <c r="F23" t="n">
-        <v>10.9</v>
+        <v>8.25</v>
       </c>
       <c r="G23" t="n">
-        <v>151.8</v>
+        <v>144.5</v>
       </c>
       <c r="H23" t="n">
-        <v>14</v>
+        <v>10.1</v>
       </c>
       <c r="I23" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>116.86</v>
+        <v>126.98</v>
       </c>
       <c r="K23" t="n">
-        <v>-78.88</v>
+        <v>-92.87</v>
       </c>
       <c r="L23" t="n">
-        <v>141</v>
+        <v>157.32</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>3.33</v>
       </c>
       <c r="F24" t="n">
-        <v>11.27</v>
+        <v>10.56</v>
       </c>
       <c r="G24" t="n">
-        <v>170.3</v>
+        <v>151.9</v>
       </c>
       <c r="H24" t="n">
-        <v>13.2</v>
+        <v>19.3</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-19.77</v>
+        <v>-1.66</v>
       </c>
       <c r="K24" t="n">
-        <v>-135.97</v>
+        <v>-175.22</v>
       </c>
       <c r="L24" t="n">
-        <v>137.4</v>
+        <v>175.23</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>2.72</v>
       </c>
       <c r="F25" t="n">
-        <v>11.04</v>
+        <v>8.94</v>
       </c>
       <c r="G25" t="n">
-        <v>154</v>
+        <v>147.3</v>
       </c>
       <c r="H25" t="n">
-        <v>11.4</v>
+        <v>11.1</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>47.07</v>
+        <v>92.86</v>
       </c>
       <c r="K25" t="n">
-        <v>84.64</v>
+        <v>67.92</v>
       </c>
       <c r="L25" t="n">
-        <v>96.84999999999999</v>
+        <v>115.04</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>3.48</v>
       </c>
       <c r="F26" t="n">
-        <v>11.59</v>
+        <v>12.66</v>
       </c>
       <c r="G26" t="n">
-        <v>159.1</v>
+        <v>158.3</v>
       </c>
       <c r="H26" t="n">
-        <v>16.7</v>
+        <v>13.7</v>
       </c>
       <c r="I26" t="n">
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>188.42</v>
+        <v>226.44</v>
       </c>
       <c r="K26" t="n">
-        <v>-77.41</v>
+        <v>-126.19</v>
       </c>
       <c r="L26" t="n">
-        <v>203.7</v>
+        <v>259.22</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>3.4</v>
       </c>
       <c r="F27" t="n">
-        <v>11.57</v>
+        <v>13.11</v>
       </c>
       <c r="G27" t="n">
-        <v>166.4</v>
+        <v>157.9</v>
       </c>
       <c r="H27" t="n">
-        <v>1.5</v>
+        <v>17.4</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>251.92</v>
+        <v>295.73</v>
       </c>
       <c r="K27" t="n">
-        <v>42.61</v>
+        <v>19.36</v>
       </c>
       <c r="L27" t="n">
-        <v>255.5</v>
+        <v>296.37</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>2.51</v>
       </c>
       <c r="F28" t="n">
-        <v>11.24</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>168.2</v>
+        <v>151.2</v>
       </c>
       <c r="H28" t="n">
-        <v>13.5</v>
+        <v>18.3</v>
       </c>
       <c r="I28" t="n">
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-19.25</v>
+        <v>2.55</v>
       </c>
       <c r="K28" t="n">
-        <v>179.3</v>
+        <v>200.6</v>
       </c>
       <c r="L28" t="n">
-        <v>180.33</v>
+        <v>200.62</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>3.59</v>
       </c>
       <c r="F29" t="n">
-        <v>11.07</v>
+        <v>11.27</v>
       </c>
       <c r="G29" t="n">
-        <v>151.9</v>
+        <v>147.9</v>
       </c>
       <c r="H29" t="n">
-        <v>13.2</v>
+        <v>10.1</v>
       </c>
       <c r="I29" t="n">
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-30.75</v>
+        <v>-37.07</v>
       </c>
       <c r="K29" t="n">
-        <v>32.57</v>
+        <v>38.9</v>
       </c>
       <c r="L29" t="n">
-        <v>44.79</v>
+        <v>53.73</v>
       </c>
     </row>
     <row r="30">
@@ -1300,25 +1300,25 @@
         <v>3.7</v>
       </c>
       <c r="F30" t="n">
-        <v>11.47</v>
+        <v>11.44</v>
       </c>
       <c r="G30" t="n">
-        <v>158.4</v>
+        <v>155.9</v>
       </c>
       <c r="H30" t="n">
-        <v>12.4</v>
+        <v>13.4</v>
       </c>
       <c r="I30" t="n">
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>57.88</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>53.39</v>
+        <v>59.85</v>
       </c>
       <c r="L30" t="n">
-        <v>78.73999999999999</v>
+        <v>89.25</v>
       </c>
     </row>
     <row r="31">
@@ -1342,25 +1342,25 @@
         <v>3.29</v>
       </c>
       <c r="F31" t="n">
-        <v>10.98</v>
+        <v>11.19</v>
       </c>
       <c r="G31" t="n">
-        <v>148</v>
+        <v>146.1</v>
       </c>
       <c r="H31" t="n">
-        <v>16.5</v>
+        <v>8.1</v>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-42.32</v>
+        <v>-45.84</v>
       </c>
       <c r="K31" t="n">
-        <v>-74.90000000000001</v>
+        <v>-82.53</v>
       </c>
       <c r="L31" t="n">
-        <v>86.03</v>
+        <v>94.41</v>
       </c>
     </row>
     <row r="32">
@@ -1384,25 +1384,25 @@
         <v>3.14</v>
       </c>
       <c r="F32" t="n">
-        <v>11.35</v>
+        <v>12.24</v>
       </c>
       <c r="G32" t="n">
-        <v>148.8</v>
+        <v>153.5</v>
       </c>
       <c r="H32" t="n">
-        <v>17.6</v>
+        <v>8.6</v>
       </c>
       <c r="I32" t="n">
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>-38.66</v>
+        <v>-46.09</v>
       </c>
       <c r="K32" t="n">
-        <v>-46.76</v>
+        <v>-59.9</v>
       </c>
       <c r="L32" t="n">
-        <v>60.67</v>
+        <v>75.58</v>
       </c>
     </row>
     <row r="33">
@@ -1426,25 +1426,25 @@
         <v>3.57</v>
       </c>
       <c r="F33" t="n">
-        <v>10.79</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>157.1</v>
+        <v>142.4</v>
       </c>
       <c r="H33" t="n">
-        <v>10.6</v>
+        <v>12.7</v>
       </c>
       <c r="I33" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-69.22</v>
+        <v>-70.12</v>
       </c>
       <c r="K33" t="n">
-        <v>-39.38</v>
+        <v>-42.81</v>
       </c>
       <c r="L33" t="n">
-        <v>79.64</v>
+        <v>82.16</v>
       </c>
     </row>
     <row r="34">
@@ -1468,25 +1468,25 @@
         <v>4.72</v>
       </c>
       <c r="F34" t="n">
-        <v>11.72</v>
+        <v>13.11</v>
       </c>
       <c r="G34" t="n">
-        <v>162.2</v>
+        <v>160.9</v>
       </c>
       <c r="H34" t="n">
-        <v>11.1</v>
+        <v>15.3</v>
       </c>
       <c r="I34" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-85.72</v>
+        <v>-106.29</v>
       </c>
       <c r="K34" t="n">
-        <v>-10.6</v>
+        <v>-18.03</v>
       </c>
       <c r="L34" t="n">
-        <v>86.37</v>
+        <v>107.81</v>
       </c>
     </row>
     <row r="35">
@@ -1510,25 +1510,25 @@
         <v>3.27</v>
       </c>
       <c r="F35" t="n">
-        <v>11</v>
+        <v>10.07</v>
       </c>
       <c r="G35" t="n">
-        <v>147.5</v>
+        <v>146.4</v>
       </c>
       <c r="H35" t="n">
-        <v>5.6</v>
+        <v>7.9</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>-66.83</v>
+        <v>-61.51</v>
       </c>
       <c r="K35" t="n">
-        <v>-71.02</v>
+        <v>-81.48999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>97.52</v>
+        <v>102.1</v>
       </c>
     </row>
     <row r="36">
@@ -1552,25 +1552,25 @@
         <v>3.52</v>
       </c>
       <c r="F36" t="n">
-        <v>11.07</v>
+        <v>10.55</v>
       </c>
       <c r="G36" t="n">
-        <v>145.6</v>
+        <v>147.9</v>
       </c>
       <c r="H36" t="n">
-        <v>11.4</v>
+        <v>6.9</v>
       </c>
       <c r="I36" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>-39.56</v>
+        <v>-37.03</v>
       </c>
       <c r="K36" t="n">
-        <v>-132.86</v>
+        <v>-145.64</v>
       </c>
       <c r="L36" t="n">
-        <v>138.62</v>
+        <v>150.27</v>
       </c>
     </row>
     <row r="37">
@@ -1594,25 +1594,25 @@
         <v>3.6</v>
       </c>
       <c r="F37" t="n">
-        <v>11.36</v>
+        <v>11.24</v>
       </c>
       <c r="G37" t="n">
-        <v>158.9</v>
+        <v>153.7</v>
       </c>
       <c r="H37" t="n">
-        <v>11</v>
+        <v>13.6</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>69.04000000000001</v>
+        <v>85.03</v>
       </c>
       <c r="K37" t="n">
-        <v>-134.63</v>
+        <v>-164.91</v>
       </c>
       <c r="L37" t="n">
-        <v>151.3</v>
+        <v>185.54</v>
       </c>
     </row>
     <row r="38">
@@ -1636,25 +1636,25 @@
         <v>3.01</v>
       </c>
       <c r="F38" t="n">
-        <v>11.17</v>
+        <v>5.89</v>
       </c>
       <c r="G38" t="n">
-        <v>150.7</v>
+        <v>149.9</v>
       </c>
       <c r="H38" t="n">
-        <v>4.6</v>
+        <v>9.5</v>
       </c>
       <c r="I38" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>-9.699999999999999</v>
+        <v>16.26</v>
       </c>
       <c r="K38" t="n">
-        <v>-88.69</v>
+        <v>-114.03</v>
       </c>
       <c r="L38" t="n">
-        <v>89.20999999999999</v>
+        <v>115.19</v>
       </c>
     </row>
     <row r="39">
@@ -1678,25 +1678,25 @@
         <v>3.36</v>
       </c>
       <c r="F39" t="n">
-        <v>12.05</v>
+        <v>11.77</v>
       </c>
       <c r="G39" t="n">
-        <v>144.8</v>
+        <v>167.5</v>
       </c>
       <c r="H39" t="n">
-        <v>16.2</v>
+        <v>6.6</v>
       </c>
       <c r="I39" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-98.14</v>
+        <v>-142.89</v>
       </c>
       <c r="K39" t="n">
-        <v>53.52</v>
+        <v>27.62</v>
       </c>
       <c r="L39" t="n">
-        <v>111.78</v>
+        <v>145.54</v>
       </c>
     </row>
     <row r="40">
@@ -1720,25 +1720,25 @@
         <v>3.71</v>
       </c>
       <c r="F40" t="n">
-        <v>11.15</v>
+        <v>10.53</v>
       </c>
       <c r="G40" t="n">
-        <v>163.9</v>
+        <v>149.5</v>
       </c>
       <c r="H40" t="n">
-        <v>10</v>
+        <v>16.1</v>
       </c>
       <c r="I40" t="n">
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>162.04</v>
+        <v>186.72</v>
       </c>
       <c r="K40" t="n">
-        <v>-137.42</v>
+        <v>-165.01</v>
       </c>
       <c r="L40" t="n">
-        <v>212.46</v>
+        <v>249.18</v>
       </c>
     </row>
     <row r="41">
@@ -1762,25 +1762,25 @@
         <v>3.35</v>
       </c>
       <c r="F41" t="n">
-        <v>11.53</v>
+        <v>11.1</v>
       </c>
       <c r="G41" t="n">
-        <v>143.9</v>
+        <v>157.1</v>
       </c>
       <c r="H41" t="n">
-        <v>15</v>
+        <v>6.1</v>
       </c>
       <c r="I41" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>250.78</v>
+        <v>301.16</v>
       </c>
       <c r="K41" t="n">
-        <v>71.56</v>
+        <v>54.69</v>
       </c>
       <c r="L41" t="n">
-        <v>260.79</v>
+        <v>306.09</v>
       </c>
     </row>
     <row r="42">
@@ -1804,25 +1804,25 @@
         <v>3.51</v>
       </c>
       <c r="F42" t="n">
-        <v>11.06</v>
+        <v>10.71</v>
       </c>
       <c r="G42" t="n">
-        <v>160.1</v>
+        <v>147.6</v>
       </c>
       <c r="H42" t="n">
-        <v>11.6</v>
+        <v>14.2</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>125.32</v>
+        <v>150.05</v>
       </c>
       <c r="K42" t="n">
-        <v>-201.66</v>
+        <v>-231.04</v>
       </c>
       <c r="L42" t="n">
-        <v>237.43</v>
+        <v>275.49</v>
       </c>
     </row>
     <row r="43">
@@ -1846,25 +1846,25 @@
         <v>3.6</v>
       </c>
       <c r="F43" t="n">
-        <v>11.33</v>
+        <v>10.97</v>
       </c>
       <c r="G43" t="n">
-        <v>140.8</v>
+        <v>153.1</v>
       </c>
       <c r="H43" t="n">
-        <v>15.4</v>
+        <v>4.6</v>
       </c>
       <c r="I43" t="n">
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-23.03</v>
+        <v>-14.17</v>
       </c>
       <c r="K43" t="n">
-        <v>-217.39</v>
+        <v>-259.12</v>
       </c>
       <c r="L43" t="n">
-        <v>218.61</v>
+        <v>259.51</v>
       </c>
     </row>
     <row r="44">
@@ -1888,25 +1888,25 @@
         <v>3.62</v>
       </c>
       <c r="F44" t="n">
-        <v>11.4</v>
+        <v>12.41</v>
       </c>
       <c r="G44" t="n">
-        <v>164.3</v>
+        <v>154.6</v>
       </c>
       <c r="H44" t="n">
-        <v>14.4</v>
+        <v>16.3</v>
       </c>
       <c r="I44" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>56.02</v>
+        <v>73.37</v>
       </c>
       <c r="K44" t="n">
-        <v>-38.21</v>
+        <v>-50.44</v>
       </c>
       <c r="L44" t="n">
-        <v>67.81</v>
+        <v>89.04000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1930,25 +1930,25 @@
         <v>4.09</v>
       </c>
       <c r="F45" t="n">
-        <v>10.84</v>
+        <v>10.65</v>
       </c>
       <c r="G45" t="n">
-        <v>153.9</v>
+        <v>143.2</v>
       </c>
       <c r="H45" t="n">
-        <v>12.6</v>
+        <v>11.1</v>
       </c>
       <c r="I45" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>71.01000000000001</v>
+        <v>84.47</v>
       </c>
       <c r="K45" t="n">
-        <v>10.82</v>
+        <v>11.97</v>
       </c>
       <c r="L45" t="n">
-        <v>71.83</v>
+        <v>85.31</v>
       </c>
     </row>
     <row r="46">
@@ -1972,25 +1972,25 @@
         <v>4.11</v>
       </c>
       <c r="F46" t="n">
-        <v>11.79</v>
+        <v>11.05</v>
       </c>
       <c r="G46" t="n">
-        <v>141</v>
+        <v>162.2</v>
       </c>
       <c r="H46" t="n">
-        <v>8.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="I46" t="n">
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-24.77</v>
+        <v>-27.68</v>
       </c>
       <c r="K46" t="n">
-        <v>-52.06</v>
+        <v>-59.62</v>
       </c>
       <c r="L46" t="n">
-        <v>57.65</v>
+        <v>65.73</v>
       </c>
     </row>
     <row r="47">
@@ -2014,25 +2014,25 @@
         <v>4</v>
       </c>
       <c r="F47" t="n">
-        <v>11.62</v>
+        <v>11.92</v>
       </c>
       <c r="G47" t="n">
-        <v>151.2</v>
+        <v>158.9</v>
       </c>
       <c r="H47" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>8.1</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>70.77</v>
+        <v>71.7</v>
       </c>
       <c r="L47" t="n">
-        <v>71.23999999999999</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="48">
@@ -2056,25 +2056,25 @@
         <v>3.56</v>
       </c>
       <c r="F48" t="n">
-        <v>11.19</v>
+        <v>13.11</v>
       </c>
       <c r="G48" t="n">
-        <v>161.7</v>
+        <v>150.2</v>
       </c>
       <c r="H48" t="n">
-        <v>16.8</v>
+        <v>15</v>
       </c>
       <c r="I48" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>39.24</v>
+        <v>48.51</v>
       </c>
       <c r="K48" t="n">
-        <v>-55.81</v>
+        <v>-68.04000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>68.23</v>
+        <v>83.56999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2098,25 +2098,25 @@
         <v>3.41</v>
       </c>
       <c r="F49" t="n">
-        <v>11.05</v>
+        <v>13.11</v>
       </c>
       <c r="G49" t="n">
-        <v>163</v>
+        <v>147.5</v>
       </c>
       <c r="H49" t="n">
-        <v>10.3</v>
+        <v>15.7</v>
       </c>
       <c r="I49" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-47.9</v>
+        <v>-64.39</v>
       </c>
       <c r="K49" t="n">
-        <v>1.68</v>
+        <v>-3.66</v>
       </c>
       <c r="L49" t="n">
-        <v>47.92</v>
+        <v>64.48999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2140,25 +2140,25 @@
         <v>2.95</v>
       </c>
       <c r="F50" t="n">
-        <v>11.87</v>
+        <v>11.56</v>
       </c>
       <c r="G50" t="n">
-        <v>145</v>
+        <v>163.9</v>
       </c>
       <c r="H50" t="n">
-        <v>16.7</v>
+        <v>6.7</v>
       </c>
       <c r="I50" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>70.86</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>-36.54</v>
+        <v>-59.69</v>
       </c>
       <c r="L50" t="n">
-        <v>79.73</v>
+        <v>106.42</v>
       </c>
     </row>
     <row r="51">
@@ -2182,25 +2182,25 @@
         <v>4.11</v>
       </c>
       <c r="F51" t="n">
-        <v>11.39</v>
+        <v>13.11</v>
       </c>
       <c r="G51" t="n">
-        <v>152.2</v>
+        <v>154.3</v>
       </c>
       <c r="H51" t="n">
-        <v>16.4</v>
+        <v>10.2</v>
       </c>
       <c r="I51" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-19.21</v>
+        <v>-17.85</v>
       </c>
       <c r="K51" t="n">
-        <v>139.65</v>
+        <v>159.38</v>
       </c>
       <c r="L51" t="n">
-        <v>140.96</v>
+        <v>160.37</v>
       </c>
     </row>
     <row r="52">
@@ -2224,25 +2224,25 @@
         <v>3.9</v>
       </c>
       <c r="F52" t="n">
-        <v>11.73</v>
+        <v>13.11</v>
       </c>
       <c r="G52" t="n">
-        <v>157.6</v>
+        <v>161.1</v>
       </c>
       <c r="H52" t="n">
-        <v>17.9</v>
+        <v>13</v>
       </c>
       <c r="I52" t="n">
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>30.92</v>
+        <v>37.4</v>
       </c>
       <c r="K52" t="n">
-        <v>-141.36</v>
+        <v>-167.23</v>
       </c>
       <c r="L52" t="n">
-        <v>144.7</v>
+        <v>171.36</v>
       </c>
     </row>
     <row r="53">
@@ -2266,25 +2266,25 @@
         <v>4.04</v>
       </c>
       <c r="F53" t="n">
-        <v>11.46</v>
+        <v>13.11</v>
       </c>
       <c r="G53" t="n">
-        <v>161.2</v>
+        <v>155.8</v>
       </c>
       <c r="H53" t="n">
-        <v>11.8</v>
+        <v>14.7</v>
       </c>
       <c r="I53" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>17.23</v>
+        <v>72.37</v>
       </c>
       <c r="K53" t="n">
-        <v>37.48</v>
+        <v>-33.72</v>
       </c>
       <c r="L53" t="n">
-        <v>41.25</v>
+        <v>79.84</v>
       </c>
     </row>
     <row r="54">
@@ -2308,25 +2308,25 @@
         <v>3.8</v>
       </c>
       <c r="F54" t="n">
-        <v>11.17</v>
+        <v>12.88</v>
       </c>
       <c r="G54" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H54" t="n">
-        <v>13.8</v>
+        <v>6.1</v>
       </c>
       <c r="I54" t="n">
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>136.19</v>
+        <v>159.56</v>
       </c>
       <c r="K54" t="n">
-        <v>-84.79000000000001</v>
+        <v>-116.59</v>
       </c>
       <c r="L54" t="n">
-        <v>160.43</v>
+        <v>197.62</v>
       </c>
     </row>
     <row r="55">
@@ -2350,25 +2350,25 @@
         <v>4.47</v>
       </c>
       <c r="F55" t="n">
-        <v>11.22</v>
+        <v>13.11</v>
       </c>
       <c r="G55" t="n">
-        <v>163.4</v>
+        <v>150.9</v>
       </c>
       <c r="H55" t="n">
-        <v>6.4</v>
+        <v>15.9</v>
       </c>
       <c r="I55" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>-33.1</v>
+        <v>-18.48</v>
       </c>
       <c r="K55" t="n">
-        <v>150.09</v>
+        <v>155.65</v>
       </c>
       <c r="L55" t="n">
-        <v>153.7</v>
+        <v>156.74</v>
       </c>
     </row>
     <row r="56">
@@ -2392,25 +2392,25 @@
         <v>3.83</v>
       </c>
       <c r="F56" t="n">
-        <v>11.31</v>
+        <v>10.9</v>
       </c>
       <c r="G56" t="n">
-        <v>165.8</v>
+        <v>152.6</v>
       </c>
       <c r="H56" t="n">
-        <v>9.300000000000001</v>
+        <v>17</v>
       </c>
       <c r="I56" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>91.94</v>
+        <v>107.13</v>
       </c>
       <c r="K56" t="n">
-        <v>-388.92</v>
+        <v>-408.69</v>
       </c>
       <c r="L56" t="n">
-        <v>399.64</v>
+        <v>422.5</v>
       </c>
     </row>
     <row r="57">
@@ -2434,25 +2434,25 @@
         <v>4.13</v>
       </c>
       <c r="F57" t="n">
-        <v>11.6</v>
+        <v>12.15</v>
       </c>
       <c r="G57" t="n">
-        <v>166.1</v>
+        <v>158.4</v>
       </c>
       <c r="H57" t="n">
-        <v>17.6</v>
+        <v>17.2</v>
       </c>
       <c r="I57" t="n">
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>28.83</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>166.9</v>
+        <v>168.36</v>
       </c>
       <c r="L57" t="n">
-        <v>169.38</v>
+        <v>190.8</v>
       </c>
     </row>
     <row r="58">
@@ -2476,25 +2476,25 @@
         <v>4.03</v>
       </c>
       <c r="F58" t="n">
-        <v>11.11</v>
+        <v>13.11</v>
       </c>
       <c r="G58" t="n">
-        <v>155.4</v>
+        <v>148.6</v>
       </c>
       <c r="H58" t="n">
-        <v>17.6</v>
+        <v>11.8</v>
       </c>
       <c r="I58" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>104.08</v>
+        <v>139.72</v>
       </c>
       <c r="K58" t="n">
-        <v>-115.82</v>
+        <v>-164.24</v>
       </c>
       <c r="L58" t="n">
-        <v>155.71</v>
+        <v>215.63</v>
       </c>
     </row>
     <row r="59">
@@ -2518,25 +2518,25 @@
         <v>3.33</v>
       </c>
       <c r="F59" t="n">
-        <v>11.43</v>
+        <v>9</v>
       </c>
       <c r="G59" t="n">
-        <v>142</v>
+        <v>155.2</v>
       </c>
       <c r="H59" t="n">
-        <v>13.1</v>
+        <v>5.1</v>
       </c>
       <c r="I59" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>8.42</v>
+        <v>9.67</v>
       </c>
       <c r="K59" t="n">
-        <v>53.72</v>
+        <v>58.95</v>
       </c>
       <c r="L59" t="n">
-        <v>54.38</v>
+        <v>59.74</v>
       </c>
     </row>
     <row r="60">
@@ -2560,25 +2560,25 @@
         <v>3.97</v>
       </c>
       <c r="F60" t="n">
-        <v>11.49</v>
+        <v>11.45</v>
       </c>
       <c r="G60" t="n">
-        <v>156.7</v>
+        <v>156.2</v>
       </c>
       <c r="H60" t="n">
-        <v>9.300000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="I60" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-50.83</v>
+        <v>-60.23</v>
       </c>
       <c r="K60" t="n">
-        <v>-49.09</v>
+        <v>-59.55</v>
       </c>
       <c r="L60" t="n">
-        <v>70.66</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="61">
@@ -2602,25 +2602,25 @@
         <v>3.71</v>
       </c>
       <c r="F61" t="n">
-        <v>11.85</v>
+        <v>10.99</v>
       </c>
       <c r="G61" t="n">
-        <v>152.1</v>
+        <v>163.6</v>
       </c>
       <c r="H61" t="n">
-        <v>8.800000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="I61" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>47.55</v>
+        <v>58.08</v>
       </c>
       <c r="K61" t="n">
-        <v>-32.08</v>
+        <v>-40.57</v>
       </c>
       <c r="L61" t="n">
-        <v>57.36</v>
+        <v>70.84999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2644,25 +2644,25 @@
         <v>3.56</v>
       </c>
       <c r="F62" t="n">
-        <v>11.25</v>
+        <v>10.66</v>
       </c>
       <c r="G62" t="n">
-        <v>147.4</v>
+        <v>151.5</v>
       </c>
       <c r="H62" t="n">
-        <v>10.3</v>
+        <v>7.8</v>
       </c>
       <c r="I62" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>15.63</v>
+        <v>18.11</v>
       </c>
       <c r="K62" t="n">
-        <v>-121.16</v>
+        <v>-135.98</v>
       </c>
       <c r="L62" t="n">
-        <v>122.16</v>
+        <v>137.18</v>
       </c>
     </row>
     <row r="63">
@@ -2686,25 +2686,25 @@
         <v>4.05</v>
       </c>
       <c r="F63" t="n">
-        <v>11.15</v>
+        <v>13.11</v>
       </c>
       <c r="G63" t="n">
-        <v>162</v>
+        <v>149.5</v>
       </c>
       <c r="H63" t="n">
-        <v>20.1</v>
+        <v>15.1</v>
       </c>
       <c r="I63" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-53.26</v>
+        <v>-59.32</v>
       </c>
       <c r="K63" t="n">
-        <v>-88.13</v>
+        <v>-103.32</v>
       </c>
       <c r="L63" t="n">
-        <v>102.98</v>
+        <v>119.14</v>
       </c>
     </row>
     <row r="64">
@@ -2728,25 +2728,25 @@
         <v>4.41</v>
       </c>
       <c r="F64" t="n">
-        <v>11.62</v>
+        <v>10.35</v>
       </c>
       <c r="G64" t="n">
-        <v>143.7</v>
+        <v>158.9</v>
       </c>
       <c r="H64" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="I64" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-31.6</v>
+        <v>-32.94</v>
       </c>
       <c r="K64" t="n">
-        <v>87.55</v>
+        <v>89.44</v>
       </c>
       <c r="L64" t="n">
-        <v>93.08</v>
+        <v>95.31</v>
       </c>
     </row>
     <row r="65">
@@ -2770,25 +2770,25 @@
         <v>4.53</v>
       </c>
       <c r="F65" t="n">
-        <v>10.51</v>
+        <v>13.11</v>
       </c>
       <c r="G65" t="n">
-        <v>150</v>
+        <v>136.7</v>
       </c>
       <c r="H65" t="n">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I65" t="n">
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.18</v>
+        <v>18.26</v>
       </c>
       <c r="K65" t="n">
-        <v>95.79000000000001</v>
+        <v>105.42</v>
       </c>
       <c r="L65" t="n">
-        <v>95.81999999999999</v>
+        <v>106.99</v>
       </c>
     </row>
     <row r="66">
@@ -2812,25 +2812,25 @@
         <v>3.75</v>
       </c>
       <c r="F66" t="n">
-        <v>11.47</v>
+        <v>13.11</v>
       </c>
       <c r="G66" t="n">
-        <v>165.6</v>
+        <v>156</v>
       </c>
       <c r="H66" t="n">
-        <v>15</v>
+        <v>16.9</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.05</v>
+        <v>11.33</v>
       </c>
       <c r="K66" t="n">
-        <v>-76.72</v>
+        <v>-93.17</v>
       </c>
       <c r="L66" t="n">
-        <v>76.78</v>
+        <v>93.86</v>
       </c>
     </row>
     <row r="67">
@@ -2854,25 +2854,25 @@
         <v>3.18</v>
       </c>
       <c r="F67" t="n">
-        <v>10.86</v>
+        <v>9.31</v>
       </c>
       <c r="G67" t="n">
-        <v>150.2</v>
+        <v>143.8</v>
       </c>
       <c r="H67" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>52.54</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>-73.16</v>
+        <v>-90.81999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>90.06999999999999</v>
+        <v>112.56</v>
       </c>
     </row>
     <row r="68">
@@ -2896,25 +2896,25 @@
         <v>4.14</v>
       </c>
       <c r="F68" t="n">
-        <v>11.48</v>
+        <v>10.22</v>
       </c>
       <c r="G68" t="n">
-        <v>165.5</v>
+        <v>156.1</v>
       </c>
       <c r="H68" t="n">
-        <v>5.3</v>
+        <v>16.9</v>
       </c>
       <c r="I68" t="n">
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>95.54000000000001</v>
+        <v>109.49</v>
       </c>
       <c r="K68" t="n">
-        <v>-112.99</v>
+        <v>-136.94</v>
       </c>
       <c r="L68" t="n">
-        <v>147.97</v>
+        <v>175.33</v>
       </c>
     </row>
     <row r="69">
@@ -2938,25 +2938,25 @@
         <v>3.58</v>
       </c>
       <c r="F69" t="n">
-        <v>12.07</v>
+        <v>13.11</v>
       </c>
       <c r="G69" t="n">
-        <v>149.5</v>
+        <v>168</v>
       </c>
       <c r="H69" t="n">
-        <v>11.7</v>
+        <v>8.9</v>
       </c>
       <c r="I69" t="n">
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>69.65000000000001</v>
+        <v>72.37</v>
       </c>
       <c r="K69" t="n">
-        <v>-95.26000000000001</v>
+        <v>-141.12</v>
       </c>
       <c r="L69" t="n">
-        <v>118.01</v>
+        <v>158.59</v>
       </c>
     </row>
     <row r="70">
@@ -2980,25 +2980,25 @@
         <v>3.87</v>
       </c>
       <c r="F70" t="n">
-        <v>11.66</v>
+        <v>11.55</v>
       </c>
       <c r="G70" t="n">
-        <v>149.5</v>
+        <v>159.8</v>
       </c>
       <c r="H70" t="n">
-        <v>9.9</v>
+        <v>8.9</v>
       </c>
       <c r="I70" t="n">
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>104.87</v>
+        <v>116.6</v>
       </c>
       <c r="K70" t="n">
-        <v>-104.44</v>
+        <v>-137.54</v>
       </c>
       <c r="L70" t="n">
-        <v>148</v>
+        <v>180.31</v>
       </c>
     </row>
     <row r="71">
@@ -3022,25 +3022,25 @@
         <v>3.71</v>
       </c>
       <c r="F71" t="n">
-        <v>11.07</v>
+        <v>13.11</v>
       </c>
       <c r="G71" t="n">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="H71" t="n">
-        <v>5.6</v>
+        <v>12.7</v>
       </c>
       <c r="I71" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>190.64</v>
+        <v>245.51</v>
       </c>
       <c r="K71" t="n">
-        <v>-274.34</v>
+        <v>-349.59</v>
       </c>
       <c r="L71" t="n">
-        <v>334.08</v>
+        <v>427.19</v>
       </c>
     </row>
     <row r="72">
@@ -3064,25 +3064,25 @@
         <v>3.55</v>
       </c>
       <c r="F72" t="n">
-        <v>11.43</v>
+        <v>11.26</v>
       </c>
       <c r="G72" t="n">
-        <v>162</v>
+        <v>155.1</v>
       </c>
       <c r="H72" t="n">
-        <v>11.4</v>
+        <v>15.2</v>
       </c>
       <c r="I72" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-130.64</v>
+        <v>-131.39</v>
       </c>
       <c r="K72" t="n">
-        <v>-183.16</v>
+        <v>-239.26</v>
       </c>
       <c r="L72" t="n">
-        <v>224.98</v>
+        <v>272.97</v>
       </c>
     </row>
     <row r="73">
@@ -3106,25 +3106,25 @@
         <v>3.52</v>
       </c>
       <c r="F73" t="n">
-        <v>11</v>
+        <v>11.9</v>
       </c>
       <c r="G73" t="n">
-        <v>149.3</v>
+        <v>146.4</v>
       </c>
       <c r="H73" t="n">
-        <v>10.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-84.58</v>
+        <v>-65</v>
       </c>
       <c r="K73" t="n">
-        <v>-159.57</v>
+        <v>-205.09</v>
       </c>
       <c r="L73" t="n">
-        <v>180.6</v>
+        <v>215.14</v>
       </c>
     </row>
     <row r="74">
@@ -3148,25 +3148,25 @@
         <v>4.07</v>
       </c>
       <c r="F74" t="n">
-        <v>11.68</v>
+        <v>10.8</v>
       </c>
       <c r="G74" t="n">
-        <v>163.5</v>
+        <v>160</v>
       </c>
       <c r="H74" t="n">
-        <v>6.7</v>
+        <v>15.9</v>
       </c>
       <c r="I74" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>65.92</v>
+        <v>77.06</v>
       </c>
       <c r="K74" t="n">
-        <v>-8.550000000000001</v>
+        <v>-10.95</v>
       </c>
       <c r="L74" t="n">
-        <v>66.47</v>
+        <v>77.83</v>
       </c>
     </row>
     <row r="75">
@@ -3190,25 +3190,25 @@
         <v>3.98</v>
       </c>
       <c r="F75" t="n">
-        <v>11.59</v>
+        <v>12.81</v>
       </c>
       <c r="G75" t="n">
-        <v>154.9</v>
+        <v>158.2</v>
       </c>
       <c r="H75" t="n">
-        <v>13.2</v>
+        <v>11.6</v>
       </c>
       <c r="I75" t="n">
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-41</v>
+        <v>-47.69</v>
       </c>
       <c r="K75" t="n">
-        <v>-45.9</v>
+        <v>-55.57</v>
       </c>
       <c r="L75" t="n">
-        <v>61.54</v>
+        <v>73.23</v>
       </c>
     </row>
     <row r="76">
@@ -3232,25 +3232,25 @@
         <v>3.7</v>
       </c>
       <c r="F76" t="n">
-        <v>11.51</v>
+        <v>10.97</v>
       </c>
       <c r="G76" t="n">
-        <v>159.7</v>
+        <v>156.6</v>
       </c>
       <c r="H76" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>64.33</v>
+        <v>66.97</v>
       </c>
       <c r="K76" t="n">
-        <v>34.66</v>
+        <v>34.92</v>
       </c>
       <c r="L76" t="n">
-        <v>73.06999999999999</v>
+        <v>75.52</v>
       </c>
     </row>
     <row r="77">
@@ -3274,25 +3274,25 @@
         <v>3.84</v>
       </c>
       <c r="F77" t="n">
-        <v>11.59</v>
+        <v>12.48</v>
       </c>
       <c r="G77" t="n">
-        <v>147.9</v>
+        <v>158.2</v>
       </c>
       <c r="H77" t="n">
-        <v>5.3</v>
+        <v>8.1</v>
       </c>
       <c r="I77" t="n">
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-56.75</v>
+        <v>-66.26000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-33.98</v>
+        <v>-44.83</v>
       </c>
       <c r="L77" t="n">
-        <v>66.15000000000001</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78">
@@ -3316,25 +3316,25 @@
         <v>4.91</v>
       </c>
       <c r="F78" t="n">
-        <v>11.54</v>
+        <v>13.11</v>
       </c>
       <c r="G78" t="n">
-        <v>148.1</v>
+        <v>157.4</v>
       </c>
       <c r="H78" t="n">
-        <v>15.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I78" t="n">
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-35.1</v>
+        <v>-41.92</v>
       </c>
       <c r="K78" t="n">
-        <v>53.36</v>
+        <v>57.98</v>
       </c>
       <c r="L78" t="n">
-        <v>63.87</v>
+        <v>71.54000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3358,25 +3358,25 @@
         <v>3.33</v>
       </c>
       <c r="F79" t="n">
-        <v>11.16</v>
+        <v>10.07</v>
       </c>
       <c r="G79" t="n">
-        <v>158.3</v>
+        <v>149.7</v>
       </c>
       <c r="H79" t="n">
-        <v>13</v>
+        <v>13.3</v>
       </c>
       <c r="I79" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-52.23</v>
+        <v>-64.54000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>-28.73</v>
+        <v>-40.15</v>
       </c>
       <c r="L79" t="n">
-        <v>59.61</v>
+        <v>76.01000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3400,25 +3400,25 @@
         <v>3.75</v>
       </c>
       <c r="F80" t="n">
-        <v>12.04</v>
+        <v>11.06</v>
       </c>
       <c r="G80" t="n">
         <v>167.3</v>
       </c>
       <c r="H80" t="n">
-        <v>9.300000000000001</v>
+        <v>17.8</v>
       </c>
       <c r="I80" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J80" t="n">
-        <v>-40.18</v>
+        <v>-37.29</v>
       </c>
       <c r="K80" t="n">
-        <v>-77.22</v>
+        <v>-96.22</v>
       </c>
       <c r="L80" t="n">
-        <v>87.05</v>
+        <v>103.19</v>
       </c>
     </row>
     <row r="81">
@@ -3442,25 +3442,25 @@
         <v>3.98</v>
       </c>
       <c r="F81" t="n">
-        <v>11.43</v>
+        <v>12.43</v>
       </c>
       <c r="G81" t="n">
-        <v>157.3</v>
+        <v>155.1</v>
       </c>
       <c r="H81" t="n">
-        <v>9.800000000000001</v>
+        <v>12.8</v>
       </c>
       <c r="I81" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>18.39</v>
+        <v>28.21</v>
       </c>
       <c r="K81" t="n">
-        <v>-84.8</v>
+        <v>-107.97</v>
       </c>
       <c r="L81" t="n">
-        <v>86.78</v>
+        <v>111.59</v>
       </c>
     </row>
     <row r="82">
@@ -3484,25 +3484,25 @@
         <v>3.6</v>
       </c>
       <c r="F82" t="n">
-        <v>11.82</v>
+        <v>10.52</v>
       </c>
       <c r="G82" t="n">
-        <v>148.6</v>
+        <v>162.9</v>
       </c>
       <c r="H82" t="n">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>126.62</v>
+        <v>151.94</v>
       </c>
       <c r="K82" t="n">
-        <v>36.92</v>
+        <v>33.03</v>
       </c>
       <c r="L82" t="n">
-        <v>131.9</v>
+        <v>155.49</v>
       </c>
     </row>
     <row r="83">
@@ -3526,25 +3526,25 @@
         <v>3.58</v>
       </c>
       <c r="F83" t="n">
-        <v>11.62</v>
+        <v>10.21</v>
       </c>
       <c r="G83" t="n">
-        <v>156.3</v>
+        <v>158.8</v>
       </c>
       <c r="H83" t="n">
-        <v>19.3</v>
+        <v>12.3</v>
       </c>
       <c r="I83" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>75.05</v>
+        <v>79.36</v>
       </c>
       <c r="K83" t="n">
-        <v>-82.38</v>
+        <v>-114.24</v>
       </c>
       <c r="L83" t="n">
-        <v>111.44</v>
+        <v>139.1</v>
       </c>
     </row>
     <row r="84">
@@ -3568,25 +3568,25 @@
         <v>3.55</v>
       </c>
       <c r="F84" t="n">
-        <v>12.02</v>
+        <v>13.11</v>
       </c>
       <c r="G84" t="n">
-        <v>145</v>
+        <v>166.8</v>
       </c>
       <c r="H84" t="n">
-        <v>15.5</v>
+        <v>6.6</v>
       </c>
       <c r="I84" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-63.81</v>
+        <v>-61.21</v>
       </c>
       <c r="K84" t="n">
-        <v>-99.17</v>
+        <v>-141.58</v>
       </c>
       <c r="L84" t="n">
-        <v>117.92</v>
+        <v>154.25</v>
       </c>
     </row>
     <row r="85">
@@ -3610,25 +3610,25 @@
         <v>4.57</v>
       </c>
       <c r="F85" t="n">
-        <v>11.3</v>
+        <v>13.11</v>
       </c>
       <c r="G85" t="n">
-        <v>163.6</v>
+        <v>157.3</v>
       </c>
       <c r="H85" t="n">
-        <v>16.3</v>
+        <v>13.6</v>
       </c>
       <c r="I85" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>96.22</v>
+        <v>53.64</v>
       </c>
       <c r="K85" t="n">
-        <v>-81.56</v>
+        <v>150.79</v>
       </c>
       <c r="L85" t="n">
-        <v>126.14</v>
+        <v>160.05</v>
       </c>
     </row>
     <row r="86">
@@ -3649,28 +3649,28 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.95</v>
+        <v>4.49</v>
       </c>
       <c r="F86" t="n">
-        <v>10.87</v>
+        <v>12.1</v>
       </c>
       <c r="G86" t="n">
-        <v>152.5</v>
+        <v>167.7</v>
       </c>
       <c r="H86" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="I86" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>251.78</v>
+        <v>349.16</v>
       </c>
       <c r="K86" t="n">
-        <v>32.86</v>
+        <v>-11.75</v>
       </c>
       <c r="L86" t="n">
-        <v>253.91</v>
+        <v>349.36</v>
       </c>
     </row>
     <row r="87">
@@ -3691,28 +3691,28 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.56</v>
+        <v>3.58</v>
       </c>
       <c r="F87" t="n">
-        <v>11.4</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G87" t="n">
-        <v>143.9</v>
+        <v>149.9</v>
       </c>
       <c r="H87" t="n">
-        <v>6.2</v>
+        <v>9.5</v>
       </c>
       <c r="I87" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-168.48</v>
+        <v>188.13</v>
       </c>
       <c r="K87" t="n">
-        <v>-108.76</v>
+        <v>-158.72</v>
       </c>
       <c r="L87" t="n">
-        <v>200.53</v>
+        <v>246.14</v>
       </c>
     </row>
     <row r="88">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.23</v>
+        <v>3.65</v>
       </c>
       <c r="F88" t="n">
-        <v>11.77</v>
+        <v>13.11</v>
       </c>
       <c r="G88" t="n">
-        <v>150.7</v>
+        <v>156.7</v>
       </c>
       <c r="H88" t="n">
-        <v>8.5</v>
+        <v>11.1</v>
       </c>
       <c r="I88" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>65.61</v>
+        <v>360.99</v>
       </c>
       <c r="K88" t="n">
-        <v>235.66</v>
+        <v>32.83</v>
       </c>
       <c r="L88" t="n">
-        <v>244.62</v>
+        <v>362.48</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-24.xlsx
+++ b/output/2025-05-24.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-72.40000000000001</v>
+        <v>-73.81999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-21.68</v>
+        <v>-22.11</v>
       </c>
       <c r="L14" t="n">
-        <v>75.58</v>
+        <v>77.06</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-49.89</v>
+        <v>-48.78</v>
       </c>
       <c r="K15" t="n">
-        <v>53.48</v>
+        <v>52.29</v>
       </c>
       <c r="L15" t="n">
-        <v>73.14</v>
+        <v>71.51000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>5.11</v>
+        <v>4.66</v>
       </c>
       <c r="K16" t="n">
-        <v>85.59</v>
+        <v>78.08</v>
       </c>
       <c r="L16" t="n">
-        <v>85.73999999999999</v>
+        <v>78.22</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>43.33</v>
+        <v>41.4</v>
       </c>
       <c r="K17" t="n">
-        <v>67.16</v>
+        <v>64.17</v>
       </c>
       <c r="L17" t="n">
-        <v>79.92</v>
+        <v>76.37</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>47.28</v>
+        <v>45.21</v>
       </c>
       <c r="K18" t="n">
-        <v>68.01000000000001</v>
+        <v>65.03</v>
       </c>
       <c r="L18" t="n">
-        <v>82.83</v>
+        <v>79.20999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>48.08</v>
+        <v>45.01</v>
       </c>
       <c r="K19" t="n">
-        <v>45.05</v>
+        <v>42.17</v>
       </c>
       <c r="L19" t="n">
-        <v>65.89</v>
+        <v>61.68</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>25.98</v>
+        <v>26.49</v>
       </c>
       <c r="K20" t="n">
-        <v>-97.68000000000001</v>
+        <v>-99.59</v>
       </c>
       <c r="L20" t="n">
-        <v>101.08</v>
+        <v>103.06</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>146.76</v>
+        <v>152.36</v>
       </c>
       <c r="K21" t="n">
-        <v>10.26</v>
+        <v>10.65</v>
       </c>
       <c r="L21" t="n">
-        <v>147.12</v>
+        <v>152.74</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>-10.06</v>
+        <v>-9.42</v>
       </c>
       <c r="K22" t="n">
-        <v>-91.31</v>
+        <v>-85.48999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>91.87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>126.98</v>
+        <v>115.93</v>
       </c>
       <c r="K23" t="n">
-        <v>-92.87</v>
+        <v>-84.8</v>
       </c>
       <c r="L23" t="n">
-        <v>157.32</v>
+        <v>143.64</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.66</v>
+        <v>-1.72</v>
       </c>
       <c r="K24" t="n">
-        <v>-175.22</v>
+        <v>-181.98</v>
       </c>
       <c r="L24" t="n">
-        <v>175.23</v>
+        <v>181.99</v>
       </c>
     </row>
     <row r="25">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>226.44</v>
+        <v>235.61</v>
       </c>
       <c r="K26" t="n">
-        <v>-126.19</v>
+        <v>-131.3</v>
       </c>
       <c r="L26" t="n">
-        <v>259.22</v>
+        <v>269.73</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>295.73</v>
+        <v>283.78</v>
       </c>
       <c r="K27" t="n">
-        <v>19.36</v>
+        <v>18.58</v>
       </c>
       <c r="L27" t="n">
-        <v>296.37</v>
+        <v>284.39</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="K28" t="n">
-        <v>200.6</v>
+        <v>196.51</v>
       </c>
       <c r="L28" t="n">
-        <v>200.62</v>
+        <v>196.52</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-37.07</v>
+        <v>-35.47</v>
       </c>
       <c r="K29" t="n">
-        <v>38.9</v>
+        <v>37.21</v>
       </c>
       <c r="L29" t="n">
-        <v>53.73</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>66.20999999999999</v>
+        <v>66.06</v>
       </c>
       <c r="K30" t="n">
-        <v>59.85</v>
+        <v>59.72</v>
       </c>
       <c r="L30" t="n">
-        <v>89.25</v>
+        <v>89.05</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-45.84</v>
+        <v>-44.9</v>
       </c>
       <c r="K31" t="n">
-        <v>-82.53</v>
+        <v>-80.83</v>
       </c>
       <c r="L31" t="n">
-        <v>94.41</v>
+        <v>92.45999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>-46.09</v>
+        <v>-42.08</v>
       </c>
       <c r="K32" t="n">
-        <v>-59.9</v>
+        <v>-54.69</v>
       </c>
       <c r="L32" t="n">
-        <v>75.58</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-70.12</v>
+        <v>-65.54000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>-42.81</v>
+        <v>-40.02</v>
       </c>
       <c r="L33" t="n">
-        <v>82.16</v>
+        <v>76.79000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-106.29</v>
+        <v>-109.64</v>
       </c>
       <c r="K34" t="n">
-        <v>-18.03</v>
+        <v>-18.59</v>
       </c>
       <c r="L34" t="n">
-        <v>107.81</v>
+        <v>111.2</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>-61.51</v>
+        <v>-56.16</v>
       </c>
       <c r="K35" t="n">
-        <v>-81.48999999999999</v>
+        <v>-74.40000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>102.1</v>
+        <v>93.22</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>-37.03</v>
+        <v>-34.65</v>
       </c>
       <c r="K36" t="n">
-        <v>-145.64</v>
+        <v>-136.28</v>
       </c>
       <c r="L36" t="n">
-        <v>150.27</v>
+        <v>140.61</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>85.03</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>-164.91</v>
+        <v>-171.14</v>
       </c>
       <c r="L37" t="n">
-        <v>185.54</v>
+        <v>192.55</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>16.26</v>
+        <v>16.89</v>
       </c>
       <c r="K38" t="n">
-        <v>-114.03</v>
+        <v>-118.42</v>
       </c>
       <c r="L38" t="n">
-        <v>115.19</v>
+        <v>119.62</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-142.89</v>
+        <v>-145.71</v>
       </c>
       <c r="K39" t="n">
-        <v>27.62</v>
+        <v>28.17</v>
       </c>
       <c r="L39" t="n">
-        <v>145.54</v>
+        <v>148.41</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>186.72</v>
+        <v>179.03</v>
       </c>
       <c r="K40" t="n">
-        <v>-165.01</v>
+        <v>-158.22</v>
       </c>
       <c r="L40" t="n">
-        <v>249.18</v>
+        <v>238.93</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>301.16</v>
+        <v>301.43</v>
       </c>
       <c r="K41" t="n">
-        <v>54.69</v>
+        <v>54.74</v>
       </c>
       <c r="L41" t="n">
-        <v>306.09</v>
+        <v>306.36</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>150.05</v>
+        <v>147.32</v>
       </c>
       <c r="K42" t="n">
-        <v>-231.04</v>
+        <v>-226.83</v>
       </c>
       <c r="L42" t="n">
-        <v>275.49</v>
+        <v>270.47</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-14.17</v>
+        <v>-13.62</v>
       </c>
       <c r="K43" t="n">
-        <v>-259.12</v>
+        <v>-249.05</v>
       </c>
       <c r="L43" t="n">
-        <v>259.51</v>
+        <v>249.43</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>73.37</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>-50.44</v>
+        <v>-51.34</v>
       </c>
       <c r="L44" t="n">
-        <v>89.04000000000001</v>
+        <v>90.62</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>84.47</v>
+        <v>87.36</v>
       </c>
       <c r="K45" t="n">
-        <v>11.97</v>
+        <v>12.38</v>
       </c>
       <c r="L45" t="n">
-        <v>85.31</v>
+        <v>88.23999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-27.68</v>
+        <v>-27.56</v>
       </c>
       <c r="K46" t="n">
-        <v>-59.62</v>
+        <v>-59.37</v>
       </c>
       <c r="L46" t="n">
-        <v>65.73</v>
+        <v>65.45999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>9.710000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="K47" t="n">
-        <v>71.7</v>
+        <v>65.23</v>
       </c>
       <c r="L47" t="n">
-        <v>72.36</v>
+        <v>65.83</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>48.51</v>
+        <v>47.45</v>
       </c>
       <c r="K48" t="n">
-        <v>-68.04000000000001</v>
+        <v>-66.55</v>
       </c>
       <c r="L48" t="n">
-        <v>83.56999999999999</v>
+        <v>81.73</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-64.39</v>
+        <v>-61.65</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.66</v>
+        <v>-3.5</v>
       </c>
       <c r="L49" t="n">
-        <v>64.48999999999999</v>
+        <v>61.75</v>
       </c>
     </row>
     <row r="50">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-17.85</v>
+        <v>-18.51</v>
       </c>
       <c r="K51" t="n">
-        <v>159.38</v>
+        <v>165.27</v>
       </c>
       <c r="L51" t="n">
-        <v>160.37</v>
+        <v>166.3</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>37.4</v>
+        <v>36.59</v>
       </c>
       <c r="K52" t="n">
-        <v>-167.23</v>
+        <v>-163.64</v>
       </c>
       <c r="L52" t="n">
-        <v>171.36</v>
+        <v>167.68</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>72.37</v>
+        <v>73.86</v>
       </c>
       <c r="K53" t="n">
-        <v>-33.72</v>
+        <v>-34.41</v>
       </c>
       <c r="L53" t="n">
-        <v>79.84</v>
+        <v>81.48</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>159.56</v>
+        <v>153.01</v>
       </c>
       <c r="K54" t="n">
-        <v>-116.59</v>
+        <v>-111.81</v>
       </c>
       <c r="L54" t="n">
-        <v>197.62</v>
+        <v>189.5</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>-18.48</v>
+        <v>-16.89</v>
       </c>
       <c r="K55" t="n">
-        <v>155.65</v>
+        <v>142.31</v>
       </c>
       <c r="L55" t="n">
-        <v>156.74</v>
+        <v>143.31</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>107.13</v>
+        <v>103.14</v>
       </c>
       <c r="K56" t="n">
-        <v>-408.69</v>
+        <v>-393.49</v>
       </c>
       <c r="L56" t="n">
-        <v>422.5</v>
+        <v>406.78</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>89.79000000000001</v>
+        <v>86.62</v>
       </c>
       <c r="K57" t="n">
-        <v>168.36</v>
+        <v>162.42</v>
       </c>
       <c r="L57" t="n">
-        <v>190.8</v>
+        <v>184.07</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>139.72</v>
+        <v>145.97</v>
       </c>
       <c r="K58" t="n">
-        <v>-164.24</v>
+        <v>-171.58</v>
       </c>
       <c r="L58" t="n">
-        <v>215.63</v>
+        <v>225.28</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>9.67</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>58.95</v>
+        <v>57.73</v>
       </c>
       <c r="L59" t="n">
-        <v>59.74</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-60.23</v>
+        <v>-60.02</v>
       </c>
       <c r="K60" t="n">
-        <v>-59.55</v>
+        <v>-59.35</v>
       </c>
       <c r="L60" t="n">
-        <v>84.7</v>
+        <v>84.41</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>58.08</v>
+        <v>59.08</v>
       </c>
       <c r="K61" t="n">
-        <v>-40.57</v>
+        <v>-41.28</v>
       </c>
       <c r="L61" t="n">
-        <v>70.84999999999999</v>
+        <v>72.06999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>18.11</v>
+        <v>18.44</v>
       </c>
       <c r="K62" t="n">
-        <v>-135.98</v>
+        <v>-138.43</v>
       </c>
       <c r="L62" t="n">
-        <v>137.18</v>
+        <v>139.65</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-59.32</v>
+        <v>-59.1</v>
       </c>
       <c r="K63" t="n">
-        <v>-103.32</v>
+        <v>-102.92</v>
       </c>
       <c r="L63" t="n">
-        <v>119.14</v>
+        <v>118.68</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-32.94</v>
+        <v>-29.92</v>
       </c>
       <c r="K64" t="n">
-        <v>89.44</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>95.31</v>
+        <v>86.55</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>18.26</v>
+        <v>16.63</v>
       </c>
       <c r="K65" t="n">
-        <v>105.42</v>
+        <v>96.05</v>
       </c>
       <c r="L65" t="n">
-        <v>106.99</v>
+        <v>97.48</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>11.33</v>
+        <v>10.34</v>
       </c>
       <c r="K66" t="n">
-        <v>-93.17</v>
+        <v>-85</v>
       </c>
       <c r="L66" t="n">
-        <v>93.86</v>
+        <v>85.62</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>66.48999999999999</v>
+        <v>69.05</v>
       </c>
       <c r="K67" t="n">
-        <v>-90.81999999999999</v>
+        <v>-94.31</v>
       </c>
       <c r="L67" t="n">
-        <v>112.56</v>
+        <v>116.88</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>109.49</v>
+        <v>100.08</v>
       </c>
       <c r="K68" t="n">
-        <v>-136.94</v>
+        <v>-125.16</v>
       </c>
       <c r="L68" t="n">
-        <v>175.33</v>
+        <v>160.25</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>72.37</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>-141.12</v>
+        <v>-141.18</v>
       </c>
       <c r="L69" t="n">
-        <v>158.59</v>
+        <v>158.66</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>116.6</v>
+        <v>111.82</v>
       </c>
       <c r="K70" t="n">
-        <v>-137.54</v>
+        <v>-131.9</v>
       </c>
       <c r="L70" t="n">
-        <v>180.31</v>
+        <v>172.92</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>245.51</v>
+        <v>246.43</v>
       </c>
       <c r="K71" t="n">
-        <v>-349.59</v>
+        <v>-350.91</v>
       </c>
       <c r="L71" t="n">
-        <v>427.19</v>
+        <v>428.8</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-131.39</v>
+        <v>-131.72</v>
       </c>
       <c r="K72" t="n">
-        <v>-239.26</v>
+        <v>-239.87</v>
       </c>
       <c r="L72" t="n">
-        <v>272.97</v>
+        <v>273.66</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-65</v>
+        <v>-60.99</v>
       </c>
       <c r="K73" t="n">
-        <v>-205.09</v>
+        <v>-192.44</v>
       </c>
       <c r="L73" t="n">
-        <v>215.14</v>
+        <v>201.87</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>77.06</v>
+        <v>73.56</v>
       </c>
       <c r="K74" t="n">
-        <v>-10.95</v>
+        <v>-10.45</v>
       </c>
       <c r="L74" t="n">
-        <v>77.83</v>
+        <v>74.29000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-47.69</v>
+        <v>-49.35</v>
       </c>
       <c r="K75" t="n">
-        <v>-55.57</v>
+        <v>-57.5</v>
       </c>
       <c r="L75" t="n">
-        <v>73.23</v>
+        <v>75.77</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>66.97</v>
+        <v>62.56</v>
       </c>
       <c r="K76" t="n">
-        <v>34.92</v>
+        <v>32.61</v>
       </c>
       <c r="L76" t="n">
-        <v>75.52</v>
+        <v>70.55</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-66.26000000000001</v>
+        <v>-66.06999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>-44.83</v>
+        <v>-44.7</v>
       </c>
       <c r="L77" t="n">
-        <v>80</v>
+        <v>79.77</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-41.92</v>
+        <v>-41.6</v>
       </c>
       <c r="K78" t="n">
-        <v>57.98</v>
+        <v>57.54</v>
       </c>
       <c r="L78" t="n">
-        <v>71.54000000000001</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-64.54000000000001</v>
+        <v>-65.78</v>
       </c>
       <c r="K79" t="n">
-        <v>-40.15</v>
+        <v>-40.92</v>
       </c>
       <c r="L79" t="n">
-        <v>76.01000000000001</v>
+        <v>77.47</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>28</v>
       </c>
       <c r="J80" t="n">
-        <v>-37.29</v>
+        <v>-34.01</v>
       </c>
       <c r="K80" t="n">
-        <v>-96.22</v>
+        <v>-87.77</v>
       </c>
       <c r="L80" t="n">
-        <v>103.19</v>
+        <v>94.13</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>28.21</v>
+        <v>26.37</v>
       </c>
       <c r="K81" t="n">
-        <v>-107.97</v>
+        <v>-100.95</v>
       </c>
       <c r="L81" t="n">
-        <v>111.59</v>
+        <v>104.34</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>151.94</v>
+        <v>157.68</v>
       </c>
       <c r="K82" t="n">
-        <v>33.03</v>
+        <v>34.28</v>
       </c>
       <c r="L82" t="n">
-        <v>155.49</v>
+        <v>161.36</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>79.36</v>
+        <v>77.77</v>
       </c>
       <c r="K83" t="n">
-        <v>-114.24</v>
+        <v>-111.96</v>
       </c>
       <c r="L83" t="n">
-        <v>139.1</v>
+        <v>136.32</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-61.21</v>
+        <v>-58.68</v>
       </c>
       <c r="K84" t="n">
-        <v>-141.58</v>
+        <v>-135.73</v>
       </c>
       <c r="L84" t="n">
-        <v>154.25</v>
+        <v>147.87</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>53.64</v>
+        <v>54.05</v>
       </c>
       <c r="K85" t="n">
-        <v>150.79</v>
+        <v>151.94</v>
       </c>
       <c r="L85" t="n">
-        <v>160.05</v>
+        <v>161.27</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>349.16</v>
+        <v>361.32</v>
       </c>
       <c r="K86" t="n">
-        <v>-11.75</v>
+        <v>-12.16</v>
       </c>
       <c r="L86" t="n">
-        <v>349.36</v>
+        <v>361.53</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>188.13</v>
+        <v>195.91</v>
       </c>
       <c r="K87" t="n">
-        <v>-158.72</v>
+        <v>-165.28</v>
       </c>
       <c r="L87" t="n">
-        <v>246.14</v>
+        <v>256.32</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>360.99</v>
+        <v>339.07</v>
       </c>
       <c r="K88" t="n">
-        <v>32.83</v>
+        <v>30.84</v>
       </c>
       <c r="L88" t="n">
-        <v>362.48</v>
+        <v>340.47</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-24.xlsx
+++ b/output/2025-05-24.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>7.6</v>
+        <v>8.17</v>
       </c>
       <c r="G14" t="n">
-        <v>157.4</v>
+        <v>158.4</v>
       </c>
       <c r="H14" t="n">
-        <v>8.4</v>
+        <v>38.3</v>
       </c>
       <c r="I14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-73.81999999999999</v>
+        <v>-22.83</v>
       </c>
       <c r="K14" t="n">
-        <v>-22.11</v>
+        <v>-62.15</v>
       </c>
       <c r="L14" t="n">
-        <v>77.06</v>
+        <v>66.20999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:47:54</t>
+          <t>04:46:40</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.64</v>
+        <v>3.99</v>
       </c>
       <c r="F15" t="n">
-        <v>11.02</v>
+        <v>7.68</v>
       </c>
       <c r="G15" t="n">
-        <v>164.9</v>
+        <v>160.6</v>
       </c>
       <c r="H15" t="n">
-        <v>9.199999999999999</v>
+        <v>45.7</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J15" t="n">
-        <v>-48.78</v>
+        <v>-62.6</v>
       </c>
       <c r="K15" t="n">
-        <v>52.29</v>
+        <v>-19.13</v>
       </c>
       <c r="L15" t="n">
-        <v>71.51000000000001</v>
+        <v>65.45999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:49:53</t>
+          <t>04:49:08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.41</v>
+        <v>3.65</v>
       </c>
       <c r="F16" t="n">
-        <v>8.35</v>
+        <v>11.63</v>
       </c>
       <c r="G16" t="n">
-        <v>157.1</v>
+        <v>165.7</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>16.2</v>
       </c>
       <c r="I16" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>4.66</v>
+        <v>55.92</v>
       </c>
       <c r="K16" t="n">
-        <v>78.08</v>
+        <v>-31.14</v>
       </c>
       <c r="L16" t="n">
-        <v>78.22</v>
+        <v>64.01000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:53:51</t>
+          <t>04:53:08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.86</v>
+        <v>3.07</v>
       </c>
       <c r="F17" t="n">
-        <v>9.27</v>
+        <v>12.44</v>
       </c>
       <c r="G17" t="n">
-        <v>162.4</v>
+        <v>152</v>
       </c>
       <c r="H17" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J17" t="n">
-        <v>41.4</v>
+        <v>-22.71</v>
       </c>
       <c r="K17" t="n">
-        <v>64.17</v>
+        <v>-71.44</v>
       </c>
       <c r="L17" t="n">
-        <v>76.37</v>
+        <v>74.95999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:55:45</t>
+          <t>04:54:07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.68</v>
+        <v>3.03</v>
       </c>
       <c r="F18" t="n">
-        <v>11.18</v>
+        <v>7.73</v>
       </c>
       <c r="G18" t="n">
-        <v>164.8</v>
+        <v>150.3</v>
       </c>
       <c r="H18" t="n">
-        <v>7.6</v>
+        <v>34.4</v>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>45.21</v>
+        <v>15.41</v>
       </c>
       <c r="K18" t="n">
-        <v>65.03</v>
+        <v>-51.62</v>
       </c>
       <c r="L18" t="n">
-        <v>79.20999999999999</v>
+        <v>53.87</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:57:31</t>
+          <t>04:55:14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="F19" t="n">
-        <v>8.720000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="G19" t="n">
-        <v>147.2</v>
+        <v>143.7</v>
       </c>
       <c r="H19" t="n">
-        <v>12</v>
+        <v>2.4</v>
       </c>
       <c r="I19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>45.01</v>
+        <v>-18.57</v>
       </c>
       <c r="K19" t="n">
-        <v>42.17</v>
+        <v>-61.16</v>
       </c>
       <c r="L19" t="n">
-        <v>61.68</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:01:30</t>
+          <t>05:00:04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.2</v>
+        <v>3.37</v>
       </c>
       <c r="F20" t="n">
-        <v>11.47</v>
+        <v>10.54</v>
       </c>
       <c r="G20" t="n">
-        <v>171</v>
+        <v>172.6</v>
       </c>
       <c r="H20" t="n">
-        <v>9.6</v>
+        <v>53.7</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>26.49</v>
+        <v>22.98</v>
       </c>
       <c r="K20" t="n">
-        <v>-99.59</v>
+        <v>118.03</v>
       </c>
       <c r="L20" t="n">
-        <v>103.06</v>
+        <v>120.25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:02:18</t>
+          <t>05:01:48</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="F21" t="n">
-        <v>9.220000000000001</v>
+        <v>10.61</v>
       </c>
       <c r="G21" t="n">
-        <v>163.9</v>
+        <v>158.8</v>
       </c>
       <c r="H21" t="n">
-        <v>11.8</v>
+        <v>40.1</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>152.36</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>10.65</v>
+        <v>-47.8</v>
       </c>
       <c r="L21" t="n">
-        <v>152.74</v>
+        <v>99.73999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:04:24</t>
+          <t>05:02:59</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.22</v>
+        <v>3.73</v>
       </c>
       <c r="F22" t="n">
-        <v>9.630000000000001</v>
+        <v>11.11</v>
       </c>
       <c r="G22" t="n">
-        <v>135.1</v>
+        <v>156</v>
       </c>
       <c r="H22" t="n">
-        <v>6.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-9.42</v>
+        <v>-97.34999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-85.48999999999999</v>
+        <v>-38.5</v>
       </c>
       <c r="L22" t="n">
-        <v>86</v>
+        <v>104.69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:09:34</t>
+          <t>05:07:17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="F23" t="n">
-        <v>8.25</v>
+        <v>8.48</v>
       </c>
       <c r="G23" t="n">
-        <v>144.5</v>
+        <v>154.5</v>
       </c>
       <c r="H23" t="n">
-        <v>10.1</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>115.93</v>
+        <v>-36.73</v>
       </c>
       <c r="K23" t="n">
-        <v>-84.8</v>
+        <v>-155.8</v>
       </c>
       <c r="L23" t="n">
-        <v>143.64</v>
+        <v>160.07</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:12:06</t>
+          <t>05:09:13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.33</v>
+        <v>3.48</v>
       </c>
       <c r="F24" t="n">
-        <v>10.56</v>
+        <v>9.34</v>
       </c>
       <c r="G24" t="n">
-        <v>151.9</v>
+        <v>161.6</v>
       </c>
       <c r="H24" t="n">
-        <v>19.3</v>
+        <v>25.6</v>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.72</v>
+        <v>162.9</v>
       </c>
       <c r="K24" t="n">
-        <v>-181.98</v>
+        <v>-23.14</v>
       </c>
       <c r="L24" t="n">
-        <v>181.99</v>
+        <v>164.53</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:13:49</t>
+          <t>05:11:41</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.72</v>
+        <v>3.75</v>
       </c>
       <c r="F25" t="n">
-        <v>8.94</v>
+        <v>7.58</v>
       </c>
       <c r="G25" t="n">
-        <v>147.3</v>
+        <v>144.4</v>
       </c>
       <c r="H25" t="n">
-        <v>11.1</v>
+        <v>33</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>92.86</v>
+        <v>-22.07</v>
       </c>
       <c r="K25" t="n">
-        <v>67.92</v>
+        <v>-239.12</v>
       </c>
       <c r="L25" t="n">
-        <v>115.04</v>
+        <v>240.14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:17:27</t>
+          <t>05:15:34</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.48</v>
+        <v>4.02</v>
       </c>
       <c r="F26" t="n">
-        <v>12.66</v>
+        <v>13.11</v>
       </c>
       <c r="G26" t="n">
-        <v>158.3</v>
+        <v>162.2</v>
       </c>
       <c r="H26" t="n">
-        <v>13.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>235.61</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-131.3</v>
+        <v>-317.49</v>
       </c>
       <c r="L26" t="n">
-        <v>269.73</v>
+        <v>327.19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:19:02</t>
+          <t>05:17:29</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="F27" t="n">
-        <v>13.11</v>
+        <v>10.2</v>
       </c>
       <c r="G27" t="n">
-        <v>157.9</v>
+        <v>143.6</v>
       </c>
       <c r="H27" t="n">
-        <v>17.4</v>
+        <v>26.3</v>
       </c>
       <c r="I27" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>283.78</v>
+        <v>187.9</v>
       </c>
       <c r="K27" t="n">
-        <v>18.58</v>
+        <v>-98.92</v>
       </c>
       <c r="L27" t="n">
-        <v>284.39</v>
+        <v>212.35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:20:29</t>
+          <t>05:19:46</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.51</v>
+        <v>3.69</v>
       </c>
       <c r="F28" t="n">
-        <v>8.369999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>151.2</v>
+        <v>147.2</v>
       </c>
       <c r="H28" t="n">
-        <v>18.3</v>
+        <v>36.6</v>
       </c>
       <c r="I28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>2.5</v>
+        <v>154.27</v>
       </c>
       <c r="K28" t="n">
-        <v>196.51</v>
+        <v>-165.21</v>
       </c>
       <c r="L28" t="n">
-        <v>196.52</v>
+        <v>226.04</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:32:23</t>
+          <t>05:29:29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.59</v>
+        <v>4.13</v>
       </c>
       <c r="F29" t="n">
-        <v>11.27</v>
+        <v>13.11</v>
       </c>
       <c r="G29" t="n">
-        <v>147.9</v>
+        <v>154.2</v>
       </c>
       <c r="H29" t="n">
-        <v>10.1</v>
+        <v>21.5</v>
       </c>
       <c r="I29" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-35.47</v>
+        <v>-25.76</v>
       </c>
       <c r="K29" t="n">
-        <v>37.21</v>
+        <v>-78.98999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>51.41</v>
+        <v>83.09</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:33:54</t>
+          <t>05:31:08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="F30" t="n">
-        <v>11.44</v>
+        <v>10.92</v>
       </c>
       <c r="G30" t="n">
-        <v>155.9</v>
+        <v>160</v>
       </c>
       <c r="H30" t="n">
-        <v>13.4</v>
+        <v>37.2</v>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J30" t="n">
-        <v>66.06</v>
+        <v>-65.45999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>59.72</v>
+        <v>-11.89</v>
       </c>
       <c r="L30" t="n">
-        <v>89.05</v>
+        <v>66.53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:34:47</t>
+          <t>05:33:12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.29</v>
+        <v>3.31</v>
       </c>
       <c r="F31" t="n">
-        <v>11.19</v>
+        <v>7.17</v>
       </c>
       <c r="G31" t="n">
-        <v>146.1</v>
+        <v>168.1</v>
       </c>
       <c r="H31" t="n">
-        <v>8.1</v>
+        <v>29.3</v>
       </c>
       <c r="I31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-44.9</v>
+        <v>-49.38</v>
       </c>
       <c r="K31" t="n">
-        <v>-80.83</v>
+        <v>-37.39</v>
       </c>
       <c r="L31" t="n">
-        <v>92.45999999999999</v>
+        <v>61.94</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:40:09</t>
+          <t>05:36:55</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.14</v>
+        <v>3.89</v>
       </c>
       <c r="F32" t="n">
-        <v>12.24</v>
+        <v>12.04</v>
       </c>
       <c r="G32" t="n">
-        <v>153.5</v>
+        <v>162.5</v>
       </c>
       <c r="H32" t="n">
-        <v>8.6</v>
+        <v>64.7</v>
       </c>
       <c r="I32" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>-42.08</v>
+        <v>-68.16</v>
       </c>
       <c r="K32" t="n">
-        <v>-54.69</v>
+        <v>-60.2</v>
       </c>
       <c r="L32" t="n">
-        <v>69</v>
+        <v>90.94</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:42:46</t>
+          <t>05:39:05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="F33" t="n">
-        <v>9.210000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="G33" t="n">
-        <v>142.4</v>
+        <v>148.1</v>
       </c>
       <c r="H33" t="n">
-        <v>12.7</v>
+        <v>6.4</v>
       </c>
       <c r="I33" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>-65.54000000000001</v>
+        <v>61.8</v>
       </c>
       <c r="K33" t="n">
-        <v>-40.02</v>
+        <v>-56.08</v>
       </c>
       <c r="L33" t="n">
-        <v>76.79000000000001</v>
+        <v>83.45</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:43:46</t>
+          <t>05:40:10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.72</v>
+        <v>3.36</v>
       </c>
       <c r="F34" t="n">
-        <v>13.11</v>
+        <v>10.72</v>
       </c>
       <c r="G34" t="n">
-        <v>160.9</v>
+        <v>147.1</v>
       </c>
       <c r="H34" t="n">
-        <v>15.3</v>
+        <v>79.5</v>
       </c>
       <c r="I34" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-109.64</v>
+        <v>-55.27</v>
       </c>
       <c r="K34" t="n">
-        <v>-18.59</v>
+        <v>92.47</v>
       </c>
       <c r="L34" t="n">
-        <v>111.2</v>
+        <v>107.73</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:48:41</t>
+          <t>05:44:21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.27</v>
+        <v>2.99</v>
       </c>
       <c r="F35" t="n">
-        <v>10.07</v>
+        <v>9.98</v>
       </c>
       <c r="G35" t="n">
-        <v>146.4</v>
+        <v>165.8</v>
       </c>
       <c r="H35" t="n">
-        <v>7.9</v>
+        <v>29.2</v>
       </c>
       <c r="I35" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>-56.16</v>
+        <v>87.05</v>
       </c>
       <c r="K35" t="n">
-        <v>-74.40000000000001</v>
+        <v>-13.28</v>
       </c>
       <c r="L35" t="n">
-        <v>93.22</v>
+        <v>88.05</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:50:06</t>
+          <t>05:45:48</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.52</v>
+        <v>3.63</v>
       </c>
       <c r="F36" t="n">
-        <v>10.55</v>
+        <v>12.33</v>
       </c>
       <c r="G36" t="n">
-        <v>147.9</v>
+        <v>153.9</v>
       </c>
       <c r="H36" t="n">
-        <v>6.9</v>
+        <v>41.5</v>
       </c>
       <c r="I36" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-34.65</v>
+        <v>44.96</v>
       </c>
       <c r="K36" t="n">
-        <v>-136.28</v>
+        <v>-124.11</v>
       </c>
       <c r="L36" t="n">
-        <v>140.61</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:52:04</t>
+          <t>05:48:03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="F37" t="n">
-        <v>11.24</v>
+        <v>10.24</v>
       </c>
       <c r="G37" t="n">
-        <v>153.7</v>
+        <v>140.6</v>
       </c>
       <c r="H37" t="n">
-        <v>13.6</v>
+        <v>20.8</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J37" t="n">
-        <v>88.23999999999999</v>
+        <v>72.03</v>
       </c>
       <c r="K37" t="n">
-        <v>-171.14</v>
+        <v>-28.68</v>
       </c>
       <c r="L37" t="n">
-        <v>192.55</v>
+        <v>77.53</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:57:08</t>
+          <t>05:53:20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.01</v>
+        <v>3.53</v>
       </c>
       <c r="F38" t="n">
-        <v>5.89</v>
+        <v>12.92</v>
       </c>
       <c r="G38" t="n">
-        <v>149.9</v>
+        <v>155.3</v>
       </c>
       <c r="H38" t="n">
-        <v>9.5</v>
+        <v>32</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>16.89</v>
+        <v>-205.54</v>
       </c>
       <c r="K38" t="n">
-        <v>-118.42</v>
+        <v>-74.04000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>119.62</v>
+        <v>218.47</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:58:32</t>
+          <t>05:54:29</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.36</v>
+        <v>3.64</v>
       </c>
       <c r="F39" t="n">
-        <v>11.77</v>
+        <v>11.28</v>
       </c>
       <c r="G39" t="n">
-        <v>167.5</v>
+        <v>147.2</v>
       </c>
       <c r="H39" t="n">
-        <v>6.6</v>
+        <v>30.4</v>
       </c>
       <c r="I39" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J39" t="n">
-        <v>-145.71</v>
+        <v>44.84</v>
       </c>
       <c r="K39" t="n">
-        <v>28.17</v>
+        <v>173.73</v>
       </c>
       <c r="L39" t="n">
-        <v>148.41</v>
+        <v>179.42</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:59:59</t>
+          <t>05:56:14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.71</v>
+        <v>3.34</v>
       </c>
       <c r="F40" t="n">
-        <v>10.53</v>
+        <v>13.11</v>
       </c>
       <c r="G40" t="n">
-        <v>149.5</v>
+        <v>140.7</v>
       </c>
       <c r="H40" t="n">
-        <v>16.1</v>
+        <v>56.3</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>179.03</v>
+        <v>86.08</v>
       </c>
       <c r="K40" t="n">
-        <v>-158.22</v>
+        <v>-202.01</v>
       </c>
       <c r="L40" t="n">
-        <v>238.93</v>
+        <v>219.59</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:04:38</t>
+          <t>06:00:56</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.35</v>
+        <v>3.23</v>
       </c>
       <c r="F41" t="n">
-        <v>11.1</v>
+        <v>10.48</v>
       </c>
       <c r="G41" t="n">
-        <v>157.1</v>
+        <v>161</v>
       </c>
       <c r="H41" t="n">
-        <v>6.1</v>
+        <v>14</v>
       </c>
       <c r="I41" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J41" t="n">
-        <v>301.43</v>
+        <v>-41.3</v>
       </c>
       <c r="K41" t="n">
-        <v>54.74</v>
+        <v>-211.23</v>
       </c>
       <c r="L41" t="n">
-        <v>306.36</v>
+        <v>215.23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:06:40</t>
+          <t>06:02:29</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.51</v>
+        <v>3.39</v>
       </c>
       <c r="F42" t="n">
-        <v>10.71</v>
+        <v>11.06</v>
       </c>
       <c r="G42" t="n">
-        <v>147.6</v>
+        <v>142.6</v>
       </c>
       <c r="H42" t="n">
-        <v>14.2</v>
+        <v>39</v>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>147.32</v>
+        <v>215.13</v>
       </c>
       <c r="K42" t="n">
-        <v>-226.83</v>
+        <v>-37.26</v>
       </c>
       <c r="L42" t="n">
-        <v>270.47</v>
+        <v>218.34</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:08:15</t>
+          <t>06:04:28</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="F43" t="n">
-        <v>10.97</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>153.1</v>
+        <v>152.7</v>
       </c>
       <c r="H43" t="n">
-        <v>4.6</v>
+        <v>35.4</v>
       </c>
       <c r="I43" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>-13.62</v>
+        <v>221.59</v>
       </c>
       <c r="K43" t="n">
-        <v>-249.05</v>
+        <v>123.47</v>
       </c>
       <c r="L43" t="n">
-        <v>249.43</v>
+        <v>253.66</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:18:42</t>
+          <t>06:18:13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.62</v>
+        <v>2.77</v>
       </c>
       <c r="F44" t="n">
-        <v>12.41</v>
+        <v>7.47</v>
       </c>
       <c r="G44" t="n">
-        <v>154.6</v>
+        <v>158</v>
       </c>
       <c r="H44" t="n">
-        <v>16.3</v>
+        <v>48.1</v>
       </c>
       <c r="I44" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>74.68000000000001</v>
+        <v>-47</v>
       </c>
       <c r="K44" t="n">
-        <v>-51.34</v>
+        <v>-0.25</v>
       </c>
       <c r="L44" t="n">
-        <v>90.62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:21:14</t>
+          <t>06:19:46</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.09</v>
+        <v>3.69</v>
       </c>
       <c r="F45" t="n">
-        <v>10.65</v>
+        <v>9.67</v>
       </c>
       <c r="G45" t="n">
-        <v>143.2</v>
+        <v>155.3</v>
       </c>
       <c r="H45" t="n">
-        <v>11.1</v>
+        <v>48.4</v>
       </c>
       <c r="I45" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>87.36</v>
+        <v>-34.86</v>
       </c>
       <c r="K45" t="n">
-        <v>12.38</v>
+        <v>-56.61</v>
       </c>
       <c r="L45" t="n">
-        <v>88.23999999999999</v>
+        <v>66.48</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:22:10</t>
+          <t>06:20:57</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.11</v>
+        <v>4.32</v>
       </c>
       <c r="F46" t="n">
-        <v>11.05</v>
+        <v>9.01</v>
       </c>
       <c r="G46" t="n">
-        <v>162.2</v>
+        <v>155.2</v>
       </c>
       <c r="H46" t="n">
-        <v>4.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J46" t="n">
-        <v>-27.56</v>
+        <v>46.69</v>
       </c>
       <c r="K46" t="n">
-        <v>-59.37</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>65.45999999999999</v>
+        <v>85.48</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:26:38</t>
+          <t>06:24:02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4</v>
+        <v>3.81</v>
       </c>
       <c r="F47" t="n">
-        <v>11.92</v>
+        <v>13.06</v>
       </c>
       <c r="G47" t="n">
-        <v>158.9</v>
+        <v>152.8</v>
       </c>
       <c r="H47" t="n">
-        <v>9.800000000000001</v>
+        <v>17.9</v>
       </c>
       <c r="I47" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>8.83</v>
+        <v>18.65</v>
       </c>
       <c r="K47" t="n">
-        <v>65.23</v>
+        <v>-64.81999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>65.83</v>
+        <v>67.45</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:28:36</t>
+          <t>06:25:52</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.56</v>
+        <v>3.14</v>
       </c>
       <c r="F48" t="n">
-        <v>13.11</v>
+        <v>10.43</v>
       </c>
       <c r="G48" t="n">
-        <v>150.2</v>
+        <v>144.8</v>
       </c>
       <c r="H48" t="n">
-        <v>15</v>
+        <v>37.7</v>
       </c>
       <c r="I48" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>47.45</v>
+        <v>62.59</v>
       </c>
       <c r="K48" t="n">
-        <v>-66.55</v>
+        <v>43.6</v>
       </c>
       <c r="L48" t="n">
-        <v>81.73</v>
+        <v>76.28</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:30:36</t>
+          <t>06:27:04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="F49" t="n">
-        <v>13.11</v>
+        <v>11.57</v>
       </c>
       <c r="G49" t="n">
-        <v>147.5</v>
+        <v>163.4</v>
       </c>
       <c r="H49" t="n">
-        <v>15.7</v>
+        <v>20.6</v>
       </c>
       <c r="I49" t="n">
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-61.65</v>
+        <v>63.1</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.5</v>
+        <v>19.1</v>
       </c>
       <c r="L49" t="n">
-        <v>61.75</v>
+        <v>65.92</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:36:49</t>
+          <t>06:32:55</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.95</v>
+        <v>4.28</v>
       </c>
       <c r="F50" t="n">
-        <v>11.56</v>
+        <v>13.11</v>
       </c>
       <c r="G50" t="n">
-        <v>163.9</v>
+        <v>160.2</v>
       </c>
       <c r="H50" t="n">
-        <v>6.7</v>
+        <v>54.8</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J50" t="n">
-        <v>88.09999999999999</v>
+        <v>50.57</v>
       </c>
       <c r="K50" t="n">
-        <v>-59.69</v>
+        <v>126.46</v>
       </c>
       <c r="L50" t="n">
-        <v>106.42</v>
+        <v>136.19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:37:48</t>
+          <t>06:35:02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.11</v>
+        <v>3.89</v>
       </c>
       <c r="F51" t="n">
-        <v>13.11</v>
+        <v>12.44</v>
       </c>
       <c r="G51" t="n">
-        <v>154.3</v>
+        <v>154.9</v>
       </c>
       <c r="H51" t="n">
-        <v>10.2</v>
+        <v>44.2</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>-18.51</v>
+        <v>82.47</v>
       </c>
       <c r="K51" t="n">
-        <v>165.27</v>
+        <v>103.86</v>
       </c>
       <c r="L51" t="n">
-        <v>166.3</v>
+        <v>132.62</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:40:00</t>
+          <t>06:36:47</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="F52" t="n">
-        <v>13.11</v>
+        <v>10.29</v>
       </c>
       <c r="G52" t="n">
-        <v>161.1</v>
+        <v>155.9</v>
       </c>
       <c r="H52" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="I52" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J52" t="n">
-        <v>36.59</v>
+        <v>-180.28</v>
       </c>
       <c r="K52" t="n">
-        <v>-163.64</v>
+        <v>0.96</v>
       </c>
       <c r="L52" t="n">
-        <v>167.68</v>
+        <v>180.29</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:44:41</t>
+          <t>06:41:03</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.04</v>
+        <v>3.72</v>
       </c>
       <c r="F53" t="n">
-        <v>13.11</v>
+        <v>10.55</v>
       </c>
       <c r="G53" t="n">
-        <v>155.8</v>
+        <v>149.4</v>
       </c>
       <c r="H53" t="n">
-        <v>14.7</v>
+        <v>31.7</v>
       </c>
       <c r="I53" t="n">
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>73.86</v>
+        <v>-99.06</v>
       </c>
       <c r="K53" t="n">
-        <v>-34.41</v>
+        <v>-201.89</v>
       </c>
       <c r="L53" t="n">
-        <v>81.48</v>
+        <v>224.88</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:47:02</t>
+          <t>06:43:25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.8</v>
+        <v>3.43</v>
       </c>
       <c r="F54" t="n">
-        <v>12.88</v>
+        <v>10.15</v>
       </c>
       <c r="G54" t="n">
-        <v>150</v>
+        <v>144.1</v>
       </c>
       <c r="H54" t="n">
-        <v>6.1</v>
+        <v>55.5</v>
       </c>
       <c r="I54" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>153.01</v>
+        <v>-201.91</v>
       </c>
       <c r="K54" t="n">
-        <v>-111.81</v>
+        <v>-63.05</v>
       </c>
       <c r="L54" t="n">
-        <v>189.5</v>
+        <v>211.53</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:47:38</t>
+          <t>06:45:43</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.47</v>
+        <v>4.23</v>
       </c>
       <c r="F55" t="n">
         <v>13.11</v>
       </c>
       <c r="G55" t="n">
-        <v>150.9</v>
+        <v>145.3</v>
       </c>
       <c r="H55" t="n">
-        <v>15.9</v>
+        <v>13.9</v>
       </c>
       <c r="I55" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>-16.89</v>
+        <v>139.23</v>
       </c>
       <c r="K55" t="n">
-        <v>142.31</v>
+        <v>-115.65</v>
       </c>
       <c r="L55" t="n">
-        <v>143.31</v>
+        <v>181</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:52:15</t>
+          <t>06:50:40</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.83</v>
+        <v>4.18</v>
       </c>
       <c r="F56" t="n">
-        <v>10.9</v>
+        <v>11.11</v>
       </c>
       <c r="G56" t="n">
-        <v>152.6</v>
+        <v>145.6</v>
       </c>
       <c r="H56" t="n">
-        <v>17</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>103.14</v>
+        <v>-78.90000000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>-393.49</v>
+        <v>-197.41</v>
       </c>
       <c r="L56" t="n">
-        <v>406.78</v>
+        <v>212.59</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:53:06</t>
+          <t>06:52:07</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.13</v>
+        <v>3.6</v>
       </c>
       <c r="F57" t="n">
-        <v>12.15</v>
+        <v>11.24</v>
       </c>
       <c r="G57" t="n">
-        <v>158.4</v>
+        <v>165.2</v>
       </c>
       <c r="H57" t="n">
-        <v>17.2</v>
+        <v>56.8</v>
       </c>
       <c r="I57" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>86.62</v>
+        <v>-40.68</v>
       </c>
       <c r="K57" t="n">
-        <v>162.42</v>
+        <v>-194.82</v>
       </c>
       <c r="L57" t="n">
-        <v>184.07</v>
+        <v>199.03</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:54:47</t>
+          <t>06:54:36</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.03</v>
+        <v>3.64</v>
       </c>
       <c r="F58" t="n">
-        <v>13.11</v>
+        <v>12.89</v>
       </c>
       <c r="G58" t="n">
-        <v>148.6</v>
+        <v>147</v>
       </c>
       <c r="H58" t="n">
-        <v>11.8</v>
+        <v>43.2</v>
       </c>
       <c r="I58" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>145.97</v>
+        <v>199.72</v>
       </c>
       <c r="K58" t="n">
-        <v>-171.58</v>
+        <v>157.06</v>
       </c>
       <c r="L58" t="n">
-        <v>225.28</v>
+        <v>254.08</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:05:15</t>
+          <t>07:03:21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.33</v>
+        <v>4.55</v>
       </c>
       <c r="F59" t="n">
-        <v>9</v>
+        <v>13.11</v>
       </c>
       <c r="G59" t="n">
-        <v>155.2</v>
+        <v>161.2</v>
       </c>
       <c r="H59" t="n">
-        <v>5.1</v>
+        <v>46.9</v>
       </c>
       <c r="I59" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>9.470000000000001</v>
+        <v>28.6</v>
       </c>
       <c r="K59" t="n">
-        <v>57.73</v>
+        <v>-89.38</v>
       </c>
       <c r="L59" t="n">
-        <v>58.5</v>
+        <v>93.84</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:07:12</t>
+          <t>07:05:35</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.97</v>
+        <v>4.17</v>
       </c>
       <c r="F60" t="n">
-        <v>11.45</v>
+        <v>13.11</v>
       </c>
       <c r="G60" t="n">
-        <v>156.2</v>
+        <v>136.5</v>
       </c>
       <c r="H60" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-60.02</v>
+        <v>42.69</v>
       </c>
       <c r="K60" t="n">
-        <v>-59.35</v>
+        <v>-57.13</v>
       </c>
       <c r="L60" t="n">
-        <v>84.41</v>
+        <v>71.31999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:08:46</t>
+          <t>07:07:06</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.71</v>
+        <v>3.15</v>
       </c>
       <c r="F61" t="n">
-        <v>10.99</v>
+        <v>9.98</v>
       </c>
       <c r="G61" t="n">
-        <v>163.6</v>
+        <v>159.8</v>
       </c>
       <c r="H61" t="n">
-        <v>10.2</v>
+        <v>16</v>
       </c>
       <c r="I61" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>59.08</v>
+        <v>-23.64</v>
       </c>
       <c r="K61" t="n">
-        <v>-41.28</v>
+        <v>35.55</v>
       </c>
       <c r="L61" t="n">
-        <v>72.06999999999999</v>
+        <v>42.69</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:13:07</t>
+          <t>07:11:48</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2644,31 +2644,31 @@
         <v>3.56</v>
       </c>
       <c r="F62" t="n">
-        <v>10.66</v>
+        <v>12.55</v>
       </c>
       <c r="G62" t="n">
-        <v>151.5</v>
+        <v>147.9</v>
       </c>
       <c r="H62" t="n">
-        <v>7.8</v>
+        <v>58.7</v>
       </c>
       <c r="I62" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>18.44</v>
+        <v>-66.5</v>
       </c>
       <c r="K62" t="n">
-        <v>-138.43</v>
+        <v>-47.73</v>
       </c>
       <c r="L62" t="n">
-        <v>139.65</v>
+        <v>81.86</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:14:13</t>
+          <t>07:13:24</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.05</v>
+        <v>3.32</v>
       </c>
       <c r="F63" t="n">
-        <v>13.11</v>
+        <v>7.35</v>
       </c>
       <c r="G63" t="n">
-        <v>149.5</v>
+        <v>148.2</v>
       </c>
       <c r="H63" t="n">
-        <v>15.1</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-59.1</v>
+        <v>66.5</v>
       </c>
       <c r="K63" t="n">
-        <v>-102.92</v>
+        <v>-27.97</v>
       </c>
       <c r="L63" t="n">
-        <v>118.68</v>
+        <v>72.14</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:15:15</t>
+          <t>07:15:13</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.41</v>
+        <v>3.78</v>
       </c>
       <c r="F64" t="n">
-        <v>10.35</v>
+        <v>11.1</v>
       </c>
       <c r="G64" t="n">
-        <v>158.9</v>
+        <v>153.2</v>
       </c>
       <c r="H64" t="n">
-        <v>6</v>
+        <v>52.2</v>
       </c>
       <c r="I64" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-29.92</v>
+        <v>69.55</v>
       </c>
       <c r="K64" t="n">
-        <v>81.20999999999999</v>
+        <v>19.87</v>
       </c>
       <c r="L64" t="n">
-        <v>86.55</v>
+        <v>72.33</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:19:57</t>
+          <t>07:20:19</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.53</v>
+        <v>3.57</v>
       </c>
       <c r="F65" t="n">
         <v>13.11</v>
       </c>
       <c r="G65" t="n">
-        <v>136.7</v>
+        <v>168</v>
       </c>
       <c r="H65" t="n">
-        <v>9.199999999999999</v>
+        <v>41.1</v>
       </c>
       <c r="I65" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>16.63</v>
+        <v>-132.49</v>
       </c>
       <c r="K65" t="n">
-        <v>96.05</v>
+        <v>20.3</v>
       </c>
       <c r="L65" t="n">
-        <v>97.48</v>
+        <v>134.04</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:20:53</t>
+          <t>07:22:27</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.75</v>
+        <v>3.47</v>
       </c>
       <c r="F66" t="n">
-        <v>13.11</v>
+        <v>11.15</v>
       </c>
       <c r="G66" t="n">
-        <v>156</v>
+        <v>156.3</v>
       </c>
       <c r="H66" t="n">
-        <v>16.9</v>
+        <v>26.8</v>
       </c>
       <c r="I66" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>10.34</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>-85</v>
+        <v>-86.19</v>
       </c>
       <c r="L66" t="n">
-        <v>85.62</v>
+        <v>112.3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:22:18</t>
+          <t>07:24:14</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.18</v>
+        <v>3.41</v>
       </c>
       <c r="F67" t="n">
-        <v>9.31</v>
+        <v>10.59</v>
       </c>
       <c r="G67" t="n">
-        <v>143.8</v>
+        <v>153.6</v>
       </c>
       <c r="H67" t="n">
-        <v>9.199999999999999</v>
+        <v>48.3</v>
       </c>
       <c r="I67" t="n">
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>69.05</v>
+        <v>-107.33</v>
       </c>
       <c r="K67" t="n">
-        <v>-94.31</v>
+        <v>-22.82</v>
       </c>
       <c r="L67" t="n">
-        <v>116.88</v>
+        <v>109.73</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:26:36</t>
+          <t>07:28:26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
       <c r="F68" t="n">
-        <v>10.22</v>
+        <v>6.38</v>
       </c>
       <c r="G68" t="n">
-        <v>156.1</v>
+        <v>158</v>
       </c>
       <c r="H68" t="n">
-        <v>16.9</v>
+        <v>54.3</v>
       </c>
       <c r="I68" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>100.08</v>
+        <v>19</v>
       </c>
       <c r="K68" t="n">
-        <v>-125.16</v>
+        <v>-208.08</v>
       </c>
       <c r="L68" t="n">
-        <v>160.25</v>
+        <v>208.95</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:28:01</t>
+          <t>07:30:32</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.58</v>
+        <v>3.69</v>
       </c>
       <c r="F69" t="n">
-        <v>13.11</v>
+        <v>12.3</v>
       </c>
       <c r="G69" t="n">
-        <v>168</v>
+        <v>145.5</v>
       </c>
       <c r="H69" t="n">
-        <v>8.9</v>
+        <v>30.5</v>
       </c>
       <c r="I69" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>72.40000000000001</v>
+        <v>-173.69</v>
       </c>
       <c r="K69" t="n">
-        <v>-141.18</v>
+        <v>-29.04</v>
       </c>
       <c r="L69" t="n">
-        <v>158.66</v>
+        <v>176.1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:29:56</t>
+          <t>07:32:53</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.87</v>
+        <v>3.47</v>
       </c>
       <c r="F70" t="n">
-        <v>11.55</v>
+        <v>10.88</v>
       </c>
       <c r="G70" t="n">
-        <v>159.8</v>
+        <v>157.4</v>
       </c>
       <c r="H70" t="n">
-        <v>8.9</v>
+        <v>22.5</v>
       </c>
       <c r="I70" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>111.82</v>
+        <v>-179.31</v>
       </c>
       <c r="K70" t="n">
-        <v>-131.9</v>
+        <v>-69.06</v>
       </c>
       <c r="L70" t="n">
-        <v>172.92</v>
+        <v>192.15</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:34:05</t>
+          <t>07:38:06</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.71</v>
+        <v>3.82</v>
       </c>
       <c r="F71" t="n">
-        <v>13.11</v>
+        <v>10.18</v>
       </c>
       <c r="G71" t="n">
-        <v>148</v>
+        <v>155.5</v>
       </c>
       <c r="H71" t="n">
-        <v>12.7</v>
+        <v>43.4</v>
       </c>
       <c r="I71" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>246.43</v>
+        <v>-178.19</v>
       </c>
       <c r="K71" t="n">
-        <v>-350.91</v>
+        <v>-164.53</v>
       </c>
       <c r="L71" t="n">
-        <v>428.8</v>
+        <v>242.53</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:36:26</t>
+          <t>07:40:30</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.55</v>
+        <v>4.33</v>
       </c>
       <c r="F72" t="n">
         <v>11.26</v>
       </c>
       <c r="G72" t="n">
-        <v>155.1</v>
+        <v>152.5</v>
       </c>
       <c r="H72" t="n">
-        <v>15.2</v>
+        <v>62.1</v>
       </c>
       <c r="I72" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>-131.72</v>
+        <v>290.23</v>
       </c>
       <c r="K72" t="n">
-        <v>-239.87</v>
+        <v>79.92</v>
       </c>
       <c r="L72" t="n">
-        <v>273.66</v>
+        <v>301.03</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:38:23</t>
+          <t>07:41:32</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.52</v>
+        <v>3.92</v>
       </c>
       <c r="F73" t="n">
-        <v>11.9</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>146.4</v>
+        <v>143.2</v>
       </c>
       <c r="H73" t="n">
-        <v>8.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="I73" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-60.99</v>
+        <v>230.47</v>
       </c>
       <c r="K73" t="n">
-        <v>-192.44</v>
+        <v>-192.63</v>
       </c>
       <c r="L73" t="n">
-        <v>201.87</v>
+        <v>300.37</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:48:48</t>
+          <t>07:53:03</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.07</v>
+        <v>4.93</v>
       </c>
       <c r="F74" t="n">
-        <v>10.8</v>
+        <v>13.11</v>
       </c>
       <c r="G74" t="n">
-        <v>160</v>
+        <v>157.9</v>
       </c>
       <c r="H74" t="n">
-        <v>15.9</v>
+        <v>13.1</v>
       </c>
       <c r="I74" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>73.56</v>
+        <v>-85.56</v>
       </c>
       <c r="K74" t="n">
-        <v>-10.45</v>
+        <v>58.49</v>
       </c>
       <c r="L74" t="n">
-        <v>74.29000000000001</v>
+        <v>103.64</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:50:57</t>
+          <t>07:55:21</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.98</v>
+        <v>4.34</v>
       </c>
       <c r="F75" t="n">
-        <v>12.81</v>
+        <v>12.91</v>
       </c>
       <c r="G75" t="n">
-        <v>158.2</v>
+        <v>155.4</v>
       </c>
       <c r="H75" t="n">
-        <v>11.6</v>
+        <v>36.1</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-49.35</v>
+        <v>-81.22</v>
       </c>
       <c r="K75" t="n">
-        <v>-57.5</v>
+        <v>-55.68</v>
       </c>
       <c r="L75" t="n">
-        <v>75.77</v>
+        <v>98.47</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:53:02</t>
+          <t>07:56:45</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.7</v>
+        <v>3.98</v>
       </c>
       <c r="F76" t="n">
-        <v>10.97</v>
+        <v>13.11</v>
       </c>
       <c r="G76" t="n">
-        <v>156.6</v>
+        <v>152.6</v>
       </c>
       <c r="H76" t="n">
-        <v>14</v>
+        <v>28.5</v>
       </c>
       <c r="I76" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>62.56</v>
+        <v>-63.24</v>
       </c>
       <c r="K76" t="n">
-        <v>32.61</v>
+        <v>52.1</v>
       </c>
       <c r="L76" t="n">
-        <v>70.55</v>
+        <v>81.94</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:57:01</t>
+          <t>08:01:18</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.84</v>
+        <v>4.25</v>
       </c>
       <c r="F77" t="n">
-        <v>12.48</v>
+        <v>13.11</v>
       </c>
       <c r="G77" t="n">
-        <v>158.2</v>
+        <v>156.7</v>
       </c>
       <c r="H77" t="n">
-        <v>8.1</v>
+        <v>45.2</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J77" t="n">
-        <v>-66.06999999999999</v>
+        <v>7.55</v>
       </c>
       <c r="K77" t="n">
-        <v>-44.7</v>
+        <v>-113.86</v>
       </c>
       <c r="L77" t="n">
-        <v>79.77</v>
+        <v>114.11</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:58:01</t>
+          <t>08:03:16</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.91</v>
+        <v>4.07</v>
       </c>
       <c r="F78" t="n">
         <v>13.11</v>
       </c>
       <c r="G78" t="n">
-        <v>157.4</v>
+        <v>148</v>
       </c>
       <c r="H78" t="n">
-        <v>8.199999999999999</v>
+        <v>33.7</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J78" t="n">
-        <v>-41.6</v>
+        <v>63.22</v>
       </c>
       <c r="K78" t="n">
-        <v>57.54</v>
+        <v>-103.96</v>
       </c>
       <c r="L78" t="n">
-        <v>71</v>
+        <v>121.68</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:59:16</t>
+          <t>08:05:09</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.33</v>
+        <v>3.96</v>
       </c>
       <c r="F79" t="n">
-        <v>10.07</v>
+        <v>13.11</v>
       </c>
       <c r="G79" t="n">
-        <v>149.7</v>
+        <v>152.6</v>
       </c>
       <c r="H79" t="n">
-        <v>13.3</v>
+        <v>51.6</v>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-65.78</v>
+        <v>-90.79000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>-40.92</v>
+        <v>-4.99</v>
       </c>
       <c r="L79" t="n">
-        <v>77.47</v>
+        <v>90.92</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:04:11</t>
+          <t>08:10:37</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="F80" t="n">
-        <v>11.06</v>
+        <v>10.4</v>
       </c>
       <c r="G80" t="n">
-        <v>167.3</v>
+        <v>151.2</v>
       </c>
       <c r="H80" t="n">
-        <v>17.8</v>
+        <v>56.4</v>
       </c>
       <c r="I80" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>-34.01</v>
+        <v>110.41</v>
       </c>
       <c r="K80" t="n">
-        <v>-87.77</v>
+        <v>-92.87</v>
       </c>
       <c r="L80" t="n">
-        <v>94.13</v>
+        <v>144.27</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:05:03</t>
+          <t>08:11:53</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.98</v>
+        <v>4.6</v>
       </c>
       <c r="F81" t="n">
-        <v>12.43</v>
+        <v>13.11</v>
       </c>
       <c r="G81" t="n">
-        <v>155.1</v>
+        <v>154.5</v>
       </c>
       <c r="H81" t="n">
-        <v>12.8</v>
+        <v>50.2</v>
       </c>
       <c r="I81" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>26.37</v>
+        <v>178.07</v>
       </c>
       <c r="K81" t="n">
-        <v>-100.95</v>
+        <v>-58.64</v>
       </c>
       <c r="L81" t="n">
-        <v>104.34</v>
+        <v>187.47</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:07:36</t>
+          <t>08:14:37</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="F82" t="n">
-        <v>10.52</v>
+        <v>10.23</v>
       </c>
       <c r="G82" t="n">
-        <v>162.9</v>
+        <v>154.9</v>
       </c>
       <c r="H82" t="n">
-        <v>8.5</v>
+        <v>40.2</v>
       </c>
       <c r="I82" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J82" t="n">
-        <v>157.68</v>
+        <v>-5.03</v>
       </c>
       <c r="K82" t="n">
-        <v>34.28</v>
+        <v>-110.4</v>
       </c>
       <c r="L82" t="n">
-        <v>161.36</v>
+        <v>110.51</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:12:00</t>
+          <t>08:19:47</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.58</v>
+        <v>3.39</v>
       </c>
       <c r="F83" t="n">
-        <v>10.21</v>
+        <v>8.01</v>
       </c>
       <c r="G83" t="n">
-        <v>158.8</v>
+        <v>158.2</v>
       </c>
       <c r="H83" t="n">
-        <v>12.3</v>
+        <v>13.3</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J83" t="n">
-        <v>77.77</v>
+        <v>-172.21</v>
       </c>
       <c r="K83" t="n">
-        <v>-111.96</v>
+        <v>-81.05</v>
       </c>
       <c r="L83" t="n">
-        <v>136.32</v>
+        <v>190.33</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:14:03</t>
+          <t>08:20:51</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.55</v>
+        <v>3.79</v>
       </c>
       <c r="F84" t="n">
-        <v>13.11</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G84" t="n">
-        <v>166.8</v>
+        <v>158.1</v>
       </c>
       <c r="H84" t="n">
-        <v>6.6</v>
+        <v>25.7</v>
       </c>
       <c r="I84" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-58.68</v>
+        <v>213.69</v>
       </c>
       <c r="K84" t="n">
-        <v>-135.73</v>
+        <v>27.59</v>
       </c>
       <c r="L84" t="n">
-        <v>147.87</v>
+        <v>215.46</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:15:55</t>
+          <t>08:22:43</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.57</v>
+        <v>3.45</v>
       </c>
       <c r="F85" t="n">
-        <v>13.11</v>
+        <v>12.45</v>
       </c>
       <c r="G85" t="n">
-        <v>157.3</v>
+        <v>176.4</v>
       </c>
       <c r="H85" t="n">
-        <v>13.6</v>
+        <v>76.2</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>54.05</v>
+        <v>-262.27</v>
       </c>
       <c r="K85" t="n">
-        <v>151.94</v>
+        <v>73.48</v>
       </c>
       <c r="L85" t="n">
-        <v>161.27</v>
+        <v>272.36</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:21:33</t>
+          <t>08:27:31</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.49</v>
+        <v>3.1</v>
       </c>
       <c r="F86" t="n">
-        <v>12.1</v>
+        <v>10.29</v>
       </c>
       <c r="G86" t="n">
-        <v>167.7</v>
+        <v>142.6</v>
       </c>
       <c r="H86" t="n">
-        <v>18</v>
+        <v>51.3</v>
       </c>
       <c r="I86" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>361.32</v>
+        <v>144.44</v>
       </c>
       <c r="K86" t="n">
-        <v>-12.16</v>
+        <v>-135.46</v>
       </c>
       <c r="L86" t="n">
-        <v>361.53</v>
+        <v>198.02</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:22:23</t>
+          <t>08:29:06</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.58</v>
+        <v>4.03</v>
       </c>
       <c r="F87" t="n">
-        <v>9.140000000000001</v>
+        <v>12.85</v>
       </c>
       <c r="G87" t="n">
-        <v>149.9</v>
+        <v>150.6</v>
       </c>
       <c r="H87" t="n">
-        <v>9.5</v>
+        <v>39.6</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J87" t="n">
-        <v>195.91</v>
+        <v>273.94</v>
       </c>
       <c r="K87" t="n">
-        <v>-165.28</v>
+        <v>-11.83</v>
       </c>
       <c r="L87" t="n">
-        <v>256.32</v>
+        <v>274.19</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:24:35</t>
+          <t>08:30:12</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.65</v>
+        <v>4.16</v>
       </c>
       <c r="F88" t="n">
-        <v>13.11</v>
+        <v>11.14</v>
       </c>
       <c r="G88" t="n">
-        <v>156.7</v>
+        <v>148.5</v>
       </c>
       <c r="H88" t="n">
-        <v>11.1</v>
+        <v>34.5</v>
       </c>
       <c r="I88" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>339.07</v>
+        <v>260.83</v>
       </c>
       <c r="K88" t="n">
-        <v>30.84</v>
+        <v>-192.43</v>
       </c>
       <c r="L88" t="n">
-        <v>340.47</v>
+        <v>324.13</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-24.xlsx
+++ b/output/2025-05-24.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>3.83</v>
       </c>
       <c r="F14" t="n">
-        <v>8.17</v>
+        <v>9.69</v>
       </c>
       <c r="G14" t="n">
-        <v>158.4</v>
+        <v>153.8</v>
       </c>
       <c r="H14" t="n">
-        <v>38.3</v>
+        <v>38.8</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-22.83</v>
+        <v>36.79</v>
       </c>
       <c r="K14" t="n">
-        <v>-62.15</v>
+        <v>-58.21</v>
       </c>
       <c r="L14" t="n">
-        <v>66.20999999999999</v>
+        <v>68.86</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:46:40</t>
+          <t>04:47:27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.99</v>
+        <v>3.13</v>
       </c>
       <c r="F15" t="n">
-        <v>7.68</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>160.6</v>
+        <v>148.2</v>
       </c>
       <c r="H15" t="n">
-        <v>45.7</v>
+        <v>42.3</v>
       </c>
       <c r="I15" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>-62.6</v>
+        <v>24.98</v>
       </c>
       <c r="K15" t="n">
-        <v>-19.13</v>
+        <v>-39.7</v>
       </c>
       <c r="L15" t="n">
-        <v>65.45999999999999</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:49:08</t>
+          <t>04:49:34</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.65</v>
+        <v>2.94</v>
       </c>
       <c r="F16" t="n">
-        <v>11.63</v>
+        <v>10.59</v>
       </c>
       <c r="G16" t="n">
-        <v>165.7</v>
+        <v>165.9</v>
       </c>
       <c r="H16" t="n">
-        <v>16.2</v>
+        <v>66.3</v>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J16" t="n">
-        <v>55.92</v>
+        <v>-51.46</v>
       </c>
       <c r="K16" t="n">
-        <v>-31.14</v>
+        <v>8.25</v>
       </c>
       <c r="L16" t="n">
-        <v>64.01000000000001</v>
+        <v>52.11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:53:08</t>
+          <t>04:54:16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.07</v>
+        <v>3.32</v>
       </c>
       <c r="F17" t="n">
-        <v>12.44</v>
+        <v>9.59</v>
       </c>
       <c r="G17" t="n">
-        <v>152</v>
+        <v>153.6</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J17" t="n">
-        <v>-22.71</v>
+        <v>80.22</v>
       </c>
       <c r="K17" t="n">
-        <v>-71.44</v>
+        <v>13.11</v>
       </c>
       <c r="L17" t="n">
-        <v>74.95999999999999</v>
+        <v>81.29000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:54:07</t>
+          <t>04:56:25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.03</v>
+        <v>3.89</v>
       </c>
       <c r="F18" t="n">
-        <v>7.73</v>
+        <v>13.11</v>
       </c>
       <c r="G18" t="n">
-        <v>150.3</v>
+        <v>169.6</v>
       </c>
       <c r="H18" t="n">
-        <v>34.4</v>
+        <v>47.7</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>15.41</v>
+        <v>-108.42</v>
       </c>
       <c r="K18" t="n">
-        <v>-51.62</v>
+        <v>-11.1</v>
       </c>
       <c r="L18" t="n">
-        <v>53.87</v>
+        <v>108.98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:55:14</t>
+          <t>04:57:33</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="F19" t="n">
-        <v>6.5</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>143.7</v>
+        <v>161.6</v>
       </c>
       <c r="H19" t="n">
-        <v>2.4</v>
+        <v>37.5</v>
       </c>
       <c r="I19" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>-18.57</v>
+        <v>29.25</v>
       </c>
       <c r="K19" t="n">
-        <v>-61.16</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>63.92</v>
+        <v>92.64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:00:04</t>
+          <t>05:02:54</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.37</v>
+        <v>3.28</v>
       </c>
       <c r="F20" t="n">
-        <v>10.54</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>172.6</v>
+        <v>165.2</v>
       </c>
       <c r="H20" t="n">
-        <v>53.7</v>
+        <v>32.8</v>
       </c>
       <c r="I20" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J20" t="n">
-        <v>22.98</v>
+        <v>16.54</v>
       </c>
       <c r="K20" t="n">
-        <v>118.03</v>
+        <v>119.13</v>
       </c>
       <c r="L20" t="n">
-        <v>120.25</v>
+        <v>120.28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:01:48</t>
+          <t>05:03:38</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="F21" t="n">
-        <v>10.61</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>158.8</v>
+        <v>153.6</v>
       </c>
       <c r="H21" t="n">
-        <v>40.1</v>
+        <v>44.6</v>
       </c>
       <c r="I21" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>87.54000000000001</v>
+        <v>-53.9</v>
       </c>
       <c r="K21" t="n">
-        <v>-47.8</v>
+        <v>-90</v>
       </c>
       <c r="L21" t="n">
-        <v>99.73999999999999</v>
+        <v>104.91</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:02:59</t>
+          <t>05:05:13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.73</v>
+        <v>3.18</v>
       </c>
       <c r="F22" t="n">
-        <v>11.11</v>
+        <v>12.68</v>
       </c>
       <c r="G22" t="n">
-        <v>156</v>
+        <v>145.4</v>
       </c>
       <c r="H22" t="n">
-        <v>81.59999999999999</v>
+        <v>21.7</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J22" t="n">
-        <v>-97.34999999999999</v>
+        <v>-56.88</v>
       </c>
       <c r="K22" t="n">
-        <v>-38.5</v>
+        <v>-108.39</v>
       </c>
       <c r="L22" t="n">
-        <v>104.69</v>
+        <v>122.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:07:17</t>
+          <t>05:09:21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="F23" t="n">
-        <v>8.48</v>
+        <v>9.73</v>
       </c>
       <c r="G23" t="n">
-        <v>154.5</v>
+        <v>160.3</v>
       </c>
       <c r="H23" t="n">
-        <v>78.09999999999999</v>
+        <v>44.7</v>
       </c>
       <c r="I23" t="n">
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-36.73</v>
+        <v>-185.85</v>
       </c>
       <c r="K23" t="n">
-        <v>-155.8</v>
+        <v>20.25</v>
       </c>
       <c r="L23" t="n">
-        <v>160.07</v>
+        <v>186.95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:09:13</t>
+          <t>05:11:21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.48</v>
+        <v>3.43</v>
       </c>
       <c r="F24" t="n">
-        <v>9.34</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>161.6</v>
+        <v>153.3</v>
       </c>
       <c r="H24" t="n">
-        <v>25.6</v>
+        <v>13.8</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>162.9</v>
+        <v>-114.3</v>
       </c>
       <c r="K24" t="n">
-        <v>-23.14</v>
+        <v>135.83</v>
       </c>
       <c r="L24" t="n">
-        <v>164.53</v>
+        <v>177.53</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:11:41</t>
+          <t>05:12:46</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.75</v>
+        <v>3.02</v>
       </c>
       <c r="F25" t="n">
-        <v>7.58</v>
+        <v>6.9</v>
       </c>
       <c r="G25" t="n">
-        <v>144.4</v>
+        <v>151</v>
       </c>
       <c r="H25" t="n">
-        <v>33</v>
+        <v>46.2</v>
       </c>
       <c r="I25" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J25" t="n">
-        <v>-22.07</v>
+        <v>-94.54000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>-239.12</v>
+        <v>90.73</v>
       </c>
       <c r="L25" t="n">
-        <v>240.14</v>
+        <v>131.03</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:15:34</t>
+          <t>05:17:30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.02</v>
+        <v>4.06</v>
       </c>
       <c r="F26" t="n">
-        <v>13.11</v>
+        <v>13.01</v>
       </c>
       <c r="G26" t="n">
-        <v>162.2</v>
+        <v>149</v>
       </c>
       <c r="H26" t="n">
-        <v>83.90000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="I26" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>79.09999999999999</v>
+        <v>201.62</v>
       </c>
       <c r="K26" t="n">
-        <v>-317.49</v>
+        <v>177.95</v>
       </c>
       <c r="L26" t="n">
-        <v>327.19</v>
+        <v>268.92</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:17:29</t>
+          <t>05:19:09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="F27" t="n">
-        <v>10.2</v>
+        <v>11.7</v>
       </c>
       <c r="G27" t="n">
-        <v>143.6</v>
+        <v>133.5</v>
       </c>
       <c r="H27" t="n">
-        <v>26.3</v>
+        <v>28.5</v>
       </c>
       <c r="I27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>187.9</v>
+        <v>250.83</v>
       </c>
       <c r="K27" t="n">
-        <v>-98.92</v>
+        <v>113.25</v>
       </c>
       <c r="L27" t="n">
-        <v>212.35</v>
+        <v>275.21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:19:46</t>
+          <t>05:20:58</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.69</v>
+        <v>3.91</v>
       </c>
       <c r="F28" t="n">
-        <v>9.619999999999999</v>
+        <v>13.11</v>
       </c>
       <c r="G28" t="n">
-        <v>147.2</v>
+        <v>144.7</v>
       </c>
       <c r="H28" t="n">
-        <v>36.6</v>
+        <v>67.3</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J28" t="n">
-        <v>154.27</v>
+        <v>51.76</v>
       </c>
       <c r="K28" t="n">
-        <v>-165.21</v>
+        <v>232.85</v>
       </c>
       <c r="L28" t="n">
-        <v>226.04</v>
+        <v>238.54</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:29:29</t>
+          <t>05:32:06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.13</v>
+        <v>2.77</v>
       </c>
       <c r="F29" t="n">
-        <v>13.11</v>
+        <v>9.09</v>
       </c>
       <c r="G29" t="n">
-        <v>154.2</v>
+        <v>143.3</v>
       </c>
       <c r="H29" t="n">
-        <v>21.5</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>-25.76</v>
+        <v>-40.59</v>
       </c>
       <c r="K29" t="n">
-        <v>-78.98999999999999</v>
+        <v>-11.36</v>
       </c>
       <c r="L29" t="n">
-        <v>83.09</v>
+        <v>42.15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:31:08</t>
+          <t>05:32:33</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.42</v>
+        <v>3.37</v>
       </c>
       <c r="F30" t="n">
-        <v>10.92</v>
+        <v>10.98</v>
       </c>
       <c r="G30" t="n">
-        <v>160</v>
+        <v>144.8</v>
       </c>
       <c r="H30" t="n">
-        <v>37.2</v>
+        <v>28.1</v>
       </c>
       <c r="I30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>-65.45999999999999</v>
+        <v>-61.44</v>
       </c>
       <c r="K30" t="n">
-        <v>-11.89</v>
+        <v>-12.48</v>
       </c>
       <c r="L30" t="n">
-        <v>66.53</v>
+        <v>62.69</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:33:12</t>
+          <t>05:35:10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="F31" t="n">
-        <v>7.17</v>
+        <v>6.53</v>
       </c>
       <c r="G31" t="n">
-        <v>168.1</v>
+        <v>140.9</v>
       </c>
       <c r="H31" t="n">
-        <v>29.3</v>
+        <v>33.7</v>
       </c>
       <c r="I31" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-49.38</v>
+        <v>-54.72</v>
       </c>
       <c r="K31" t="n">
-        <v>-37.39</v>
+        <v>31</v>
       </c>
       <c r="L31" t="n">
-        <v>61.94</v>
+        <v>62.89</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:36:55</t>
+          <t>05:39:31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.89</v>
+        <v>3.63</v>
       </c>
       <c r="F32" t="n">
-        <v>12.04</v>
+        <v>13.11</v>
       </c>
       <c r="G32" t="n">
-        <v>162.5</v>
+        <v>159</v>
       </c>
       <c r="H32" t="n">
-        <v>64.7</v>
+        <v>59.3</v>
       </c>
       <c r="I32" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-68.16</v>
+        <v>23.04</v>
       </c>
       <c r="K32" t="n">
-        <v>-60.2</v>
+        <v>102.79</v>
       </c>
       <c r="L32" t="n">
-        <v>90.94</v>
+        <v>105.34</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:39:05</t>
+          <t>05:41:38</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="F33" t="n">
-        <v>9.48</v>
+        <v>10.49</v>
       </c>
       <c r="G33" t="n">
-        <v>148.1</v>
+        <v>159.2</v>
       </c>
       <c r="H33" t="n">
-        <v>6.4</v>
+        <v>58</v>
       </c>
       <c r="I33" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>61.8</v>
+        <v>-78.51000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>-56.08</v>
+        <v>18.29</v>
       </c>
       <c r="L33" t="n">
-        <v>83.45</v>
+        <v>80.61</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:40:10</t>
+          <t>05:42:48</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.36</v>
+        <v>2.81</v>
       </c>
       <c r="F34" t="n">
-        <v>10.72</v>
+        <v>7.36</v>
       </c>
       <c r="G34" t="n">
-        <v>147.1</v>
+        <v>154.9</v>
       </c>
       <c r="H34" t="n">
-        <v>79.5</v>
+        <v>59.3</v>
       </c>
       <c r="I34" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J34" t="n">
-        <v>-55.27</v>
+        <v>-52.13</v>
       </c>
       <c r="K34" t="n">
-        <v>92.47</v>
+        <v>48.72</v>
       </c>
       <c r="L34" t="n">
-        <v>107.73</v>
+        <v>71.34999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:44:21</t>
+          <t>05:47:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.99</v>
+        <v>3.28</v>
       </c>
       <c r="F35" t="n">
-        <v>9.98</v>
+        <v>10.87</v>
       </c>
       <c r="G35" t="n">
-        <v>165.8</v>
+        <v>155.1</v>
       </c>
       <c r="H35" t="n">
-        <v>29.2</v>
+        <v>76.8</v>
       </c>
       <c r="I35" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>87.05</v>
+        <v>108.44</v>
       </c>
       <c r="K35" t="n">
-        <v>-13.28</v>
+        <v>32.79</v>
       </c>
       <c r="L35" t="n">
-        <v>88.05</v>
+        <v>113.29</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:45:48</t>
+          <t>05:49:29</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.63</v>
+        <v>3.17</v>
       </c>
       <c r="F36" t="n">
-        <v>12.33</v>
+        <v>11.02</v>
       </c>
       <c r="G36" t="n">
-        <v>153.9</v>
+        <v>138.4</v>
       </c>
       <c r="H36" t="n">
-        <v>41.5</v>
+        <v>40.3</v>
       </c>
       <c r="I36" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J36" t="n">
-        <v>44.96</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-124.11</v>
+        <v>-69.38</v>
       </c>
       <c r="L36" t="n">
-        <v>132</v>
+        <v>107.41</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:48:03</t>
+          <t>05:49:56</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.26</v>
+        <v>3.04</v>
       </c>
       <c r="F37" t="n">
-        <v>10.24</v>
+        <v>9.19</v>
       </c>
       <c r="G37" t="n">
-        <v>140.6</v>
+        <v>166.7</v>
       </c>
       <c r="H37" t="n">
-        <v>20.8</v>
+        <v>25.1</v>
       </c>
       <c r="I37" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>72.03</v>
+        <v>-65.28</v>
       </c>
       <c r="K37" t="n">
-        <v>-28.68</v>
+        <v>80.18000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>77.53</v>
+        <v>103.39</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:53:20</t>
+          <t>05:55:13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.53</v>
+        <v>3.8</v>
       </c>
       <c r="F38" t="n">
-        <v>12.92</v>
+        <v>8.26</v>
       </c>
       <c r="G38" t="n">
-        <v>155.3</v>
+        <v>150.3</v>
       </c>
       <c r="H38" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="I38" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-205.54</v>
+        <v>-81.97</v>
       </c>
       <c r="K38" t="n">
-        <v>-74.04000000000001</v>
+        <v>-135.61</v>
       </c>
       <c r="L38" t="n">
-        <v>218.47</v>
+        <v>158.46</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:54:29</t>
+          <t>05:57:55</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.64</v>
+        <v>3.23</v>
       </c>
       <c r="F39" t="n">
-        <v>11.28</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>147.2</v>
+        <v>155.7</v>
       </c>
       <c r="H39" t="n">
-        <v>30.4</v>
+        <v>47.2</v>
       </c>
       <c r="I39" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J39" t="n">
-        <v>44.84</v>
+        <v>36.03</v>
       </c>
       <c r="K39" t="n">
-        <v>173.73</v>
+        <v>195.31</v>
       </c>
       <c r="L39" t="n">
-        <v>179.42</v>
+        <v>198.61</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:56:14</t>
+          <t>05:59:38</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.34</v>
+        <v>3.83</v>
       </c>
       <c r="F40" t="n">
-        <v>13.11</v>
+        <v>11.79</v>
       </c>
       <c r="G40" t="n">
-        <v>140.7</v>
+        <v>137.4</v>
       </c>
       <c r="H40" t="n">
-        <v>56.3</v>
+        <v>55.6</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J40" t="n">
-        <v>86.08</v>
+        <v>259.95</v>
       </c>
       <c r="K40" t="n">
-        <v>-202.01</v>
+        <v>-143.9</v>
       </c>
       <c r="L40" t="n">
-        <v>219.59</v>
+        <v>297.12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:00:56</t>
+          <t>06:03:58</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.23</v>
+        <v>3.49</v>
       </c>
       <c r="F41" t="n">
-        <v>10.48</v>
+        <v>10.62</v>
       </c>
       <c r="G41" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H41" t="n">
-        <v>14</v>
+        <v>59.6</v>
       </c>
       <c r="I41" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-41.3</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>-211.23</v>
+        <v>-215.99</v>
       </c>
       <c r="L41" t="n">
-        <v>215.23</v>
+        <v>226.81</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:02:29</t>
+          <t>06:05:38</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.39</v>
+        <v>3.85</v>
       </c>
       <c r="F42" t="n">
-        <v>11.06</v>
+        <v>13.11</v>
       </c>
       <c r="G42" t="n">
-        <v>142.6</v>
+        <v>151.4</v>
       </c>
       <c r="H42" t="n">
-        <v>39</v>
+        <v>43.9</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>215.13</v>
+        <v>-340</v>
       </c>
       <c r="K42" t="n">
-        <v>-37.26</v>
+        <v>-243.82</v>
       </c>
       <c r="L42" t="n">
-        <v>218.34</v>
+        <v>418.39</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:04:28</t>
+          <t>06:07:40</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.67</v>
+        <v>2.83</v>
       </c>
       <c r="F43" t="n">
-        <v>9.949999999999999</v>
+        <v>5.54</v>
       </c>
       <c r="G43" t="n">
-        <v>152.7</v>
+        <v>154.2</v>
       </c>
       <c r="H43" t="n">
-        <v>35.4</v>
+        <v>14.7</v>
       </c>
       <c r="I43" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J43" t="n">
-        <v>221.59</v>
+        <v>-12.31</v>
       </c>
       <c r="K43" t="n">
-        <v>123.47</v>
+        <v>195.08</v>
       </c>
       <c r="L43" t="n">
-        <v>253.66</v>
+        <v>195.46</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:18:13</t>
+          <t>06:15:44</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.77</v>
+        <v>3.7</v>
       </c>
       <c r="F44" t="n">
-        <v>7.47</v>
+        <v>13.11</v>
       </c>
       <c r="G44" t="n">
-        <v>158</v>
+        <v>163.7</v>
       </c>
       <c r="H44" t="n">
-        <v>48.1</v>
+        <v>45.9</v>
       </c>
       <c r="I44" t="n">
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>-47</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.25</v>
+        <v>-55.2</v>
       </c>
       <c r="L44" t="n">
-        <v>47</v>
+        <v>55.78</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:19:46</t>
+          <t>06:17:38</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.69</v>
+        <v>3.86</v>
       </c>
       <c r="F45" t="n">
-        <v>9.67</v>
+        <v>11.73</v>
       </c>
       <c r="G45" t="n">
-        <v>155.3</v>
+        <v>153.6</v>
       </c>
       <c r="H45" t="n">
-        <v>48.4</v>
+        <v>51.2</v>
       </c>
       <c r="I45" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J45" t="n">
-        <v>-34.86</v>
+        <v>8.25</v>
       </c>
       <c r="K45" t="n">
-        <v>-56.61</v>
+        <v>-66.44</v>
       </c>
       <c r="L45" t="n">
-        <v>66.48</v>
+        <v>66.95</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:20:57</t>
+          <t>06:19:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.32</v>
+        <v>3.62</v>
       </c>
       <c r="F46" t="n">
-        <v>9.01</v>
+        <v>11.38</v>
       </c>
       <c r="G46" t="n">
-        <v>155.2</v>
+        <v>153.7</v>
       </c>
       <c r="H46" t="n">
-        <v>67.40000000000001</v>
+        <v>61</v>
       </c>
       <c r="I46" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J46" t="n">
-        <v>46.69</v>
+        <v>-57.73</v>
       </c>
       <c r="K46" t="n">
-        <v>71.59999999999999</v>
+        <v>52.16</v>
       </c>
       <c r="L46" t="n">
-        <v>85.48</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:24:02</t>
+          <t>06:23:22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.81</v>
+        <v>3.43</v>
       </c>
       <c r="F47" t="n">
-        <v>13.06</v>
+        <v>13.11</v>
       </c>
       <c r="G47" t="n">
-        <v>152.8</v>
+        <v>162.3</v>
       </c>
       <c r="H47" t="n">
-        <v>17.9</v>
+        <v>51.2</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J47" t="n">
-        <v>18.65</v>
+        <v>-74.48</v>
       </c>
       <c r="K47" t="n">
-        <v>-64.81999999999999</v>
+        <v>-29.19</v>
       </c>
       <c r="L47" t="n">
-        <v>67.45</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:25:52</t>
+          <t>06:24:30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="F48" t="n">
-        <v>10.43</v>
+        <v>12.09</v>
       </c>
       <c r="G48" t="n">
-        <v>144.8</v>
+        <v>150.8</v>
       </c>
       <c r="H48" t="n">
-        <v>37.7</v>
+        <v>26.4</v>
       </c>
       <c r="I48" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J48" t="n">
-        <v>62.59</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>43.6</v>
+        <v>20.94</v>
       </c>
       <c r="L48" t="n">
-        <v>76.28</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:27:04</t>
+          <t>06:25:20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.39</v>
+        <v>3.99</v>
       </c>
       <c r="F49" t="n">
-        <v>11.57</v>
+        <v>8.82</v>
       </c>
       <c r="G49" t="n">
-        <v>163.4</v>
+        <v>144.4</v>
       </c>
       <c r="H49" t="n">
-        <v>20.6</v>
+        <v>33</v>
       </c>
       <c r="I49" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>63.1</v>
+        <v>-32.03</v>
       </c>
       <c r="K49" t="n">
-        <v>19.1</v>
+        <v>-112.98</v>
       </c>
       <c r="L49" t="n">
-        <v>65.92</v>
+        <v>117.43</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:32:55</t>
+          <t>06:30:27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.28</v>
+        <v>4.27</v>
       </c>
       <c r="F50" t="n">
         <v>13.11</v>
       </c>
       <c r="G50" t="n">
-        <v>160.2</v>
+        <v>162.2</v>
       </c>
       <c r="H50" t="n">
-        <v>54.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J50" t="n">
-        <v>50.57</v>
+        <v>41.66</v>
       </c>
       <c r="K50" t="n">
-        <v>126.46</v>
+        <v>-183.04</v>
       </c>
       <c r="L50" t="n">
-        <v>136.19</v>
+        <v>187.72</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:35:02</t>
+          <t>06:32:23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="F51" t="n">
-        <v>12.44</v>
+        <v>11.42</v>
       </c>
       <c r="G51" t="n">
-        <v>154.9</v>
+        <v>143.6</v>
       </c>
       <c r="H51" t="n">
-        <v>44.2</v>
+        <v>26.3</v>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>82.47</v>
+        <v>113.93</v>
       </c>
       <c r="K51" t="n">
-        <v>103.86</v>
+        <v>-43.4</v>
       </c>
       <c r="L51" t="n">
-        <v>132.62</v>
+        <v>121.92</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:36:47</t>
+          <t>06:34:02</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.85</v>
+        <v>3.93</v>
       </c>
       <c r="F52" t="n">
-        <v>10.29</v>
+        <v>10.86</v>
       </c>
       <c r="G52" t="n">
-        <v>155.9</v>
+        <v>147.2</v>
       </c>
       <c r="H52" t="n">
-        <v>28</v>
+        <v>36.6</v>
       </c>
       <c r="I52" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J52" t="n">
-        <v>-180.28</v>
+        <v>92.44</v>
       </c>
       <c r="K52" t="n">
-        <v>0.96</v>
+        <v>-89.34999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>180.29</v>
+        <v>128.57</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:41:03</t>
+          <t>06:37:16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.72</v>
+        <v>4.35</v>
       </c>
       <c r="F53" t="n">
-        <v>10.55</v>
+        <v>13.11</v>
       </c>
       <c r="G53" t="n">
-        <v>149.4</v>
+        <v>154.2</v>
       </c>
       <c r="H53" t="n">
-        <v>31.7</v>
+        <v>21.5</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>-99.06</v>
+        <v>-151.06</v>
       </c>
       <c r="K53" t="n">
-        <v>-201.89</v>
+        <v>-261.61</v>
       </c>
       <c r="L53" t="n">
-        <v>224.88</v>
+        <v>302.09</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:43:25</t>
+          <t>06:39:41</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.43</v>
+        <v>3.64</v>
       </c>
       <c r="F54" t="n">
-        <v>10.15</v>
+        <v>12.02</v>
       </c>
       <c r="G54" t="n">
-        <v>144.1</v>
+        <v>160</v>
       </c>
       <c r="H54" t="n">
-        <v>55.5</v>
+        <v>37.2</v>
       </c>
       <c r="I54" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J54" t="n">
-        <v>-201.91</v>
+        <v>-254.07</v>
       </c>
       <c r="K54" t="n">
-        <v>-63.05</v>
+        <v>13.15</v>
       </c>
       <c r="L54" t="n">
-        <v>211.53</v>
+        <v>254.41</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:45:43</t>
+          <t>06:40:50</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.23</v>
+        <v>3.53</v>
       </c>
       <c r="F55" t="n">
-        <v>13.11</v>
+        <v>8.25</v>
       </c>
       <c r="G55" t="n">
-        <v>145.3</v>
+        <v>168.1</v>
       </c>
       <c r="H55" t="n">
-        <v>13.9</v>
+        <v>29.3</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J55" t="n">
-        <v>139.23</v>
+        <v>-214.62</v>
       </c>
       <c r="K55" t="n">
-        <v>-115.65</v>
+        <v>-97.15000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>181</v>
+        <v>235.58</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:50:40</t>
+          <t>06:46:04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.18</v>
+        <v>4.1</v>
       </c>
       <c r="F56" t="n">
-        <v>11.11</v>
+        <v>13.11</v>
       </c>
       <c r="G56" t="n">
-        <v>145.6</v>
+        <v>162.5</v>
       </c>
       <c r="H56" t="n">
-        <v>64.40000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>-78.90000000000001</v>
+        <v>-275.94</v>
       </c>
       <c r="K56" t="n">
-        <v>-197.41</v>
+        <v>-140.54</v>
       </c>
       <c r="L56" t="n">
-        <v>212.59</v>
+        <v>309.66</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:52:07</t>
+          <t>06:47:36</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="F57" t="n">
-        <v>11.24</v>
+        <v>10.6</v>
       </c>
       <c r="G57" t="n">
-        <v>165.2</v>
+        <v>148.1</v>
       </c>
       <c r="H57" t="n">
-        <v>56.8</v>
+        <v>6.4</v>
       </c>
       <c r="I57" t="n">
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-40.68</v>
+        <v>218.64</v>
       </c>
       <c r="K57" t="n">
-        <v>-194.82</v>
+        <v>-169.51</v>
       </c>
       <c r="L57" t="n">
-        <v>199.03</v>
+        <v>276.66</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:54:36</t>
+          <t>06:49:45</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="F58" t="n">
-        <v>12.89</v>
+        <v>11.81</v>
       </c>
       <c r="G58" t="n">
-        <v>147</v>
+        <v>147.1</v>
       </c>
       <c r="H58" t="n">
-        <v>43.2</v>
+        <v>79.5</v>
       </c>
       <c r="I58" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J58" t="n">
-        <v>199.72</v>
+        <v>-181.69</v>
       </c>
       <c r="K58" t="n">
-        <v>157.06</v>
+        <v>298.84</v>
       </c>
       <c r="L58" t="n">
-        <v>254.08</v>
+        <v>349.74</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:03:21</t>
+          <t>06:59:33</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.55</v>
+        <v>3.23</v>
       </c>
       <c r="F59" t="n">
-        <v>13.11</v>
+        <v>11.12</v>
       </c>
       <c r="G59" t="n">
-        <v>161.2</v>
+        <v>165.8</v>
       </c>
       <c r="H59" t="n">
-        <v>46.9</v>
+        <v>29.2</v>
       </c>
       <c r="I59" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J59" t="n">
-        <v>28.6</v>
+        <v>52.31</v>
       </c>
       <c r="K59" t="n">
-        <v>-89.38</v>
+        <v>2.97</v>
       </c>
       <c r="L59" t="n">
-        <v>93.84</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:05:35</t>
+          <t>07:01:37</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.17</v>
+        <v>3.87</v>
       </c>
       <c r="F60" t="n">
         <v>13.11</v>
       </c>
       <c r="G60" t="n">
-        <v>136.5</v>
+        <v>153.9</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>41.5</v>
       </c>
       <c r="I60" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>42.69</v>
+        <v>25.33</v>
       </c>
       <c r="K60" t="n">
-        <v>-57.13</v>
+        <v>-77.27</v>
       </c>
       <c r="L60" t="n">
-        <v>71.31999999999999</v>
+        <v>81.31</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:07:06</t>
+          <t>07:03:30</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.15</v>
+        <v>3.49</v>
       </c>
       <c r="F61" t="n">
-        <v>9.98</v>
+        <v>11.39</v>
       </c>
       <c r="G61" t="n">
-        <v>159.8</v>
+        <v>140.6</v>
       </c>
       <c r="H61" t="n">
-        <v>16</v>
+        <v>20.8</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J61" t="n">
-        <v>-23.64</v>
+        <v>46.23</v>
       </c>
       <c r="K61" t="n">
-        <v>35.55</v>
+        <v>-12.01</v>
       </c>
       <c r="L61" t="n">
-        <v>42.69</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:11:48</t>
+          <t>07:08:09</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.56</v>
+        <v>3.76</v>
       </c>
       <c r="F62" t="n">
-        <v>12.55</v>
+        <v>13.11</v>
       </c>
       <c r="G62" t="n">
-        <v>147.9</v>
+        <v>155.3</v>
       </c>
       <c r="H62" t="n">
-        <v>58.7</v>
+        <v>32</v>
       </c>
       <c r="I62" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J62" t="n">
-        <v>-66.5</v>
+        <v>-120.33</v>
       </c>
       <c r="K62" t="n">
-        <v>-47.73</v>
+        <v>-12.67</v>
       </c>
       <c r="L62" t="n">
-        <v>81.86</v>
+        <v>121</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:13:24</t>
+          <t>07:10:09</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.32</v>
+        <v>3.87</v>
       </c>
       <c r="F63" t="n">
-        <v>7.35</v>
+        <v>12.48</v>
       </c>
       <c r="G63" t="n">
-        <v>148.2</v>
+        <v>147.2</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>30.4</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J63" t="n">
-        <v>66.5</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-27.97</v>
+        <v>97.19</v>
       </c>
       <c r="L63" t="n">
-        <v>72.14</v>
+        <v>97.53</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:15:13</t>
+          <t>07:12:33</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.78</v>
+        <v>3.57</v>
       </c>
       <c r="F64" t="n">
-        <v>11.1</v>
+        <v>13.11</v>
       </c>
       <c r="G64" t="n">
-        <v>153.2</v>
+        <v>140.7</v>
       </c>
       <c r="H64" t="n">
-        <v>52.2</v>
+        <v>56.3</v>
       </c>
       <c r="I64" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>69.55</v>
+        <v>40.9</v>
       </c>
       <c r="K64" t="n">
-        <v>19.87</v>
+        <v>-120.01</v>
       </c>
       <c r="L64" t="n">
-        <v>72.33</v>
+        <v>126.79</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:20:19</t>
+          <t>07:17:17</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.57</v>
+        <v>3.46</v>
       </c>
       <c r="F65" t="n">
-        <v>13.11</v>
+        <v>11.62</v>
       </c>
       <c r="G65" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="H65" t="n">
-        <v>41.1</v>
+        <v>14</v>
       </c>
       <c r="I65" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J65" t="n">
-        <v>-132.49</v>
+        <v>-43.7</v>
       </c>
       <c r="K65" t="n">
-        <v>20.3</v>
+        <v>-131.35</v>
       </c>
       <c r="L65" t="n">
-        <v>134.04</v>
+        <v>138.43</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:22:27</t>
+          <t>07:18:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.47</v>
+        <v>3.62</v>
       </c>
       <c r="F66" t="n">
-        <v>11.15</v>
+        <v>12.22</v>
       </c>
       <c r="G66" t="n">
-        <v>156.3</v>
+        <v>142.6</v>
       </c>
       <c r="H66" t="n">
-        <v>26.8</v>
+        <v>39</v>
       </c>
       <c r="I66" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>71.98999999999999</v>
+        <v>139.3</v>
       </c>
       <c r="K66" t="n">
-        <v>-86.19</v>
+        <v>0.79</v>
       </c>
       <c r="L66" t="n">
-        <v>112.3</v>
+        <v>139.3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:24:14</t>
+          <t>07:19:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.41</v>
+        <v>3.89</v>
       </c>
       <c r="F67" t="n">
-        <v>10.59</v>
+        <v>11.11</v>
       </c>
       <c r="G67" t="n">
-        <v>153.6</v>
+        <v>152.7</v>
       </c>
       <c r="H67" t="n">
-        <v>48.3</v>
+        <v>35.4</v>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-107.33</v>
+        <v>114.2</v>
       </c>
       <c r="K67" t="n">
-        <v>-22.82</v>
+        <v>108.2</v>
       </c>
       <c r="L67" t="n">
-        <v>109.73</v>
+        <v>157.32</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:28:26</t>
+          <t>07:24:01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.09</v>
+        <v>2.96</v>
       </c>
       <c r="F68" t="n">
-        <v>6.38</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G68" t="n">
         <v>158</v>
       </c>
       <c r="H68" t="n">
-        <v>54.3</v>
+        <v>48.1</v>
       </c>
       <c r="I68" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J68" t="n">
-        <v>19</v>
+        <v>-198.86</v>
       </c>
       <c r="K68" t="n">
-        <v>-208.08</v>
+        <v>36.14</v>
       </c>
       <c r="L68" t="n">
-        <v>208.95</v>
+        <v>202.12</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:30:32</t>
+          <t>07:24:35</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.69</v>
+        <v>3.89</v>
       </c>
       <c r="F69" t="n">
-        <v>12.3</v>
+        <v>10.71</v>
       </c>
       <c r="G69" t="n">
-        <v>145.5</v>
+        <v>155.3</v>
       </c>
       <c r="H69" t="n">
-        <v>30.5</v>
+        <v>48.4</v>
       </c>
       <c r="I69" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J69" t="n">
-        <v>-173.69</v>
+        <v>-196.64</v>
       </c>
       <c r="K69" t="n">
-        <v>-29.04</v>
+        <v>-199.24</v>
       </c>
       <c r="L69" t="n">
-        <v>176.1</v>
+        <v>279.94</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:32:53</t>
+          <t>07:26:34</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.47</v>
+        <v>4.52</v>
       </c>
       <c r="F70" t="n">
-        <v>10.88</v>
+        <v>10.11</v>
       </c>
       <c r="G70" t="n">
-        <v>157.4</v>
+        <v>155.2</v>
       </c>
       <c r="H70" t="n">
-        <v>22.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J70" t="n">
-        <v>-179.31</v>
+        <v>113.29</v>
       </c>
       <c r="K70" t="n">
-        <v>-69.06</v>
+        <v>303.37</v>
       </c>
       <c r="L70" t="n">
-        <v>192.15</v>
+        <v>323.83</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:38:06</t>
+          <t>07:31:10</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.82</v>
+        <v>4.01</v>
       </c>
       <c r="F71" t="n">
-        <v>10.18</v>
+        <v>13.11</v>
       </c>
       <c r="G71" t="n">
-        <v>155.5</v>
+        <v>152.8</v>
       </c>
       <c r="H71" t="n">
-        <v>43.4</v>
+        <v>17.9</v>
       </c>
       <c r="I71" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>-178.19</v>
+        <v>54.92</v>
       </c>
       <c r="K71" t="n">
-        <v>-164.53</v>
+        <v>-242.58</v>
       </c>
       <c r="L71" t="n">
-        <v>242.53</v>
+        <v>248.72</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:40:30</t>
+          <t>07:33:10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.33</v>
+        <v>3.34</v>
       </c>
       <c r="F72" t="n">
-        <v>11.26</v>
+        <v>11.41</v>
       </c>
       <c r="G72" t="n">
-        <v>152.5</v>
+        <v>144.8</v>
       </c>
       <c r="H72" t="n">
-        <v>62.1</v>
+        <v>37.7</v>
       </c>
       <c r="I72" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J72" t="n">
-        <v>290.23</v>
+        <v>174.69</v>
       </c>
       <c r="K72" t="n">
-        <v>79.92</v>
+        <v>192.98</v>
       </c>
       <c r="L72" t="n">
-        <v>301.03</v>
+        <v>260.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:41:32</t>
+          <t>07:34:57</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.92</v>
+        <v>3.59</v>
       </c>
       <c r="F73" t="n">
-        <v>9.359999999999999</v>
+        <v>12.58</v>
       </c>
       <c r="G73" t="n">
-        <v>143.2</v>
+        <v>163.4</v>
       </c>
       <c r="H73" t="n">
-        <v>30</v>
+        <v>20.6</v>
       </c>
       <c r="I73" t="n">
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>230.47</v>
+        <v>199.76</v>
       </c>
       <c r="K73" t="n">
-        <v>-192.63</v>
+        <v>117.82</v>
       </c>
       <c r="L73" t="n">
-        <v>300.37</v>
+        <v>231.91</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:53:03</t>
+          <t>07:47:07</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.93</v>
+        <v>4.49</v>
       </c>
       <c r="F74" t="n">
         <v>13.11</v>
       </c>
       <c r="G74" t="n">
-        <v>157.9</v>
+        <v>160.2</v>
       </c>
       <c r="H74" t="n">
-        <v>13.1</v>
+        <v>54.8</v>
       </c>
       <c r="I74" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J74" t="n">
-        <v>-85.56</v>
+        <v>17.24</v>
       </c>
       <c r="K74" t="n">
-        <v>58.49</v>
+        <v>79.62</v>
       </c>
       <c r="L74" t="n">
-        <v>103.64</v>
+        <v>81.45999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:55:21</t>
+          <t>07:48:18</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.34</v>
+        <v>4.1</v>
       </c>
       <c r="F75" t="n">
-        <v>12.91</v>
+        <v>13.11</v>
       </c>
       <c r="G75" t="n">
-        <v>155.4</v>
+        <v>154.9</v>
       </c>
       <c r="H75" t="n">
-        <v>36.1</v>
+        <v>44.2</v>
       </c>
       <c r="I75" t="n">
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-81.22</v>
+        <v>32.69</v>
       </c>
       <c r="K75" t="n">
-        <v>-55.68</v>
+        <v>67.72</v>
       </c>
       <c r="L75" t="n">
-        <v>98.47</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:56:45</t>
+          <t>07:49:39</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.98</v>
+        <v>4.06</v>
       </c>
       <c r="F76" t="n">
-        <v>13.11</v>
+        <v>11.42</v>
       </c>
       <c r="G76" t="n">
-        <v>152.6</v>
+        <v>155.9</v>
       </c>
       <c r="H76" t="n">
-        <v>28.5</v>
+        <v>28</v>
       </c>
       <c r="I76" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J76" t="n">
-        <v>-63.24</v>
+        <v>-28.03</v>
       </c>
       <c r="K76" t="n">
-        <v>52.1</v>
+        <v>-97.11</v>
       </c>
       <c r="L76" t="n">
-        <v>81.94</v>
+        <v>101.07</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:01:18</t>
+          <t>07:52:45</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="F77" t="n">
         <v>13.11</v>
       </c>
       <c r="G77" t="n">
-        <v>156.7</v>
+        <v>161.7</v>
       </c>
       <c r="H77" t="n">
-        <v>45.2</v>
+        <v>30.5</v>
       </c>
       <c r="I77" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J77" t="n">
-        <v>7.55</v>
+        <v>41.34</v>
       </c>
       <c r="K77" t="n">
-        <v>-113.86</v>
+        <v>-45.98</v>
       </c>
       <c r="L77" t="n">
-        <v>114.11</v>
+        <v>61.84</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:03:16</t>
+          <t>07:54:01</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.07</v>
+        <v>4.3</v>
       </c>
       <c r="F78" t="n">
-        <v>13.11</v>
+        <v>12.31</v>
       </c>
       <c r="G78" t="n">
-        <v>148</v>
+        <v>149.9</v>
       </c>
       <c r="H78" t="n">
-        <v>33.7</v>
+        <v>17.5</v>
       </c>
       <c r="I78" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>63.22</v>
+        <v>-119.96</v>
       </c>
       <c r="K78" t="n">
-        <v>-103.96</v>
+        <v>-7.9</v>
       </c>
       <c r="L78" t="n">
-        <v>121.68</v>
+        <v>120.22</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:05:09</t>
+          <t>07:56:13</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.96</v>
+        <v>4.46</v>
       </c>
       <c r="F79" t="n">
         <v>13.11</v>
       </c>
       <c r="G79" t="n">
-        <v>152.6</v>
+        <v>158</v>
       </c>
       <c r="H79" t="n">
-        <v>51.6</v>
+        <v>72.2</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>-90.79000000000001</v>
+        <v>54.75</v>
       </c>
       <c r="K79" t="n">
-        <v>-4.99</v>
+        <v>-75.89</v>
       </c>
       <c r="L79" t="n">
-        <v>90.92</v>
+        <v>93.56999999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:10:37</t>
+          <t>08:00:12</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.78</v>
+        <v>3.41</v>
       </c>
       <c r="F80" t="n">
-        <v>10.4</v>
+        <v>10.36</v>
       </c>
       <c r="G80" t="n">
-        <v>151.2</v>
+        <v>161.6</v>
       </c>
       <c r="H80" t="n">
-        <v>56.4</v>
+        <v>29.1</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J80" t="n">
-        <v>110.41</v>
+        <v>120.52</v>
       </c>
       <c r="K80" t="n">
-        <v>-92.87</v>
+        <v>-45.1</v>
       </c>
       <c r="L80" t="n">
-        <v>144.27</v>
+        <v>128.68</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:11:53</t>
+          <t>08:02:18</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="F81" t="n">
-        <v>13.11</v>
+        <v>10.97</v>
       </c>
       <c r="G81" t="n">
-        <v>154.5</v>
+        <v>161.4</v>
       </c>
       <c r="H81" t="n">
-        <v>50.2</v>
+        <v>32.3</v>
       </c>
       <c r="I81" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J81" t="n">
-        <v>178.07</v>
+        <v>-109.49</v>
       </c>
       <c r="K81" t="n">
-        <v>-58.64</v>
+        <v>102.74</v>
       </c>
       <c r="L81" t="n">
-        <v>187.47</v>
+        <v>150.14</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:14:37</t>
+          <t>08:03:13</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.25</v>
+        <v>4.35</v>
       </c>
       <c r="F82" t="n">
-        <v>10.23</v>
+        <v>13.11</v>
       </c>
       <c r="G82" t="n">
-        <v>154.9</v>
+        <v>145.8</v>
       </c>
       <c r="H82" t="n">
-        <v>40.2</v>
+        <v>22.6</v>
       </c>
       <c r="I82" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J82" t="n">
-        <v>-5.03</v>
+        <v>-61.41</v>
       </c>
       <c r="K82" t="n">
-        <v>-110.4</v>
+        <v>140.84</v>
       </c>
       <c r="L82" t="n">
-        <v>110.51</v>
+        <v>153.65</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:19:47</t>
+          <t>08:06:53</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.39</v>
+        <v>3.53</v>
       </c>
       <c r="F83" t="n">
-        <v>8.01</v>
+        <v>9.34</v>
       </c>
       <c r="G83" t="n">
-        <v>158.2</v>
+        <v>151</v>
       </c>
       <c r="H83" t="n">
-        <v>13.3</v>
+        <v>19.6</v>
       </c>
       <c r="I83" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>-172.21</v>
+        <v>-10.85</v>
       </c>
       <c r="K83" t="n">
-        <v>-81.05</v>
+        <v>-125.67</v>
       </c>
       <c r="L83" t="n">
-        <v>190.33</v>
+        <v>126.13</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:20:51</t>
+          <t>08:07:38</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.79</v>
+        <v>4.02</v>
       </c>
       <c r="F84" t="n">
-        <v>8.109999999999999</v>
+        <v>13.11</v>
       </c>
       <c r="G84" t="n">
-        <v>158.1</v>
+        <v>170.8</v>
       </c>
       <c r="H84" t="n">
-        <v>25.7</v>
+        <v>52.6</v>
       </c>
       <c r="I84" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J84" t="n">
-        <v>213.69</v>
+        <v>-97.41</v>
       </c>
       <c r="K84" t="n">
-        <v>27.59</v>
+        <v>-156.15</v>
       </c>
       <c r="L84" t="n">
-        <v>215.46</v>
+        <v>184.04</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:22:43</t>
+          <t>08:10:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.45</v>
+        <v>4.35</v>
       </c>
       <c r="F85" t="n">
-        <v>12.45</v>
+        <v>13.11</v>
       </c>
       <c r="G85" t="n">
-        <v>176.4</v>
+        <v>154.4</v>
       </c>
       <c r="H85" t="n">
-        <v>76.2</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J85" t="n">
-        <v>-262.27</v>
+        <v>203.69</v>
       </c>
       <c r="K85" t="n">
-        <v>73.48</v>
+        <v>220.67</v>
       </c>
       <c r="L85" t="n">
-        <v>272.36</v>
+        <v>300.3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:27:31</t>
+          <t>08:14:27</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="F86" t="n">
-        <v>10.29</v>
+        <v>11.89</v>
       </c>
       <c r="G86" t="n">
-        <v>142.6</v>
+        <v>159.8</v>
       </c>
       <c r="H86" t="n">
-        <v>51.3</v>
+        <v>16</v>
       </c>
       <c r="I86" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>144.44</v>
+        <v>-104.19</v>
       </c>
       <c r="K86" t="n">
-        <v>-135.46</v>
+        <v>173.77</v>
       </c>
       <c r="L86" t="n">
-        <v>198.02</v>
+        <v>202.61</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:29:06</t>
+          <t>08:15:42</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.03</v>
+        <v>3.73</v>
       </c>
       <c r="F87" t="n">
-        <v>12.85</v>
+        <v>13.11</v>
       </c>
       <c r="G87" t="n">
-        <v>150.6</v>
+        <v>158.1</v>
       </c>
       <c r="H87" t="n">
-        <v>39.6</v>
+        <v>23.9</v>
       </c>
       <c r="I87" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>273.94</v>
+        <v>-88.09999999999999</v>
       </c>
       <c r="K87" t="n">
-        <v>-11.83</v>
+        <v>-242.85</v>
       </c>
       <c r="L87" t="n">
-        <v>274.19</v>
+        <v>258.33</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:30:12</t>
+          <t>08:16:52</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.16</v>
+        <v>3.57</v>
       </c>
       <c r="F88" t="n">
-        <v>11.14</v>
+        <v>8.66</v>
       </c>
       <c r="G88" t="n">
-        <v>148.5</v>
+        <v>148.2</v>
       </c>
       <c r="H88" t="n">
-        <v>34.5</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>260.83</v>
+        <v>225.93</v>
       </c>
       <c r="K88" t="n">
-        <v>-192.43</v>
+        <v>-57.35</v>
       </c>
       <c r="L88" t="n">
-        <v>324.13</v>
+        <v>233.1</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-24.xlsx
+++ b/output/2025-05-24.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-66.70999999999999</v>
+        <v>-64.48</v>
       </c>
       <c r="K14" t="n">
-        <v>-19.31</v>
+        <v>-18.67</v>
       </c>
       <c r="L14" t="n">
-        <v>69.45</v>
+        <v>67.13</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-42.14</v>
+        <v>-42.3</v>
       </c>
       <c r="K15" t="n">
-        <v>46.24</v>
+        <v>46.42</v>
       </c>
       <c r="L15" t="n">
-        <v>62.56</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>5.59</v>
+        <v>5.28</v>
       </c>
       <c r="K16" t="n">
-        <v>93.3</v>
+        <v>88.04000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>93.45999999999999</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>41.11</v>
+        <v>42.63</v>
       </c>
       <c r="K17" t="n">
-        <v>67.05</v>
+        <v>69.53</v>
       </c>
       <c r="L17" t="n">
-        <v>78.65000000000001</v>
+        <v>81.56</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>38.89</v>
+        <v>39.76</v>
       </c>
       <c r="K18" t="n">
-        <v>58.6</v>
+        <v>59.92</v>
       </c>
       <c r="L18" t="n">
-        <v>70.33</v>
+        <v>71.91</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>40.33</v>
+        <v>42.71</v>
       </c>
       <c r="K19" t="n">
-        <v>41.75</v>
+        <v>44.22</v>
       </c>
       <c r="L19" t="n">
-        <v>58.05</v>
+        <v>61.48</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>25.59</v>
+        <v>29.74</v>
       </c>
       <c r="K20" t="n">
-        <v>-73.56999999999999</v>
+        <v>-85.5</v>
       </c>
       <c r="L20" t="n">
-        <v>77.90000000000001</v>
+        <v>90.53</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>128.67</v>
+        <v>132.79</v>
       </c>
       <c r="K21" t="n">
-        <v>17.22</v>
+        <v>17.78</v>
       </c>
       <c r="L21" t="n">
-        <v>129.82</v>
+        <v>133.98</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-20.74</v>
+        <v>-23.44</v>
       </c>
       <c r="K22" t="n">
-        <v>-79.14</v>
+        <v>-89.42</v>
       </c>
       <c r="L22" t="n">
-        <v>81.81</v>
+        <v>92.44</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>116.86</v>
+        <v>128.11</v>
       </c>
       <c r="K23" t="n">
-        <v>-78.88</v>
+        <v>-86.48</v>
       </c>
       <c r="L23" t="n">
-        <v>141</v>
+        <v>154.57</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-19.77</v>
+        <v>-22.46</v>
       </c>
       <c r="K24" t="n">
-        <v>-135.97</v>
+        <v>-154.49</v>
       </c>
       <c r="L24" t="n">
-        <v>137.4</v>
+        <v>156.11</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>47.07</v>
+        <v>56.2</v>
       </c>
       <c r="K25" t="n">
-        <v>84.64</v>
+        <v>101.06</v>
       </c>
       <c r="L25" t="n">
-        <v>96.84999999999999</v>
+        <v>115.64</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>188.42</v>
+        <v>221.66</v>
       </c>
       <c r="K26" t="n">
-        <v>-77.41</v>
+        <v>-91.06</v>
       </c>
       <c r="L26" t="n">
-        <v>203.7</v>
+        <v>239.63</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>251.92</v>
+        <v>272.69</v>
       </c>
       <c r="K27" t="n">
-        <v>42.61</v>
+        <v>46.12</v>
       </c>
       <c r="L27" t="n">
-        <v>255.5</v>
+        <v>276.56</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-19.25</v>
+        <v>-21.69</v>
       </c>
       <c r="K28" t="n">
-        <v>179.3</v>
+        <v>202.07</v>
       </c>
       <c r="L28" t="n">
-        <v>180.33</v>
+        <v>203.23</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-30.75</v>
+        <v>-34.02</v>
       </c>
       <c r="K29" t="n">
-        <v>32.57</v>
+        <v>36.03</v>
       </c>
       <c r="L29" t="n">
-        <v>44.79</v>
+        <v>49.56</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>57.88</v>
+        <v>56.5</v>
       </c>
       <c r="K30" t="n">
-        <v>53.39</v>
+        <v>52.12</v>
       </c>
       <c r="L30" t="n">
-        <v>78.73999999999999</v>
+        <v>76.87</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-42.32</v>
+        <v>-40.84</v>
       </c>
       <c r="K31" t="n">
-        <v>-74.90000000000001</v>
+        <v>-72.27</v>
       </c>
       <c r="L31" t="n">
-        <v>86.03</v>
+        <v>83.01000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>-38.66</v>
+        <v>-40.63</v>
       </c>
       <c r="K32" t="n">
-        <v>-46.76</v>
+        <v>-49.14</v>
       </c>
       <c r="L32" t="n">
-        <v>60.67</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-69.22</v>
+        <v>-70.3</v>
       </c>
       <c r="K33" t="n">
-        <v>-39.38</v>
+        <v>-39.99</v>
       </c>
       <c r="L33" t="n">
-        <v>79.64</v>
+        <v>80.88</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>-85.72</v>
+        <v>-88.7</v>
       </c>
       <c r="K34" t="n">
-        <v>-10.6</v>
+        <v>-10.96</v>
       </c>
       <c r="L34" t="n">
-        <v>86.37</v>
+        <v>89.37</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-66.83</v>
+        <v>-72.52</v>
       </c>
       <c r="K35" t="n">
-        <v>-71.02</v>
+        <v>-77.06</v>
       </c>
       <c r="L35" t="n">
-        <v>97.52</v>
+        <v>105.81</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-39.56</v>
+        <v>-40.01</v>
       </c>
       <c r="K36" t="n">
-        <v>-132.86</v>
+        <v>-134.39</v>
       </c>
       <c r="L36" t="n">
-        <v>138.62</v>
+        <v>140.22</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>69.04000000000001</v>
+        <v>68.97</v>
       </c>
       <c r="K37" t="n">
-        <v>-134.63</v>
+        <v>-134.5</v>
       </c>
       <c r="L37" t="n">
-        <v>151.3</v>
+        <v>151.15</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-9.699999999999999</v>
+        <v>-11.72</v>
       </c>
       <c r="K38" t="n">
-        <v>-88.69</v>
+        <v>-107.19</v>
       </c>
       <c r="L38" t="n">
-        <v>89.20999999999999</v>
+        <v>107.83</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-98.14</v>
+        <v>-114.14</v>
       </c>
       <c r="K39" t="n">
-        <v>53.52</v>
+        <v>62.25</v>
       </c>
       <c r="L39" t="n">
-        <v>111.78</v>
+        <v>130.01</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>162.04</v>
+        <v>169.69</v>
       </c>
       <c r="K40" t="n">
-        <v>-137.42</v>
+        <v>-143.91</v>
       </c>
       <c r="L40" t="n">
-        <v>212.46</v>
+        <v>222.49</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>250.78</v>
+        <v>269.47</v>
       </c>
       <c r="K41" t="n">
-        <v>71.56</v>
+        <v>76.89</v>
       </c>
       <c r="L41" t="n">
-        <v>260.79</v>
+        <v>280.22</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>125.32</v>
+        <v>140.73</v>
       </c>
       <c r="K42" t="n">
-        <v>-201.66</v>
+        <v>-226.46</v>
       </c>
       <c r="L42" t="n">
-        <v>237.43</v>
+        <v>266.63</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-23.03</v>
+        <v>-26.2</v>
       </c>
       <c r="K43" t="n">
-        <v>-217.39</v>
+        <v>-247.3</v>
       </c>
       <c r="L43" t="n">
-        <v>218.61</v>
+        <v>248.69</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>56.02</v>
+        <v>55.18</v>
       </c>
       <c r="K44" t="n">
-        <v>-38.21</v>
+        <v>-37.63</v>
       </c>
       <c r="L44" t="n">
-        <v>67.81</v>
+        <v>66.79000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>71.01000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>10.82</v>
+        <v>10.72</v>
       </c>
       <c r="L45" t="n">
-        <v>71.83</v>
+        <v>71.20999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-24.77</v>
+        <v>-26.04</v>
       </c>
       <c r="K46" t="n">
-        <v>-52.06</v>
+        <v>-54.73</v>
       </c>
       <c r="L46" t="n">
-        <v>57.65</v>
+        <v>60.61</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>8.1</v>
+        <v>8.67</v>
       </c>
       <c r="K47" t="n">
-        <v>70.77</v>
+        <v>75.72</v>
       </c>
       <c r="L47" t="n">
-        <v>71.23999999999999</v>
+        <v>76.22</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>39.24</v>
+        <v>43.52</v>
       </c>
       <c r="K48" t="n">
-        <v>-55.81</v>
+        <v>-61.9</v>
       </c>
       <c r="L48" t="n">
-        <v>68.23</v>
+        <v>75.67</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>-47.9</v>
+        <v>-53.8</v>
       </c>
       <c r="K49" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="L49" t="n">
-        <v>47.92</v>
+        <v>53.83</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>70.86</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>-36.54</v>
+        <v>-40.95</v>
       </c>
       <c r="L50" t="n">
-        <v>79.73</v>
+        <v>89.34</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-19.21</v>
+        <v>-20.31</v>
       </c>
       <c r="K51" t="n">
-        <v>139.65</v>
+        <v>147.62</v>
       </c>
       <c r="L51" t="n">
-        <v>140.96</v>
+        <v>149.02</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>30.92</v>
+        <v>32.05</v>
       </c>
       <c r="K52" t="n">
-        <v>-141.36</v>
+        <v>-146.55</v>
       </c>
       <c r="L52" t="n">
-        <v>144.7</v>
+        <v>150.01</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>17.23</v>
+        <v>21.24</v>
       </c>
       <c r="K53" t="n">
-        <v>37.48</v>
+        <v>46.21</v>
       </c>
       <c r="L53" t="n">
-        <v>41.25</v>
+        <v>50.86</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>136.19</v>
+        <v>149.26</v>
       </c>
       <c r="K54" t="n">
-        <v>-84.79000000000001</v>
+        <v>-92.93000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>160.43</v>
+        <v>175.83</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-33.1</v>
+        <v>-38.42</v>
       </c>
       <c r="K55" t="n">
-        <v>150.09</v>
+        <v>174.25</v>
       </c>
       <c r="L55" t="n">
-        <v>153.7</v>
+        <v>178.44</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>91.94</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>-388.92</v>
+        <v>-406.97</v>
       </c>
       <c r="L56" t="n">
-        <v>399.64</v>
+        <v>418.19</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>28.83</v>
+        <v>36.89</v>
       </c>
       <c r="K57" t="n">
-        <v>166.9</v>
+        <v>213.56</v>
       </c>
       <c r="L57" t="n">
-        <v>169.38</v>
+        <v>216.73</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>104.08</v>
+        <v>137.58</v>
       </c>
       <c r="K58" t="n">
-        <v>-115.82</v>
+        <v>-153.1</v>
       </c>
       <c r="L58" t="n">
-        <v>155.71</v>
+        <v>205.84</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>8.42</v>
+        <v>8.92</v>
       </c>
       <c r="K59" t="n">
-        <v>53.72</v>
+        <v>56.88</v>
       </c>
       <c r="L59" t="n">
-        <v>54.38</v>
+        <v>57.58</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>-50.83</v>
+        <v>-49.77</v>
       </c>
       <c r="K60" t="n">
-        <v>-49.09</v>
+        <v>-48.07</v>
       </c>
       <c r="L60" t="n">
-        <v>70.66</v>
+        <v>69.19</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>47.55</v>
+        <v>48.92</v>
       </c>
       <c r="K61" t="n">
-        <v>-32.08</v>
+        <v>-33.01</v>
       </c>
       <c r="L61" t="n">
-        <v>57.36</v>
+        <v>59.02</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>15.63</v>
+        <v>14.62</v>
       </c>
       <c r="K62" t="n">
-        <v>-121.16</v>
+        <v>-113.34</v>
       </c>
       <c r="L62" t="n">
-        <v>122.16</v>
+        <v>114.28</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-53.26</v>
+        <v>-52.49</v>
       </c>
       <c r="K63" t="n">
-        <v>-88.13</v>
+        <v>-86.86</v>
       </c>
       <c r="L63" t="n">
-        <v>102.98</v>
+        <v>101.49</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-31.6</v>
+        <v>-30.78</v>
       </c>
       <c r="K64" t="n">
-        <v>87.55</v>
+        <v>85.27</v>
       </c>
       <c r="L64" t="n">
-        <v>93.08</v>
+        <v>90.66</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.18</v>
+        <v>-2.5</v>
       </c>
       <c r="K65" t="n">
-        <v>95.79000000000001</v>
+        <v>109.85</v>
       </c>
       <c r="L65" t="n">
-        <v>95.81999999999999</v>
+        <v>109.88</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.05</v>
+        <v>-3.67</v>
       </c>
       <c r="K66" t="n">
-        <v>-76.72</v>
+        <v>-92.33</v>
       </c>
       <c r="L66" t="n">
-        <v>76.78</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>52.54</v>
+        <v>57.59</v>
       </c>
       <c r="K67" t="n">
-        <v>-73.16</v>
+        <v>-80.19</v>
       </c>
       <c r="L67" t="n">
-        <v>90.06999999999999</v>
+        <v>98.73</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>95.54000000000001</v>
+        <v>104.62</v>
       </c>
       <c r="K68" t="n">
-        <v>-112.99</v>
+        <v>-123.73</v>
       </c>
       <c r="L68" t="n">
-        <v>147.97</v>
+        <v>162.03</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>69.65000000000001</v>
+        <v>82.48</v>
       </c>
       <c r="K69" t="n">
-        <v>-95.26000000000001</v>
+        <v>-112.81</v>
       </c>
       <c r="L69" t="n">
-        <v>118.01</v>
+        <v>139.75</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>104.87</v>
+        <v>116.36</v>
       </c>
       <c r="K70" t="n">
-        <v>-104.44</v>
+        <v>-115.9</v>
       </c>
       <c r="L70" t="n">
-        <v>148</v>
+        <v>164.23</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>190.64</v>
+        <v>197.72</v>
       </c>
       <c r="K71" t="n">
-        <v>-274.34</v>
+        <v>-284.53</v>
       </c>
       <c r="L71" t="n">
-        <v>334.08</v>
+        <v>346.49</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-130.64</v>
+        <v>-147.1</v>
       </c>
       <c r="K72" t="n">
-        <v>-183.16</v>
+        <v>-206.23</v>
       </c>
       <c r="L72" t="n">
-        <v>224.98</v>
+        <v>253.31</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-84.58</v>
+        <v>-99.89</v>
       </c>
       <c r="K73" t="n">
-        <v>-159.57</v>
+        <v>-188.44</v>
       </c>
       <c r="L73" t="n">
-        <v>180.6</v>
+        <v>213.27</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>65.92</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-8.550000000000001</v>
+        <v>-8.43</v>
       </c>
       <c r="L74" t="n">
-        <v>66.47</v>
+        <v>65.55</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-41</v>
+        <v>-43.38</v>
       </c>
       <c r="K75" t="n">
-        <v>-45.9</v>
+        <v>-48.57</v>
       </c>
       <c r="L75" t="n">
-        <v>61.54</v>
+        <v>65.12</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>64.33</v>
+        <v>64.55</v>
       </c>
       <c r="K76" t="n">
-        <v>34.66</v>
+        <v>34.78</v>
       </c>
       <c r="L76" t="n">
-        <v>73.06999999999999</v>
+        <v>73.31999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-56.75</v>
+        <v>-60.52</v>
       </c>
       <c r="K77" t="n">
-        <v>-33.98</v>
+        <v>-36.23</v>
       </c>
       <c r="L77" t="n">
-        <v>66.15000000000001</v>
+        <v>70.54000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-35.1</v>
+        <v>-39.78</v>
       </c>
       <c r="K78" t="n">
-        <v>53.36</v>
+        <v>60.47</v>
       </c>
       <c r="L78" t="n">
-        <v>63.87</v>
+        <v>72.38</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>-52.23</v>
+        <v>-55.87</v>
       </c>
       <c r="K79" t="n">
-        <v>-28.73</v>
+        <v>-30.73</v>
       </c>
       <c r="L79" t="n">
-        <v>59.61</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-40.18</v>
+        <v>-45.61</v>
       </c>
       <c r="K80" t="n">
-        <v>-77.22</v>
+        <v>-87.66</v>
       </c>
       <c r="L80" t="n">
-        <v>87.05</v>
+        <v>98.81</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>18.39</v>
+        <v>20.88</v>
       </c>
       <c r="K81" t="n">
-        <v>-84.8</v>
+        <v>-96.29000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>86.78</v>
+        <v>98.52</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>126.62</v>
+        <v>129.9</v>
       </c>
       <c r="K82" t="n">
-        <v>36.92</v>
+        <v>37.88</v>
       </c>
       <c r="L82" t="n">
-        <v>131.9</v>
+        <v>135.31</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>75.05</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>-82.38</v>
+        <v>-101.06</v>
       </c>
       <c r="L83" t="n">
-        <v>111.44</v>
+        <v>136.71</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-63.81</v>
+        <v>-75.8</v>
       </c>
       <c r="K84" t="n">
-        <v>-99.17</v>
+        <v>-117.79</v>
       </c>
       <c r="L84" t="n">
-        <v>117.92</v>
+        <v>140.07</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>96.22</v>
+        <v>124.42</v>
       </c>
       <c r="K85" t="n">
-        <v>-81.56</v>
+        <v>-105.46</v>
       </c>
       <c r="L85" t="n">
-        <v>126.14</v>
+        <v>163.11</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>251.78</v>
+        <v>287.75</v>
       </c>
       <c r="K86" t="n">
-        <v>32.86</v>
+        <v>37.56</v>
       </c>
       <c r="L86" t="n">
-        <v>253.91</v>
+        <v>290.19</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-168.48</v>
+        <v>-221.12</v>
       </c>
       <c r="K87" t="n">
-        <v>-108.76</v>
+        <v>-142.74</v>
       </c>
       <c r="L87" t="n">
-        <v>200.53</v>
+        <v>263.19</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>65.61</v>
+        <v>77.37</v>
       </c>
       <c r="K88" t="n">
-        <v>235.66</v>
+        <v>277.88</v>
       </c>
       <c r="L88" t="n">
-        <v>244.62</v>
+        <v>288.45</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-24.xlsx
+++ b/output/2025-05-24.xlsx
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-42.3</v>
+        <v>-47.39</v>
       </c>
       <c r="K15" t="n">
-        <v>46.42</v>
+        <v>52.01</v>
       </c>
       <c r="L15" t="n">
-        <v>62.8</v>
+        <v>70.37</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>5.28</v>
+        <v>5.65</v>
       </c>
       <c r="K16" t="n">
-        <v>88.04000000000001</v>
+        <v>94.25</v>
       </c>
       <c r="L16" t="n">
-        <v>88.2</v>
+        <v>94.42</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>42.63</v>
+        <v>47.86</v>
       </c>
       <c r="K17" t="n">
-        <v>69.53</v>
+        <v>78.06</v>
       </c>
       <c r="L17" t="n">
-        <v>81.56</v>
+        <v>91.56</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>39.76</v>
+        <v>43.44</v>
       </c>
       <c r="K18" t="n">
-        <v>59.92</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>71.91</v>
+        <v>78.56</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>42.71</v>
+        <v>43.21</v>
       </c>
       <c r="K19" t="n">
-        <v>44.22</v>
+        <v>44.73</v>
       </c>
       <c r="L19" t="n">
-        <v>61.48</v>
+        <v>62.19</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-34.02</v>
+        <v>-37.74</v>
       </c>
       <c r="K29" t="n">
-        <v>36.03</v>
+        <v>39.97</v>
       </c>
       <c r="L29" t="n">
-        <v>49.56</v>
+        <v>54.97</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>56.5</v>
+        <v>64.08</v>
       </c>
       <c r="K30" t="n">
-        <v>52.12</v>
+        <v>59.11</v>
       </c>
       <c r="L30" t="n">
-        <v>76.87</v>
+        <v>87.18000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-40.84</v>
+        <v>-42.74</v>
       </c>
       <c r="K31" t="n">
-        <v>-72.27</v>
+        <v>-75.64</v>
       </c>
       <c r="L31" t="n">
-        <v>83.01000000000001</v>
+        <v>86.88</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>-40.63</v>
+        <v>-41.19</v>
       </c>
       <c r="K32" t="n">
-        <v>-49.14</v>
+        <v>-49.82</v>
       </c>
       <c r="L32" t="n">
-        <v>63.76</v>
+        <v>64.64</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-70.3</v>
+        <v>-75.56</v>
       </c>
       <c r="K33" t="n">
-        <v>-39.99</v>
+        <v>-42.99</v>
       </c>
       <c r="L33" t="n">
-        <v>80.88</v>
+        <v>86.93000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>-88.7</v>
+        <v>-113.69</v>
       </c>
       <c r="K34" t="n">
-        <v>-10.96</v>
+        <v>-14.05</v>
       </c>
       <c r="L34" t="n">
-        <v>89.37</v>
+        <v>114.56</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>55.18</v>
+        <v>61.58</v>
       </c>
       <c r="K44" t="n">
-        <v>-37.63</v>
+        <v>-42</v>
       </c>
       <c r="L44" t="n">
-        <v>66.79000000000001</v>
+        <v>74.54000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>70.40000000000001</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>10.72</v>
+        <v>13.17</v>
       </c>
       <c r="L45" t="n">
-        <v>71.20999999999999</v>
+        <v>87.45999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-26.04</v>
+        <v>-32.12</v>
       </c>
       <c r="K46" t="n">
-        <v>-54.73</v>
+        <v>-67.48999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>60.61</v>
+        <v>74.75</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>8.67</v>
+        <v>9.94</v>
       </c>
       <c r="K47" t="n">
-        <v>75.72</v>
+        <v>86.86</v>
       </c>
       <c r="L47" t="n">
-        <v>76.22</v>
+        <v>87.42</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>43.52</v>
+        <v>46.71</v>
       </c>
       <c r="K48" t="n">
-        <v>-61.9</v>
+        <v>-66.44</v>
       </c>
       <c r="L48" t="n">
-        <v>75.67</v>
+        <v>81.22</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>-53.8</v>
+        <v>-56.51</v>
       </c>
       <c r="K49" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="L49" t="n">
-        <v>53.83</v>
+        <v>56.54</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>8.92</v>
+        <v>9.4</v>
       </c>
       <c r="K59" t="n">
-        <v>56.88</v>
+        <v>59.98</v>
       </c>
       <c r="L59" t="n">
-        <v>57.58</v>
+        <v>60.71</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>-49.77</v>
+        <v>-59.64</v>
       </c>
       <c r="K60" t="n">
-        <v>-48.07</v>
+        <v>-57.6</v>
       </c>
       <c r="L60" t="n">
-        <v>69.19</v>
+        <v>82.92</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>48.92</v>
+        <v>55.6</v>
       </c>
       <c r="K61" t="n">
-        <v>-33.01</v>
+        <v>-37.51</v>
       </c>
       <c r="L61" t="n">
-        <v>59.02</v>
+        <v>67.06999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>14.62</v>
+        <v>15.69</v>
       </c>
       <c r="K62" t="n">
-        <v>-113.34</v>
+        <v>-121.65</v>
       </c>
       <c r="L62" t="n">
-        <v>114.28</v>
+        <v>122.65</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-52.49</v>
+        <v>-60.67</v>
       </c>
       <c r="K63" t="n">
-        <v>-86.86</v>
+        <v>-100.4</v>
       </c>
       <c r="L63" t="n">
-        <v>101.49</v>
+        <v>117.31</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-30.78</v>
+        <v>-37.61</v>
       </c>
       <c r="K64" t="n">
-        <v>85.27</v>
+        <v>104.2</v>
       </c>
       <c r="L64" t="n">
-        <v>90.66</v>
+        <v>110.78</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>65.01000000000001</v>
+        <v>79.52</v>
       </c>
       <c r="K74" t="n">
-        <v>-8.43</v>
+        <v>-10.31</v>
       </c>
       <c r="L74" t="n">
-        <v>65.55</v>
+        <v>80.18000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-43.38</v>
+        <v>-52.09</v>
       </c>
       <c r="K75" t="n">
-        <v>-48.57</v>
+        <v>-58.32</v>
       </c>
       <c r="L75" t="n">
-        <v>65.12</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>64.55</v>
+        <v>73.20999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>34.78</v>
+        <v>39.44</v>
       </c>
       <c r="L76" t="n">
-        <v>73.31999999999999</v>
+        <v>83.16</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-60.52</v>
+        <v>-67.73999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>-36.23</v>
+        <v>-40.55</v>
       </c>
       <c r="L77" t="n">
-        <v>70.54000000000001</v>
+        <v>78.95</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-39.78</v>
+        <v>-52.49</v>
       </c>
       <c r="K78" t="n">
-        <v>60.47</v>
+        <v>79.8</v>
       </c>
       <c r="L78" t="n">
-        <v>72.38</v>
+        <v>95.51000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>-55.87</v>
+        <v>-58.04</v>
       </c>
       <c r="K79" t="n">
-        <v>-30.73</v>
+        <v>-31.92</v>
       </c>
       <c r="L79" t="n">
-        <v>63.76</v>
+        <v>66.23999999999999</v>
       </c>
     </row>
     <row r="80">
